--- a/spec/meals/Meals Acceptance Checklist v1.0.xlsx
+++ b/spec/meals/Meals Acceptance Checklist v1.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wcoop\Documents\HomeMaintenanceApp\spec\meals\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D6E245C-B71E-4126-9FC5-DFB143FC9110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7036922-060B-48E0-A57F-6D69BEA330D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5030" uniqueCount="1128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5032" uniqueCount="1132">
   <si>
     <t>Meals Acceptance Checklist</t>
   </si>
@@ -3100,9 +3100,6 @@
   </si>
   <si>
     <t>Owner navigation works; logged-out access does not expose private data; nested routing remains usable.</t>
-  </si>
-  <si>
-    <t>Remove any incidental test data; sign out if appropriate.</t>
   </si>
   <si>
     <t>E2E-01</t>
@@ -3489,33 +3486,9 @@
     <t>P0-TECH-001</t>
   </si>
   <si>
-    <t>Top-level Meals link technically validated; owner UAT remains. MEALS-DEF-001 CLOSED: initial workbook date marshaling failed before save; original bytes preserved. COM variant setter fixed and isolated-copy dated-update/integrity tests passed. Local dev base 07fee6170fd48880d4bde57e13d05e65c3cbbc0c.</t>
-  </si>
-  <si>
     <t>MEALS-DEF-001</t>
   </si>
   <si>
-    <t>spec/meals/README.md#phase-0a-technical-evidence</t>
-  </si>
-  <si>
-    <t>Recipes/Shopping switching and active states technically verified. Non-data-backed Phase 0A placeholders only; owner UAT remains.</t>
-  </si>
-  <si>
-    <t>Explicit /meals namespace and unknown/nested Meals isolation tested; /cooking not introduced. Owner UAT remains.</t>
-  </si>
-  <si>
-    <t>/meals/recipes foundation route tested beneath actual hosted basename; no Recipe Library data functionality claimed. Owner UAT remains.</t>
-  </si>
-  <si>
-    <t>/meals replacement redirect to /meals/recipes verified in local browser with the real router and synthetic Auth transport. Owner UAT remains.</t>
-  </si>
-  <si>
-    <t>Shared shell at 1280px: no horizontal overflow, correct active links, 44px internal navigation. Desktop screenshot inspected; owner visual/usability UAT remains.</t>
-  </si>
-  <si>
-    <t>Same responsive shell at 375px: no horizontal overflow, wrapped navigation, 44px internal controls. Mobile browser screenshot inspected; physical Capacitor/device UAT remains.</t>
-  </si>
-  <si>
     <t>Executed routing/auth regressions and local browser synthetic-transport checks. Meals mounts under the unchanged existing exact-owner boundary/controller; no separate Meals login or data subsystem.</t>
   </si>
   <si>
@@ -3535,6 +3508,45 @@
   </si>
   <si>
     <t>spec/meals/README.md#phase-0a-technical-evidence; web release validation: spec/meals/README.md#web-release-validation</t>
+  </si>
+  <si>
+    <t>P0-UAT-001</t>
+  </si>
+  <si>
+    <t>spec/meals/README.md#phase-0a-technical-evidence; P0-UAT-001: designated owner reported live Life Manager UAT PASS on 2026-10-28; release 8298e2e0797ddff7d2d53cc058fa41fb407ac0ab; recorded by Copilot from owner report, not automated authenticated verification</t>
+  </si>
+  <si>
+    <t>Top-level Meals link technically validated; owner UAT remains. MEALS-DEF-001 CLOSED: initial workbook date marshaling failed before save; original bytes preserved. COM variant setter fixed and isolated-copy dated-update/integrity tests passed. Local dev base 07fee6170fd48880d4bde57e13d05e65c3cbbc0c.; P0-UAT-001 owner report: Meals appeared in live navigation; navigation/routing, desktop and mobile responsive presentation, and complete E2E-00 passed; everything else worked as expected. Add Recipe is intentionally nonfunctional in Phase 0A; Recipe Editor is Phase 1, not a defect or future-feature acceptance. Prior technical run P0-TECH-001 and its evidence remain above. Mobile result is live-web UAT, not a native Capacitor release.</t>
+  </si>
+  <si>
+    <t>Recipes/Shopping switching and active states technically verified. Non-data-backed Phase 0A placeholders only; owner UAT remains.; P0-UAT-001 owner report: Meals appeared in live navigation; navigation/routing, desktop and mobile responsive presentation, and complete E2E-00 passed; everything else worked as expected. Add Recipe is intentionally nonfunctional in Phase 0A; Recipe Editor is Phase 1, not a defect or future-feature acceptance. Prior technical run P0-TECH-001 and its evidence remain above. Mobile result is live-web UAT, not a native Capacitor release.</t>
+  </si>
+  <si>
+    <t>Explicit /meals namespace and unknown/nested Meals isolation tested; /cooking not introduced. Owner UAT remains.; P0-UAT-001 owner report: Meals appeared in live navigation; navigation/routing, desktop and mobile responsive presentation, and complete E2E-00 passed; everything else worked as expected. Add Recipe is intentionally nonfunctional in Phase 0A; Recipe Editor is Phase 1, not a defect or future-feature acceptance. Prior technical run P0-TECH-001 and its evidence remain above. Mobile result is live-web UAT, not a native Capacitor release.</t>
+  </si>
+  <si>
+    <t>/meals/recipes foundation route tested beneath actual hosted basename; no Recipe Library data functionality claimed. Owner UAT remains.; P0-UAT-001 owner report: Meals appeared in live navigation; navigation/routing, desktop and mobile responsive presentation, and complete E2E-00 passed; everything else worked as expected. Add Recipe is intentionally nonfunctional in Phase 0A; Recipe Editor is Phase 1, not a defect or future-feature acceptance. Prior technical run P0-TECH-001 and its evidence remain above. Mobile result is live-web UAT, not a native Capacitor release.</t>
+  </si>
+  <si>
+    <t>/meals replacement redirect to /meals/recipes verified in local browser with the real router and synthetic Auth transport. Owner UAT remains.; P0-UAT-001 owner report: Meals appeared in live navigation; navigation/routing, desktop and mobile responsive presentation, and complete E2E-00 passed; everything else worked as expected. Add Recipe is intentionally nonfunctional in Phase 0A; Recipe Editor is Phase 1, not a defect or future-feature acceptance. Prior technical run P0-TECH-001 and its evidence remain above. Mobile result is live-web UAT, not a native Capacitor release.</t>
+  </si>
+  <si>
+    <t>Shared shell at 1280px: no horizontal overflow, correct active links, 44px internal navigation. Desktop screenshot inspected; owner visual/usability UAT remains.; P0-UAT-001 owner report: Meals appeared in live navigation; navigation/routing, desktop and mobile responsive presentation, and complete E2E-00 passed; everything else worked as expected. Add Recipe is intentionally nonfunctional in Phase 0A; Recipe Editor is Phase 1, not a defect or future-feature acceptance. Prior technical run P0-TECH-001 and its evidence remain above. Mobile result is live-web UAT, not a native Capacitor release.</t>
+  </si>
+  <si>
+    <t>Same responsive shell at 375px: no horizontal overflow, wrapped navigation, 44px internal controls. Mobile browser screenshot inspected; physical Capacitor/device UAT remains.; P0-UAT-001 owner report: Meals appeared in live navigation; navigation/routing, desktop and mobile responsive presentation, and complete E2E-00 passed; everything else worked as expected. Add Recipe is intentionally nonfunctional in Phase 0A; Recipe Editor is Phase 1, not a defect or future-feature acceptance. Prior technical run P0-TECH-001 and its evidence remain above. Mobile result is live-web UAT, not a native Capacitor release.</t>
+  </si>
+  <si>
+    <t>Remove any incidental test data; sign out if appropriate.; P0-UAT-001 owner report: Meals appeared in live navigation; navigation/routing, desktop and mobile responsive presentation, and complete E2E-00 passed; everything else worked as expected. Add Recipe is intentionally nonfunctional in Phase 0A; Recipe Editor is Phase 1, not a defect or future-feature acceptance. Prior technical run P0-TECH-001 and its evidence remain above. Mobile result is live-web UAT, not a native Capacitor release.</t>
+  </si>
+  <si>
+    <t>Accepted</t>
+  </si>
+  <si>
+    <t>2026-10-28</t>
+  </si>
+  <si>
+    <t>Phase 0A Meals foundation accepted. Live web routing, navigation, owner-auth integration, responsive shell, nested route refresh, and E2E-00 passed. Acceptance includes the Acceptance Workbook update tooling and Phase 0A release/deployment infrastructure. Recipe persistence, Recipe functionality beyond the Phase 0A shell/placeholders (including Add/Edit), Shopping functionality/persistence, meal-plan persistence, Weekly Planner meal integration, Recipe Import, future Meals database objects, and future Meals database-security/catalog verification remain outside this acceptance and are not yet accepted. Owner explicitly authorized this scope-limited acceptance on 2026-10-28 following P0-UAT-001.</t>
   </si>
 </sst>
 </file>
@@ -4779,7 +4791,7 @@
       </c>
       <c r="C7" s="5">
         <f>COUNTIF('Functional Acceptance'!$L:$L,"Pass")</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D7" s="5">
         <f>COUNTIF('Functional Acceptance'!$L:$L,"Pass with Known Issue")</f>
@@ -4795,7 +4807,7 @@
       </c>
       <c r="G7" s="5">
         <f>COUNTIF('Functional Acceptance'!$L:$L,"Ready to Test")</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H7" s="5">
         <f>COUNTIF('Functional Acceptance'!$L:$L,"Not Built")</f>
@@ -4816,7 +4828,7 @@
       </c>
       <c r="C8" s="5">
         <f>COUNTIF('End-to-End Tests'!$J:$J,"Pass")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="5">
         <f>COUNTIF('End-to-End Tests'!$J:$J,"Pass with Known Issue")</f>
@@ -4832,7 +4844,7 @@
       </c>
       <c r="G8" s="5">
         <f>COUNTIF('End-to-End Tests'!$J:$J,"Ready to Test")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" s="5">
         <f>COUNTIF('End-to-End Tests'!$J:$J,"Not Built")</f>
@@ -5110,7 +5122,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>48</v>
       </c>
@@ -5126,7 +5138,7 @@
       </c>
       <c r="E23" s="2">
         <f>COUNTIFS('Functional Acceptance'!D:D,A23,'Functional Acceptance'!L:L,"Pass")+COUNTIFS('Security Acceptance'!D:D,A23,'Security Acceptance'!N:N,"Pass")+COUNTIFS('Database Verification'!D:D,A23,'Database Verification'!N:N,"Pass")+COUNTIFS('End-to-End Tests'!C:C,A23,'End-to-End Tests'!J:J,"Pass")</f>
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F23" s="2">
         <f>COUNTIFS('Functional Acceptance'!D:D,A23,'Functional Acceptance'!L:L,"Pass with Known Issue")+COUNTIFS('Security Acceptance'!D:D,A23,'Security Acceptance'!N:N,"Pass with Known Issue")+COUNTIFS('Database Verification'!D:D,A23,'Database Verification'!N:N,"Pass with Known Issue")+COUNTIFS('End-to-End Tests'!C:C,A23,'End-to-End Tests'!J:J,"Pass with Known Issue")</f>
@@ -5160,10 +5172,14 @@
         <v>70</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="P23" s="2"/>
-      <c r="Q23" s="2"/>
+        <v>1129</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>1131</v>
+      </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
@@ -5475,7 +5491,7 @@
     </row>
     <row r="2" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1111</v>
+        <v>1119</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>94</v>
@@ -5508,24 +5524,24 @@
         <v>102</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M2" s="7">
         <v>46323</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>1114</v>
+        <v>1120</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>1112</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>1111</v>
+        <v>1119</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>103</v>
@@ -5558,22 +5574,22 @@
         <v>106</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M3" s="7">
         <v>46323</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2" t="s">
-        <v>1114</v>
+        <v>1120</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>1115</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1111</v>
+        <v>1119</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>107</v>
@@ -5606,22 +5622,22 @@
         <v>111</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M4" s="7">
         <v>46323</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2" t="s">
-        <v>1114</v>
+        <v>1120</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>1116</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>1111</v>
+        <v>1119</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>112</v>
@@ -5654,17 +5670,17 @@
         <v>115</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M5" s="7">
         <v>46323</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2" t="s">
-        <v>1114</v>
+        <v>1120</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>1117</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="60" x14ac:dyDescent="0.25">
@@ -5789,7 +5805,7 @@
     </row>
     <row r="9" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>1111</v>
+        <v>1119</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>128</v>
@@ -5822,17 +5838,17 @@
         <v>131</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M9" s="7">
         <v>46323</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2" t="s">
-        <v>1114</v>
+        <v>1120</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>1118</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="45" x14ac:dyDescent="0.25">
@@ -11957,7 +11973,7 @@
     </row>
     <row r="163" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
-        <v>1111</v>
+        <v>1119</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>765</v>
@@ -11990,22 +12006,22 @@
         <v>770</v>
       </c>
       <c r="L163" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M163" s="7">
         <v>46323</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" s="2" t="s">
-        <v>1114</v>
+        <v>1120</v>
       </c>
       <c r="P163" s="2" t="s">
-        <v>1119</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="164" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
-        <v>1111</v>
+        <v>1119</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>771</v>
@@ -12038,17 +12054,17 @@
         <v>770</v>
       </c>
       <c r="L164" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M164" s="7">
         <v>46323</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" s="2" t="s">
-        <v>1114</v>
+        <v>1120</v>
       </c>
       <c r="P164" s="2" t="s">
-        <v>1120</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="165" spans="1:16" ht="45" x14ac:dyDescent="0.25">
@@ -12601,7 +12617,7 @@
     </row>
     <row r="2" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>812</v>
@@ -12647,10 +12663,10 @@
       </c>
       <c r="P2" s="2"/>
       <c r="Q2" s="2" t="s">
-        <v>1127</v>
+        <v>1118</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>1121</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="90" x14ac:dyDescent="0.25">
@@ -12839,7 +12855,7 @@
     </row>
     <row r="7" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>840</v>
@@ -12885,15 +12901,15 @@
       </c>
       <c r="P7" s="2"/>
       <c r="Q7" s="2" t="s">
-        <v>1127</v>
+        <v>1118</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>1122</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>845</v>
@@ -12939,15 +12955,15 @@
       </c>
       <c r="P8" s="2"/>
       <c r="Q8" s="2" t="s">
-        <v>1127</v>
+        <v>1118</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>1123</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>849</v>
@@ -12993,10 +13009,10 @@
       </c>
       <c r="P9" s="2"/>
       <c r="Q9" s="2" t="s">
-        <v>1127</v>
+        <v>1118</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>1124</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="60" x14ac:dyDescent="0.25">
@@ -13415,7 +13431,7 @@
     </row>
     <row r="19" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>892</v>
@@ -13461,10 +13477,10 @@
       </c>
       <c r="P19" s="2"/>
       <c r="Q19" s="2" t="s">
-        <v>1127</v>
+        <v>1118</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>1125</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="20" spans="1:18" ht="90" x14ac:dyDescent="0.25">
@@ -13561,7 +13577,7 @@
     </row>
     <row r="22" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>904</v>
@@ -13607,10 +13623,10 @@
       </c>
       <c r="P22" s="2"/>
       <c r="Q22" s="2" t="s">
-        <v>1127</v>
+        <v>1118</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>1126</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="23" spans="1:18" ht="60" x14ac:dyDescent="0.25">
@@ -14887,7 +14903,7 @@
     </row>
     <row r="2" spans="1:15" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1111</v>
+        <v>1119</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>992</v>
@@ -14914,24 +14930,24 @@
         <v>997</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K2" s="7">
         <v>46323</v>
       </c>
       <c r="L2" s="2"/>
       <c r="M2" s="2" t="s">
-        <v>1114</v>
+        <v>1120</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2" t="s">
-        <v>998</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="105" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="2" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>50</v>
@@ -14940,19 +14956,19 @@
         <v>98</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>999</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>1000</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>1001</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>1002</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>1003</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>1004</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>6</v>
@@ -14961,14 +14977,14 @@
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
       <c r="N3" s="2" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="O3" s="2"/>
     </row>
     <row r="4" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="2" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>50</v>
@@ -14977,19 +14993,19 @@
         <v>98</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>1006</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>1007</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>1008</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>1009</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>1010</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>1011</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>6</v>
@@ -14998,14 +15014,14 @@
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
       <c r="N4" s="2" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="O4" s="2"/>
     </row>
     <row r="5" spans="1:15" ht="90" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="2" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>52</v>
@@ -15014,19 +15030,19 @@
         <v>98</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>1012</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>1013</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>1014</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>1015</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>1016</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>1017</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>6</v>
@@ -15035,14 +15051,14 @@
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
       <c r="N5" s="2" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="O5" s="2"/>
     </row>
     <row r="6" spans="1:15" ht="150" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>52</v>
@@ -15051,19 +15067,19 @@
         <v>98</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>1018</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>1019</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>1020</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>1021</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="I6" s="2" t="s">
         <v>1022</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>1023</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>6</v>
@@ -15072,14 +15088,14 @@
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
       <c r="N6" s="2" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="O6" s="2"/>
     </row>
     <row r="7" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>54</v>
@@ -15088,19 +15104,19 @@
         <v>98</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>1025</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>1026</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>1027</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="I7" s="2" t="s">
         <v>1028</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>1029</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>6</v>
@@ -15109,14 +15125,14 @@
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
       <c r="N7" s="2" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="O7" s="2"/>
     </row>
     <row r="8" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>54</v>
@@ -15125,19 +15141,19 @@
         <v>98</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>1031</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>1032</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>1033</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="I8" s="2" t="s">
         <v>1034</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>1035</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>6</v>
@@ -15146,14 +15162,14 @@
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="O8" s="2"/>
     </row>
     <row r="9" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>54</v>
@@ -15162,19 +15178,19 @@
         <v>98</v>
       </c>
       <c r="E9" s="2" t="s">
+        <v>1036</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>1037</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="G9" s="2" t="s">
         <v>1038</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="H9" s="2" t="s">
         <v>1039</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="I9" s="2" t="s">
         <v>1040</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>1041</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>6</v>
@@ -15183,14 +15199,14 @@
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="O9" s="2"/>
     </row>
     <row r="10" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="2" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>54</v>
@@ -15199,19 +15215,19 @@
         <v>98</v>
       </c>
       <c r="E10" s="2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>1043</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="G10" s="2" t="s">
         <v>1044</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="H10" s="2" t="s">
         <v>1045</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="I10" s="2" t="s">
         <v>1046</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>1047</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>6</v>
@@ -15220,14 +15236,14 @@
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="O10" s="2"/>
     </row>
     <row r="11" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>54</v>
@@ -15236,19 +15252,19 @@
         <v>98</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>758</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="H11" s="2" t="s">
+        <v>1050</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>1051</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>1052</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>6</v>
@@ -15257,14 +15273,14 @@
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
       <c r="N11" s="2" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="O11" s="2"/>
     </row>
     <row r="12" spans="1:15" ht="75" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>50</v>
@@ -15273,19 +15289,19 @@
         <v>98</v>
       </c>
       <c r="E12" s="2" t="s">
+        <v>1053</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>1054</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="G12" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="H12" s="2" t="s">
         <v>1056</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="I12" s="2" t="s">
         <v>1057</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>1058</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>6</v>
@@ -15295,13 +15311,13 @@
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
       <c r="O12" s="2" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="105" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>52</v>
@@ -15310,19 +15326,19 @@
         <v>98</v>
       </c>
       <c r="E13" s="2" t="s">
+        <v>1060</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>1061</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="G13" s="2" t="s">
         <v>1062</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="H13" s="2" t="s">
         <v>1063</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="I13" s="2" t="s">
         <v>1064</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>1065</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>6</v>
@@ -15332,7 +15348,7 @@
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
       <c r="O13" s="2" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
     </row>
   </sheetData>
@@ -15443,31 +15459,31 @@
         <v>84</v>
       </c>
       <c r="F1" s="6" t="s">
+        <v>1066</v>
+      </c>
+      <c r="G1" s="6" t="s">
         <v>1067</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="6" t="s">
         <v>1068</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="I1" s="6" t="s">
         <v>1069</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="J1" s="6" t="s">
         <v>1070</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="6" t="s">
         <v>1071</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>1072</v>
       </c>
       <c r="L1" s="6" t="s">
         <v>91</v>
       </c>
       <c r="M1" s="6" t="s">
+        <v>1072</v>
+      </c>
+      <c r="N1" s="6" t="s">
         <v>1073</v>
-      </c>
-      <c r="N1" s="6" t="s">
-        <v>1074</v>
       </c>
       <c r="O1" s="6" t="s">
         <v>47</v>
@@ -15493,7 +15509,7 @@
         <v>821</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>43</v>
@@ -15518,7 +15534,7 @@
         <v>spec/meals/README.md#phase-0a-technical-evidence; web release validation: spec/meals/README.md#web-release-validation</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O2" s="2"/>
     </row>
@@ -15542,7 +15558,7 @@
         <v>826</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>43</v>
@@ -15567,7 +15583,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O3" s="2"/>
     </row>
@@ -15591,7 +15607,7 @@
         <v>831</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>43</v>
@@ -15616,7 +15632,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O4" s="2"/>
     </row>
@@ -15640,7 +15656,7 @@
         <v>835</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>43</v>
@@ -15665,7 +15681,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O5" s="2"/>
     </row>
@@ -15689,7 +15705,7 @@
         <v>839</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>43</v>
@@ -15714,7 +15730,7 @@
         <v>0</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O6" s="2"/>
     </row>
@@ -15738,7 +15754,7 @@
         <v>844</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>43</v>
@@ -15763,7 +15779,7 @@
         <v>spec/meals/README.md#phase-0a-technical-evidence; web release validation: spec/meals/README.md#web-release-validation</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O7" s="2"/>
     </row>
@@ -15787,7 +15803,7 @@
         <v>848</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>43</v>
@@ -15812,7 +15828,7 @@
         <v>spec/meals/README.md#phase-0a-technical-evidence; web release validation: spec/meals/README.md#web-release-validation</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O8" s="2"/>
     </row>
@@ -15836,7 +15852,7 @@
         <v>852</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>43</v>
@@ -15861,7 +15877,7 @@
         <v>spec/meals/README.md#phase-0a-technical-evidence; web release validation: spec/meals/README.md#web-release-validation</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O9" s="2"/>
     </row>
@@ -15885,7 +15901,7 @@
         <v>856</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>43</v>
@@ -15910,7 +15926,7 @@
         <v>0</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O10" s="2"/>
     </row>
@@ -15934,7 +15950,7 @@
         <v>933</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>44</v>
@@ -15956,13 +15972,13 @@
         <v>0</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O11" s="2"/>
     </row>
     <row r="12" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>54</v>
@@ -15977,13 +15993,13 @@
         <v>98</v>
       </c>
       <c r="F12" s="2" t="s">
+        <v>1078</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>1079</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="H12" s="2" t="s">
         <v>1080</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>1081</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
@@ -15991,7 +16007,7 @@
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="O12" s="2"/>
     </row>
@@ -16015,7 +16031,7 @@
         <v>860</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>43</v>
@@ -16040,7 +16056,7 @@
         <v>0</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O13" s="2"/>
     </row>
@@ -16064,7 +16080,7 @@
         <v>864</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>43</v>
@@ -16089,7 +16105,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O14" s="2"/>
     </row>
@@ -16113,7 +16129,7 @@
         <v>868</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>43</v>
@@ -16138,7 +16154,7 @@
         <v>0</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O15" s="2"/>
     </row>
@@ -16162,7 +16178,7 @@
         <v>938</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>44</v>
@@ -16184,7 +16200,7 @@
         <v>0</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O16" s="2"/>
     </row>
@@ -16208,7 +16224,7 @@
         <v>102</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>41</v>
@@ -16218,7 +16234,7 @@
       </c>
       <c r="J17" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I17,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K17" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I17,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -16230,10 +16246,10 @@
       </c>
       <c r="M17" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I17,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>spec/meals/README.md#phase-0a-technical-evidence</v>
+        <v>spec/meals/README.md#phase-0a-technical-evidence; P0-UAT-001: designated owner reported live Life Manager UAT PASS on 2026-10-28; release 8298e2e0797ddff7d2d53cc058fa41fb407ac0ab; recorded by Copilot from owner report, not automated authenticated verification</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O17" s="2"/>
     </row>
@@ -16257,7 +16273,7 @@
         <v>106</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>41</v>
@@ -16267,7 +16283,7 @@
       </c>
       <c r="J18" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I18,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K18" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I18,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -16279,10 +16295,10 @@
       </c>
       <c r="M18" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I18,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>spec/meals/README.md#phase-0a-technical-evidence</v>
+        <v>spec/meals/README.md#phase-0a-technical-evidence; P0-UAT-001: designated owner reported live Life Manager UAT PASS on 2026-10-28; release 8298e2e0797ddff7d2d53cc058fa41fb407ac0ab; recorded by Copilot from owner report, not automated authenticated verification</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O18" s="2"/>
     </row>
@@ -16306,7 +16322,7 @@
         <v>111</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>41</v>
@@ -16316,7 +16332,7 @@
       </c>
       <c r="J19" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I19,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K19" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I19,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -16328,10 +16344,10 @@
       </c>
       <c r="M19" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I19,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>spec/meals/README.md#phase-0a-technical-evidence</v>
+        <v>spec/meals/README.md#phase-0a-technical-evidence; P0-UAT-001: designated owner reported live Life Manager UAT PASS on 2026-10-28; release 8298e2e0797ddff7d2d53cc058fa41fb407ac0ab; recorded by Copilot from owner report, not automated authenticated verification</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O19" s="2"/>
     </row>
@@ -16355,7 +16371,7 @@
         <v>115</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>41</v>
@@ -16365,7 +16381,7 @@
       </c>
       <c r="J20" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I20,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K20" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I20,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -16377,10 +16393,10 @@
       </c>
       <c r="M20" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I20,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>spec/meals/README.md#phase-0a-technical-evidence</v>
+        <v>spec/meals/README.md#phase-0a-technical-evidence; P0-UAT-001: designated owner reported live Life Manager UAT PASS on 2026-10-28; release 8298e2e0797ddff7d2d53cc058fa41fb407ac0ab; recorded by Copilot from owner report, not automated authenticated verification</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O20" s="2"/>
     </row>
@@ -16404,7 +16420,7 @@
         <v>119</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>41</v>
@@ -16429,7 +16445,7 @@
         <v>0</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O21" s="2"/>
     </row>
@@ -16453,7 +16469,7 @@
         <v>123</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>41</v>
@@ -16478,7 +16494,7 @@
         <v>0</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O22" s="2"/>
     </row>
@@ -16502,7 +16518,7 @@
         <v>127</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>41</v>
@@ -16527,13 +16543,13 @@
         <v>0</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O23" s="2"/>
     </row>
     <row r="24" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>56</v>
@@ -16548,13 +16564,13 @@
         <v>98</v>
       </c>
       <c r="F24" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>1085</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="H24" s="2" t="s">
         <v>1086</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>1087</v>
       </c>
       <c r="I24" s="2"/>
       <c r="J24" s="2" t="s">
@@ -16588,7 +16604,7 @@
         <v>131</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>41</v>
@@ -16598,7 +16614,7 @@
       </c>
       <c r="J25" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I25,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K25" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I25,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -16610,10 +16626,10 @@
       </c>
       <c r="M25" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I25,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>spec/meals/README.md#phase-0a-technical-evidence</v>
+        <v>spec/meals/README.md#phase-0a-technical-evidence; P0-UAT-001: designated owner reported live Life Manager UAT PASS on 2026-10-28; release 8298e2e0797ddff7d2d53cc058fa41fb407ac0ab; recorded by Copilot from owner report, not automated authenticated verification</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O25" s="2"/>
     </row>
@@ -16637,7 +16653,7 @@
         <v>139</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>41</v>
@@ -16662,7 +16678,7 @@
         <v>0</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O26" s="2"/>
     </row>
@@ -16686,7 +16702,7 @@
         <v>146</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>41</v>
@@ -16711,7 +16727,7 @@
         <v>0</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O27" s="2"/>
     </row>
@@ -16735,7 +16751,7 @@
         <v>150</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>41</v>
@@ -16760,7 +16776,7 @@
         <v>0</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O28" s="2"/>
     </row>
@@ -16784,7 +16800,7 @@
         <v>154</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>41</v>
@@ -16809,7 +16825,7 @@
         <v>0</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O29" s="2"/>
     </row>
@@ -16833,7 +16849,7 @@
         <v>159</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>41</v>
@@ -16858,7 +16874,7 @@
         <v>0</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O30" s="2"/>
     </row>
@@ -16882,7 +16898,7 @@
         <v>164</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>41</v>
@@ -16907,7 +16923,7 @@
         <v>0</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O31" s="2"/>
     </row>
@@ -16931,7 +16947,7 @@
         <v>168</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>41</v>
@@ -16956,7 +16972,7 @@
         <v>0</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O32" s="2"/>
     </row>
@@ -16980,7 +16996,7 @@
         <v>172</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>41</v>
@@ -17005,7 +17021,7 @@
         <v>0</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O33" s="2"/>
     </row>
@@ -17029,7 +17045,7 @@
         <v>176</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>41</v>
@@ -17054,7 +17070,7 @@
         <v>0</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O34" s="2"/>
     </row>
@@ -17078,7 +17094,7 @@
         <v>180</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>41</v>
@@ -17103,7 +17119,7 @@
         <v>0</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O35" s="2"/>
     </row>
@@ -17127,7 +17143,7 @@
         <v>184</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>41</v>
@@ -17152,7 +17168,7 @@
         <v>0</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O36" s="2"/>
     </row>
@@ -17176,7 +17192,7 @@
         <v>189</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>41</v>
@@ -17201,7 +17217,7 @@
         <v>0</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O37" s="2"/>
     </row>
@@ -17225,7 +17241,7 @@
         <v>194</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>41</v>
@@ -17250,7 +17266,7 @@
         <v>0</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O38" s="2"/>
     </row>
@@ -17274,7 +17290,7 @@
         <v>198</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>41</v>
@@ -17299,7 +17315,7 @@
         <v>0</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O39" s="2"/>
     </row>
@@ -17323,7 +17339,7 @@
         <v>202</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>41</v>
@@ -17348,7 +17364,7 @@
         <v>0</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O40" s="2"/>
     </row>
@@ -17372,7 +17388,7 @@
         <v>206</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>41</v>
@@ -17397,7 +17413,7 @@
         <v>0</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O41" s="2"/>
     </row>
@@ -17421,7 +17437,7 @@
         <v>210</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>41</v>
@@ -17446,7 +17462,7 @@
         <v>0</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O42" s="2"/>
     </row>
@@ -17470,7 +17486,7 @@
         <v>214</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>41</v>
@@ -17495,7 +17511,7 @@
         <v>0</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O43" s="2"/>
     </row>
@@ -17519,7 +17535,7 @@
         <v>218</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>41</v>
@@ -17544,7 +17560,7 @@
         <v>0</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O44" s="2"/>
     </row>
@@ -17568,7 +17584,7 @@
         <v>222</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>41</v>
@@ -17593,7 +17609,7 @@
         <v>0</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O45" s="2"/>
     </row>
@@ -17617,7 +17633,7 @@
         <v>227</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>41</v>
@@ -17642,7 +17658,7 @@
         <v>0</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O46" s="2"/>
     </row>
@@ -17666,7 +17682,7 @@
         <v>231</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>41</v>
@@ -17691,7 +17707,7 @@
         <v>0</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O47" s="2"/>
     </row>
@@ -17715,7 +17731,7 @@
         <v>236</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>41</v>
@@ -17740,7 +17756,7 @@
         <v>0</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O48" s="2"/>
     </row>
@@ -17764,7 +17780,7 @@
         <v>240</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>41</v>
@@ -17789,7 +17805,7 @@
         <v>0</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O49" s="2"/>
     </row>
@@ -17813,7 +17829,7 @@
         <v>244</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>41</v>
@@ -17838,7 +17854,7 @@
         <v>0</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O50" s="2"/>
     </row>
@@ -17862,7 +17878,7 @@
         <v>249</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>41</v>
@@ -17887,7 +17903,7 @@
         <v>0</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O51" s="2"/>
     </row>
@@ -17911,7 +17927,7 @@
         <v>254</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>41</v>
@@ -17936,7 +17952,7 @@
         <v>0</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O52" s="2"/>
     </row>
@@ -17960,7 +17976,7 @@
         <v>258</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>41</v>
@@ -17985,7 +18001,7 @@
         <v>0</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O53" s="2"/>
     </row>
@@ -18009,7 +18025,7 @@
         <v>262</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>41</v>
@@ -18034,7 +18050,7 @@
         <v>0</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O54" s="2"/>
     </row>
@@ -18058,7 +18074,7 @@
         <v>266</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>41</v>
@@ -18083,7 +18099,7 @@
         <v>0</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O55" s="2"/>
     </row>
@@ -18107,7 +18123,7 @@
         <v>270</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>41</v>
@@ -18132,7 +18148,7 @@
         <v>0</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O56" s="2"/>
     </row>
@@ -18156,7 +18172,7 @@
         <v>274</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>41</v>
@@ -18181,7 +18197,7 @@
         <v>0</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O57" s="2"/>
     </row>
@@ -18205,7 +18221,7 @@
         <v>278</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>41</v>
@@ -18230,7 +18246,7 @@
         <v>0</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O58" s="2"/>
     </row>
@@ -18254,7 +18270,7 @@
         <v>282</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>41</v>
@@ -18279,7 +18295,7 @@
         <v>0</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O59" s="2"/>
     </row>
@@ -18303,7 +18319,7 @@
         <v>286</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>41</v>
@@ -18328,7 +18344,7 @@
         <v>0</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O60" s="2"/>
     </row>
@@ -18352,7 +18368,7 @@
         <v>290</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>41</v>
@@ -18377,7 +18393,7 @@
         <v>0</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O61" s="2"/>
     </row>
@@ -18401,7 +18417,7 @@
         <v>294</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>41</v>
@@ -18426,7 +18442,7 @@
         <v>0</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O62" s="2"/>
     </row>
@@ -18450,7 +18466,7 @@
         <v>299</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>41</v>
@@ -18475,7 +18491,7 @@
         <v>0</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O63" s="2"/>
     </row>
@@ -18499,7 +18515,7 @@
         <v>304</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>41</v>
@@ -18524,7 +18540,7 @@
         <v>0</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O64" s="2"/>
     </row>
@@ -18548,7 +18564,7 @@
         <v>308</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>41</v>
@@ -18573,7 +18589,7 @@
         <v>0</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O65" s="2"/>
     </row>
@@ -18597,7 +18613,7 @@
         <v>312</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>41</v>
@@ -18622,7 +18638,7 @@
         <v>0</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O66" s="2"/>
     </row>
@@ -18646,7 +18662,7 @@
         <v>316</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>41</v>
@@ -18671,7 +18687,7 @@
         <v>0</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O67" s="2"/>
     </row>
@@ -18695,7 +18711,7 @@
         <v>320</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>41</v>
@@ -18720,7 +18736,7 @@
         <v>0</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O68" s="2"/>
     </row>
@@ -18744,7 +18760,7 @@
         <v>324</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>41</v>
@@ -18769,7 +18785,7 @@
         <v>0</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O69" s="2"/>
     </row>
@@ -18793,7 +18809,7 @@
         <v>328</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>41</v>
@@ -18818,7 +18834,7 @@
         <v>0</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O70" s="2"/>
     </row>
@@ -18842,7 +18858,7 @@
         <v>332</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>41</v>
@@ -18867,7 +18883,7 @@
         <v>0</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O71" s="2"/>
     </row>
@@ -18891,7 +18907,7 @@
         <v>336</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>41</v>
@@ -18916,7 +18932,7 @@
         <v>0</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O72" s="2"/>
     </row>
@@ -18940,7 +18956,7 @@
         <v>340</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>41</v>
@@ -18965,7 +18981,7 @@
         <v>0</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O73" s="2"/>
     </row>
@@ -18989,7 +19005,7 @@
         <v>344</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>41</v>
@@ -19014,7 +19030,7 @@
         <v>0</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O74" s="2"/>
     </row>
@@ -19038,7 +19054,7 @@
         <v>349</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>41</v>
@@ -19063,7 +19079,7 @@
         <v>0</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O75" s="2"/>
     </row>
@@ -19087,7 +19103,7 @@
         <v>353</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>41</v>
@@ -19112,7 +19128,7 @@
         <v>0</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O76" s="2"/>
     </row>
@@ -19136,7 +19152,7 @@
         <v>357</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>41</v>
@@ -19161,7 +19177,7 @@
         <v>0</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O77" s="2"/>
     </row>
@@ -19185,7 +19201,7 @@
         <v>361</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>41</v>
@@ -19210,7 +19226,7 @@
         <v>0</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O78" s="2"/>
     </row>
@@ -19234,7 +19250,7 @@
         <v>365</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>41</v>
@@ -19259,7 +19275,7 @@
         <v>0</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O79" s="2"/>
     </row>
@@ -19283,7 +19299,7 @@
         <v>370</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>41</v>
@@ -19308,7 +19324,7 @@
         <v>0</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O80" s="2"/>
     </row>
@@ -19332,7 +19348,7 @@
         <v>375</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>41</v>
@@ -19357,7 +19373,7 @@
         <v>0</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O81" s="2"/>
     </row>
@@ -19381,7 +19397,7 @@
         <v>379</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>41</v>
@@ -19406,7 +19422,7 @@
         <v>0</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O82" s="2"/>
     </row>
@@ -19430,7 +19446,7 @@
         <v>384</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>41</v>
@@ -19455,7 +19471,7 @@
         <v>0</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O83" s="2"/>
     </row>
@@ -19479,7 +19495,7 @@
         <v>389</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>41</v>
@@ -19504,7 +19520,7 @@
         <v>0</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O84" s="2"/>
     </row>
@@ -19528,7 +19544,7 @@
         <v>393</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>41</v>
@@ -19553,7 +19569,7 @@
         <v>0</v>
       </c>
       <c r="N85" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O85" s="2"/>
     </row>
@@ -19577,7 +19593,7 @@
         <v>397</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>41</v>
@@ -19602,7 +19618,7 @@
         <v>0</v>
       </c>
       <c r="N86" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O86" s="2"/>
     </row>
@@ -19626,7 +19642,7 @@
         <v>402</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>41</v>
@@ -19651,7 +19667,7 @@
         <v>0</v>
       </c>
       <c r="N87" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O87" s="2"/>
     </row>
@@ -19675,7 +19691,7 @@
         <v>406</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>41</v>
@@ -19700,7 +19716,7 @@
         <v>0</v>
       </c>
       <c r="N88" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O88" s="2"/>
     </row>
@@ -19724,7 +19740,7 @@
         <v>410</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>41</v>
@@ -19749,7 +19765,7 @@
         <v>0</v>
       </c>
       <c r="N89" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O89" s="2"/>
     </row>
@@ -19773,7 +19789,7 @@
         <v>414</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>41</v>
@@ -19798,7 +19814,7 @@
         <v>0</v>
       </c>
       <c r="N90" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O90" s="2"/>
     </row>
@@ -19822,7 +19838,7 @@
         <v>418</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>41</v>
@@ -19847,7 +19863,7 @@
         <v>0</v>
       </c>
       <c r="N91" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O91" s="2"/>
     </row>
@@ -19871,7 +19887,7 @@
         <v>423</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>41</v>
@@ -19896,7 +19912,7 @@
         <v>0</v>
       </c>
       <c r="N92" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O92" s="2"/>
     </row>
@@ -19920,7 +19936,7 @@
         <v>427</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>41</v>
@@ -19945,7 +19961,7 @@
         <v>0</v>
       </c>
       <c r="N93" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O93" s="2"/>
     </row>
@@ -19969,7 +19985,7 @@
         <v>431</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>41</v>
@@ -19994,7 +20010,7 @@
         <v>0</v>
       </c>
       <c r="N94" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O94" s="2"/>
     </row>
@@ -20018,7 +20034,7 @@
         <v>435</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>41</v>
@@ -20043,7 +20059,7 @@
         <v>0</v>
       </c>
       <c r="N95" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O95" s="2"/>
     </row>
@@ -20067,7 +20083,7 @@
         <v>439</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>41</v>
@@ -20092,7 +20108,7 @@
         <v>0</v>
       </c>
       <c r="N96" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O96" s="2"/>
     </row>
@@ -20116,7 +20132,7 @@
         <v>443</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>41</v>
@@ -20141,7 +20157,7 @@
         <v>0</v>
       </c>
       <c r="N97" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O97" s="2"/>
     </row>
@@ -20165,7 +20181,7 @@
         <v>447</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>41</v>
@@ -20190,7 +20206,7 @@
         <v>0</v>
       </c>
       <c r="N98" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O98" s="2"/>
     </row>
@@ -20214,7 +20230,7 @@
         <v>452</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>41</v>
@@ -20239,7 +20255,7 @@
         <v>0</v>
       </c>
       <c r="N99" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O99" s="2"/>
     </row>
@@ -20263,7 +20279,7 @@
         <v>456</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>41</v>
@@ -20288,7 +20304,7 @@
         <v>0</v>
       </c>
       <c r="N100" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O100" s="2"/>
     </row>
@@ -20312,7 +20328,7 @@
         <v>460</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>41</v>
@@ -20337,7 +20353,7 @@
         <v>0</v>
       </c>
       <c r="N101" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O101" s="2"/>
     </row>
@@ -20361,7 +20377,7 @@
         <v>464</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>41</v>
@@ -20386,7 +20402,7 @@
         <v>0</v>
       </c>
       <c r="N102" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O102" s="2"/>
     </row>
@@ -20410,7 +20426,7 @@
         <v>470</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>41</v>
@@ -20435,7 +20451,7 @@
         <v>0</v>
       </c>
       <c r="N103" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O103" s="2"/>
     </row>
@@ -20459,7 +20475,7 @@
         <v>474</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>41</v>
@@ -20484,7 +20500,7 @@
         <v>0</v>
       </c>
       <c r="N104" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O104" s="2"/>
     </row>
@@ -20508,7 +20524,7 @@
         <v>478</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>41</v>
@@ -20533,7 +20549,7 @@
         <v>0</v>
       </c>
       <c r="N105" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O105" s="2"/>
     </row>
@@ -20557,7 +20573,7 @@
         <v>482</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>41</v>
@@ -20582,7 +20598,7 @@
         <v>0</v>
       </c>
       <c r="N106" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O106" s="2"/>
     </row>
@@ -20606,7 +20622,7 @@
         <v>486</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>41</v>
@@ -20631,7 +20647,7 @@
         <v>0</v>
       </c>
       <c r="N107" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O107" s="2"/>
     </row>
@@ -20655,7 +20671,7 @@
         <v>490</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>41</v>
@@ -20680,7 +20696,7 @@
         <v>0</v>
       </c>
       <c r="N108" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O108" s="2"/>
     </row>
@@ -20704,7 +20720,7 @@
         <v>494</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>41</v>
@@ -20729,7 +20745,7 @@
         <v>0</v>
       </c>
       <c r="N109" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O109" s="2"/>
     </row>
@@ -20753,7 +20769,7 @@
         <v>498</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>41</v>
@@ -20778,7 +20794,7 @@
         <v>0</v>
       </c>
       <c r="N110" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O110" s="2"/>
     </row>
@@ -20802,7 +20818,7 @@
         <v>502</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>41</v>
@@ -20827,7 +20843,7 @@
         <v>0</v>
       </c>
       <c r="N111" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O111" s="2"/>
     </row>
@@ -20851,7 +20867,7 @@
         <v>506</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>41</v>
@@ -20876,7 +20892,7 @@
         <v>0</v>
       </c>
       <c r="N112" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O112" s="2"/>
     </row>
@@ -20900,7 +20916,7 @@
         <v>511</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>41</v>
@@ -20925,7 +20941,7 @@
         <v>0</v>
       </c>
       <c r="N113" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O113" s="2"/>
     </row>
@@ -20949,7 +20965,7 @@
         <v>515</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>41</v>
@@ -20974,7 +20990,7 @@
         <v>0</v>
       </c>
       <c r="N114" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O114" s="2"/>
     </row>
@@ -20998,7 +21014,7 @@
         <v>520</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>41</v>
@@ -21023,7 +21039,7 @@
         <v>0</v>
       </c>
       <c r="N115" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O115" s="2"/>
     </row>
@@ -21047,7 +21063,7 @@
         <v>525</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>41</v>
@@ -21072,7 +21088,7 @@
         <v>0</v>
       </c>
       <c r="N116" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O116" s="2"/>
     </row>
@@ -21096,7 +21112,7 @@
         <v>529</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>41</v>
@@ -21121,7 +21137,7 @@
         <v>0</v>
       </c>
       <c r="N117" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O117" s="2"/>
     </row>
@@ -21145,7 +21161,7 @@
         <v>533</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>41</v>
@@ -21170,7 +21186,7 @@
         <v>0</v>
       </c>
       <c r="N118" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O118" s="2"/>
     </row>
@@ -21194,7 +21210,7 @@
         <v>537</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>41</v>
@@ -21219,7 +21235,7 @@
         <v>0</v>
       </c>
       <c r="N119" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O119" s="2"/>
     </row>
@@ -21243,7 +21259,7 @@
         <v>541</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>41</v>
@@ -21268,7 +21284,7 @@
         <v>0</v>
       </c>
       <c r="N120" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O120" s="2"/>
     </row>
@@ -21292,7 +21308,7 @@
         <v>545</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>41</v>
@@ -21317,7 +21333,7 @@
         <v>0</v>
       </c>
       <c r="N121" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O121" s="2"/>
     </row>
@@ -21341,7 +21357,7 @@
         <v>549</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>41</v>
@@ -21366,7 +21382,7 @@
         <v>0</v>
       </c>
       <c r="N122" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O122" s="2"/>
     </row>
@@ -21390,7 +21406,7 @@
         <v>553</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>41</v>
@@ -21415,7 +21431,7 @@
         <v>0</v>
       </c>
       <c r="N123" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O123" s="2"/>
     </row>
@@ -21439,7 +21455,7 @@
         <v>557</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>41</v>
@@ -21464,7 +21480,7 @@
         <v>0</v>
       </c>
       <c r="N124" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O124" s="2"/>
     </row>
@@ -21488,7 +21504,7 @@
         <v>561</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>41</v>
@@ -21513,7 +21529,7 @@
         <v>0</v>
       </c>
       <c r="N125" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O125" s="2"/>
     </row>
@@ -21537,7 +21553,7 @@
         <v>565</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>41</v>
@@ -21562,7 +21578,7 @@
         <v>0</v>
       </c>
       <c r="N126" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O126" s="2"/>
     </row>
@@ -21586,7 +21602,7 @@
         <v>569</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>41</v>
@@ -21611,7 +21627,7 @@
         <v>0</v>
       </c>
       <c r="N127" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O127" s="2"/>
     </row>
@@ -21635,7 +21651,7 @@
         <v>573</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>41</v>
@@ -21660,7 +21676,7 @@
         <v>0</v>
       </c>
       <c r="N128" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O128" s="2"/>
     </row>
@@ -21684,7 +21700,7 @@
         <v>577</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>41</v>
@@ -21709,7 +21725,7 @@
         <v>0</v>
       </c>
       <c r="N129" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O129" s="2"/>
     </row>
@@ -21733,7 +21749,7 @@
         <v>581</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>41</v>
@@ -21758,7 +21774,7 @@
         <v>0</v>
       </c>
       <c r="N130" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O130" s="2"/>
     </row>
@@ -21782,7 +21798,7 @@
         <v>585</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>41</v>
@@ -21807,7 +21823,7 @@
         <v>0</v>
       </c>
       <c r="N131" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O131" s="2"/>
     </row>
@@ -21831,7 +21847,7 @@
         <v>590</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>41</v>
@@ -21856,7 +21872,7 @@
         <v>0</v>
       </c>
       <c r="N132" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O132" s="2"/>
     </row>
@@ -21880,7 +21896,7 @@
         <v>594</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>41</v>
@@ -21905,7 +21921,7 @@
         <v>0</v>
       </c>
       <c r="N133" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O133" s="2"/>
     </row>
@@ -21929,7 +21945,7 @@
         <v>598</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>41</v>
@@ -21954,7 +21970,7 @@
         <v>0</v>
       </c>
       <c r="N134" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O134" s="2"/>
     </row>
@@ -21978,7 +21994,7 @@
         <v>602</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>41</v>
@@ -22003,7 +22019,7 @@
         <v>0</v>
       </c>
       <c r="N135" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O135" s="2"/>
     </row>
@@ -22027,7 +22043,7 @@
         <v>606</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>41</v>
@@ -22052,7 +22068,7 @@
         <v>0</v>
       </c>
       <c r="N136" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O136" s="2"/>
     </row>
@@ -22076,7 +22092,7 @@
         <v>610</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>41</v>
@@ -22101,7 +22117,7 @@
         <v>0</v>
       </c>
       <c r="N137" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O137" s="2"/>
     </row>
@@ -22125,7 +22141,7 @@
         <v>614</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>41</v>
@@ -22150,7 +22166,7 @@
         <v>0</v>
       </c>
       <c r="N138" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O138" s="2"/>
     </row>
@@ -22174,7 +22190,7 @@
         <v>618</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>41</v>
@@ -22199,7 +22215,7 @@
         <v>0</v>
       </c>
       <c r="N139" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O139" s="2"/>
     </row>
@@ -22223,7 +22239,7 @@
         <v>622</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>41</v>
@@ -22248,7 +22264,7 @@
         <v>0</v>
       </c>
       <c r="N140" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O140" s="2"/>
     </row>
@@ -22272,7 +22288,7 @@
         <v>626</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>41</v>
@@ -22297,7 +22313,7 @@
         <v>0</v>
       </c>
       <c r="N141" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O141" s="2"/>
     </row>
@@ -22321,7 +22337,7 @@
         <v>630</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>41</v>
@@ -22346,7 +22362,7 @@
         <v>0</v>
       </c>
       <c r="N142" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O142" s="2"/>
     </row>
@@ -22370,7 +22386,7 @@
         <v>634</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>41</v>
@@ -22395,7 +22411,7 @@
         <v>0</v>
       </c>
       <c r="N143" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O143" s="2"/>
     </row>
@@ -22419,7 +22435,7 @@
         <v>639</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>41</v>
@@ -22444,7 +22460,7 @@
         <v>0</v>
       </c>
       <c r="N144" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O144" s="2"/>
     </row>
@@ -22468,7 +22484,7 @@
         <v>644</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>41</v>
@@ -22493,7 +22509,7 @@
         <v>0</v>
       </c>
       <c r="N145" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O145" s="2"/>
     </row>
@@ -22517,7 +22533,7 @@
         <v>648</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>41</v>
@@ -22542,7 +22558,7 @@
         <v>0</v>
       </c>
       <c r="N146" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O146" s="2"/>
     </row>
@@ -22566,7 +22582,7 @@
         <v>652</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H147" s="2" t="s">
         <v>41</v>
@@ -22591,7 +22607,7 @@
         <v>0</v>
       </c>
       <c r="N147" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O147" s="2"/>
     </row>
@@ -22615,7 +22631,7 @@
         <v>656</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>41</v>
@@ -22640,7 +22656,7 @@
         <v>0</v>
       </c>
       <c r="N148" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O148" s="2"/>
     </row>
@@ -22664,7 +22680,7 @@
         <v>660</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H149" s="2" t="s">
         <v>41</v>
@@ -22689,7 +22705,7 @@
         <v>0</v>
       </c>
       <c r="N149" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O149" s="2"/>
     </row>
@@ -22713,7 +22729,7 @@
         <v>664</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H150" s="2" t="s">
         <v>41</v>
@@ -22738,7 +22754,7 @@
         <v>0</v>
       </c>
       <c r="N150" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O150" s="2"/>
     </row>
@@ -22762,7 +22778,7 @@
         <v>668</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>41</v>
@@ -22787,7 +22803,7 @@
         <v>0</v>
       </c>
       <c r="N151" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O151" s="2"/>
     </row>
@@ -22811,7 +22827,7 @@
         <v>672</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>41</v>
@@ -22836,7 +22852,7 @@
         <v>0</v>
       </c>
       <c r="N152" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O152" s="2"/>
     </row>
@@ -22860,7 +22876,7 @@
         <v>676</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H153" s="2" t="s">
         <v>41</v>
@@ -22885,7 +22901,7 @@
         <v>0</v>
       </c>
       <c r="N153" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O153" s="2"/>
     </row>
@@ -22909,7 +22925,7 @@
         <v>680</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>41</v>
@@ -22934,7 +22950,7 @@
         <v>0</v>
       </c>
       <c r="N154" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O154" s="2"/>
     </row>
@@ -22958,7 +22974,7 @@
         <v>684</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>41</v>
@@ -22983,7 +22999,7 @@
         <v>0</v>
       </c>
       <c r="N155" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O155" s="2"/>
     </row>
@@ -23007,7 +23023,7 @@
         <v>688</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>41</v>
@@ -23032,7 +23048,7 @@
         <v>0</v>
       </c>
       <c r="N156" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O156" s="2"/>
     </row>
@@ -23056,7 +23072,7 @@
         <v>692</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H157" s="2" t="s">
         <v>41</v>
@@ -23081,7 +23097,7 @@
         <v>0</v>
       </c>
       <c r="N157" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O157" s="2"/>
     </row>
@@ -23105,7 +23121,7 @@
         <v>696</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>41</v>
@@ -23130,7 +23146,7 @@
         <v>0</v>
       </c>
       <c r="N158" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O158" s="2"/>
     </row>
@@ -23154,7 +23170,7 @@
         <v>700</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>41</v>
@@ -23179,7 +23195,7 @@
         <v>0</v>
       </c>
       <c r="N159" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O159" s="2"/>
     </row>
@@ -23203,7 +23219,7 @@
         <v>705</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>41</v>
@@ -23228,7 +23244,7 @@
         <v>0</v>
       </c>
       <c r="N160" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O160" s="2"/>
     </row>
@@ -23252,7 +23268,7 @@
         <v>709</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H161" s="2" t="s">
         <v>41</v>
@@ -23277,7 +23293,7 @@
         <v>0</v>
       </c>
       <c r="N161" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O161" s="2"/>
     </row>
@@ -23301,7 +23317,7 @@
         <v>713</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>41</v>
@@ -23326,7 +23342,7 @@
         <v>0</v>
       </c>
       <c r="N162" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O162" s="2"/>
     </row>
@@ -23350,7 +23366,7 @@
         <v>718</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H163" s="2" t="s">
         <v>41</v>
@@ -23375,7 +23391,7 @@
         <v>0</v>
       </c>
       <c r="N163" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O163" s="2"/>
     </row>
@@ -23399,7 +23415,7 @@
         <v>722</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H164" s="2" t="s">
         <v>41</v>
@@ -23424,7 +23440,7 @@
         <v>0</v>
       </c>
       <c r="N164" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O164" s="2"/>
     </row>
@@ -23448,7 +23464,7 @@
         <v>726</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H165" s="2" t="s">
         <v>41</v>
@@ -23473,7 +23489,7 @@
         <v>0</v>
       </c>
       <c r="N165" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O165" s="2"/>
     </row>
@@ -23497,7 +23513,7 @@
         <v>730</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H166" s="2" t="s">
         <v>41</v>
@@ -23522,7 +23538,7 @@
         <v>0</v>
       </c>
       <c r="N166" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O166" s="2"/>
     </row>
@@ -23546,7 +23562,7 @@
         <v>734</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H167" s="2" t="s">
         <v>41</v>
@@ -23571,7 +23587,7 @@
         <v>0</v>
       </c>
       <c r="N167" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O167" s="2"/>
     </row>
@@ -23595,7 +23611,7 @@
         <v>739</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H168" s="2" t="s">
         <v>41</v>
@@ -23620,7 +23636,7 @@
         <v>0</v>
       </c>
       <c r="N168" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O168" s="2"/>
     </row>
@@ -23644,7 +23660,7 @@
         <v>743</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H169" s="2" t="s">
         <v>41</v>
@@ -23669,7 +23685,7 @@
         <v>0</v>
       </c>
       <c r="N169" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O169" s="2"/>
     </row>
@@ -23693,7 +23709,7 @@
         <v>748</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H170" s="2" t="s">
         <v>41</v>
@@ -23718,7 +23734,7 @@
         <v>0</v>
       </c>
       <c r="N170" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O170" s="2"/>
     </row>
@@ -23742,7 +23758,7 @@
         <v>752</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H171" s="2" t="s">
         <v>41</v>
@@ -23767,7 +23783,7 @@
         <v>0</v>
       </c>
       <c r="N171" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O171" s="2"/>
     </row>
@@ -23791,7 +23807,7 @@
         <v>756</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H172" s="2" t="s">
         <v>41</v>
@@ -23816,7 +23832,7 @@
         <v>0</v>
       </c>
       <c r="N172" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O172" s="2"/>
     </row>
@@ -23840,7 +23856,7 @@
         <v>760</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H173" s="2" t="s">
         <v>41</v>
@@ -23865,7 +23881,7 @@
         <v>0</v>
       </c>
       <c r="N173" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O173" s="2"/>
     </row>
@@ -23889,7 +23905,7 @@
         <v>764</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H174" s="2" t="s">
         <v>41</v>
@@ -23914,11 +23930,11 @@
         <v>0</v>
       </c>
       <c r="N174" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O174" s="2"/>
     </row>
-    <row r="175" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>766</v>
       </c>
@@ -23938,7 +23954,7 @@
         <v>770</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H175" s="2" t="s">
         <v>41</v>
@@ -23948,7 +23964,7 @@
       </c>
       <c r="J175" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I175,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K175" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I175,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -23960,10 +23976,10 @@
       </c>
       <c r="M175" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I175,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>spec/meals/README.md#phase-0a-technical-evidence</v>
+        <v>spec/meals/README.md#phase-0a-technical-evidence; P0-UAT-001: designated owner reported live Life Manager UAT PASS on 2026-10-28; release 8298e2e0797ddff7d2d53cc058fa41fb407ac0ab; recorded by Copilot from owner report, not automated authenticated verification</v>
       </c>
       <c r="N175" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O175" s="2"/>
     </row>
@@ -23987,7 +24003,7 @@
         <v>775</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H176" s="2" t="s">
         <v>41</v>
@@ -24012,7 +24028,7 @@
         <v>0</v>
       </c>
       <c r="N176" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O176" s="2"/>
     </row>
@@ -24036,7 +24052,7 @@
         <v>779</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H177" s="2" t="s">
         <v>41</v>
@@ -24061,7 +24077,7 @@
         <v>0</v>
       </c>
       <c r="N177" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O177" s="2"/>
     </row>
@@ -24085,7 +24101,7 @@
         <v>784</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H178" s="2" t="s">
         <v>41</v>
@@ -24110,7 +24126,7 @@
         <v>0</v>
       </c>
       <c r="N178" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O178" s="2"/>
     </row>
@@ -24134,7 +24150,7 @@
         <v>788</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H179" s="2" t="s">
         <v>41</v>
@@ -24159,7 +24175,7 @@
         <v>0</v>
       </c>
       <c r="N179" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O179" s="2"/>
     </row>
@@ -24183,7 +24199,7 @@
         <v>792</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H180" s="2" t="s">
         <v>41</v>
@@ -24208,7 +24224,7 @@
         <v>0</v>
       </c>
       <c r="N180" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O180" s="2"/>
     </row>
@@ -24232,7 +24248,7 @@
         <v>796</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H181" s="2" t="s">
         <v>41</v>
@@ -24257,7 +24273,7 @@
         <v>0</v>
       </c>
       <c r="N181" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O181" s="2"/>
     </row>
@@ -24281,7 +24297,7 @@
         <v>801</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H182" s="2" t="s">
         <v>41</v>
@@ -24306,7 +24322,7 @@
         <v>0</v>
       </c>
       <c r="N182" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O182" s="2"/>
     </row>
@@ -24330,7 +24346,7 @@
         <v>805</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H183" s="2" t="s">
         <v>41</v>
@@ -24355,7 +24371,7 @@
         <v>0</v>
       </c>
       <c r="N183" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O183" s="2"/>
     </row>
@@ -24379,7 +24395,7 @@
         <v>809</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H184" s="2" t="s">
         <v>41</v>
@@ -24404,7 +24420,7 @@
         <v>0</v>
       </c>
       <c r="N184" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O184" s="2"/>
     </row>
@@ -24419,7 +24435,7 @@
         <v>941</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="E185" s="2" t="s">
         <v>98</v>
@@ -24428,7 +24444,7 @@
         <v>942</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H185" s="2" t="s">
         <v>44</v>
@@ -24450,7 +24466,7 @@
         <v>0</v>
       </c>
       <c r="N185" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O185" s="2"/>
     </row>
@@ -24465,7 +24481,7 @@
         <v>941</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="E186" s="2" t="s">
         <v>98</v>
@@ -24474,7 +24490,7 @@
         <v>945</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H186" s="2" t="s">
         <v>44</v>
@@ -24496,7 +24512,7 @@
         <v>0</v>
       </c>
       <c r="N186" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O186" s="2"/>
     </row>
@@ -24511,7 +24527,7 @@
         <v>941</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="E187" s="2" t="s">
         <v>98</v>
@@ -24520,7 +24536,7 @@
         <v>948</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H187" s="2" t="s">
         <v>44</v>
@@ -24542,7 +24558,7 @@
         <v>0</v>
       </c>
       <c r="N187" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O187" s="2"/>
     </row>
@@ -24557,7 +24573,7 @@
         <v>941</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="E188" s="2" t="s">
         <v>98</v>
@@ -24566,7 +24582,7 @@
         <v>951</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H188" s="2" t="s">
         <v>44</v>
@@ -24588,7 +24604,7 @@
         <v>0</v>
       </c>
       <c r="N188" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O188" s="2"/>
     </row>
@@ -24603,7 +24619,7 @@
         <v>941</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>98</v>
@@ -24612,7 +24628,7 @@
         <v>954</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H189" s="2" t="s">
         <v>44</v>
@@ -24634,7 +24650,7 @@
         <v>0</v>
       </c>
       <c r="N189" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O189" s="2"/>
     </row>
@@ -24649,7 +24665,7 @@
         <v>941</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="E190" s="2" t="s">
         <v>98</v>
@@ -24658,7 +24674,7 @@
         <v>957</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H190" s="2" t="s">
         <v>44</v>
@@ -24680,7 +24696,7 @@
         <v>0</v>
       </c>
       <c r="N190" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O190" s="2"/>
     </row>
@@ -24695,7 +24711,7 @@
         <v>941</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="E191" s="2" t="s">
         <v>98</v>
@@ -24704,7 +24720,7 @@
         <v>960</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H191" s="2" t="s">
         <v>44</v>
@@ -24726,7 +24742,7 @@
         <v>0</v>
       </c>
       <c r="N191" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O191" s="2"/>
     </row>
@@ -24741,7 +24757,7 @@
         <v>941</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="E192" s="2" t="s">
         <v>98</v>
@@ -24750,7 +24766,7 @@
         <v>963</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H192" s="2" t="s">
         <v>44</v>
@@ -24772,7 +24788,7 @@
         <v>0</v>
       </c>
       <c r="N192" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O192" s="2"/>
     </row>
@@ -24787,7 +24803,7 @@
         <v>941</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="E193" s="2" t="s">
         <v>98</v>
@@ -24796,7 +24812,7 @@
         <v>966</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H193" s="2" t="s">
         <v>44</v>
@@ -24818,7 +24834,7 @@
         <v>0</v>
       </c>
       <c r="N193" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O193" s="2"/>
     </row>
@@ -24833,7 +24849,7 @@
         <v>941</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="E194" s="2" t="s">
         <v>98</v>
@@ -24842,7 +24858,7 @@
         <v>969</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H194" s="2" t="s">
         <v>44</v>
@@ -24864,7 +24880,7 @@
         <v>0</v>
       </c>
       <c r="N194" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O194" s="2"/>
     </row>
@@ -24879,7 +24895,7 @@
         <v>941</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="E195" s="2" t="s">
         <v>98</v>
@@ -24888,7 +24904,7 @@
         <v>972</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H195" s="2" t="s">
         <v>44</v>
@@ -24910,7 +24926,7 @@
         <v>0</v>
       </c>
       <c r="N195" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O195" s="2"/>
     </row>
@@ -24925,7 +24941,7 @@
         <v>941</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="E196" s="2" t="s">
         <v>98</v>
@@ -24934,7 +24950,7 @@
         <v>975</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H196" s="2" t="s">
         <v>44</v>
@@ -24956,7 +24972,7 @@
         <v>0</v>
       </c>
       <c r="N196" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O196" s="2"/>
     </row>
@@ -24980,7 +24996,7 @@
         <v>978</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H197" s="2" t="s">
         <v>44</v>
@@ -25002,7 +25018,7 @@
         <v>0</v>
       </c>
       <c r="N197" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O197" s="2"/>
     </row>
@@ -25026,7 +25042,7 @@
         <v>875</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="H198" s="2" t="s">
         <v>43</v>
@@ -25051,7 +25067,7 @@
         <v>0</v>
       </c>
       <c r="N198" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O198" s="2"/>
     </row>
@@ -25075,7 +25091,7 @@
         <v>879</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="H199" s="2" t="s">
         <v>43</v>
@@ -25100,7 +25116,7 @@
         <v>0</v>
       </c>
       <c r="N199" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O199" s="2"/>
     </row>
@@ -25124,7 +25140,7 @@
         <v>883</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="H200" s="2" t="s">
         <v>43</v>
@@ -25149,7 +25165,7 @@
         <v>0</v>
       </c>
       <c r="N200" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O200" s="2"/>
     </row>
@@ -25173,7 +25189,7 @@
         <v>887</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="H201" s="2" t="s">
         <v>43</v>
@@ -25198,7 +25214,7 @@
         <v>0</v>
       </c>
       <c r="N201" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O201" s="2"/>
     </row>
@@ -25222,7 +25238,7 @@
         <v>891</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="H202" s="2" t="s">
         <v>43</v>
@@ -25247,11 +25263,11 @@
         <v>0</v>
       </c>
       <c r="N202" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O202" s="2"/>
     </row>
-    <row r="203" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>893</v>
       </c>
@@ -25271,7 +25287,7 @@
         <v>895</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="H203" s="2" t="s">
         <v>43</v>
@@ -25296,7 +25312,7 @@
         <v>spec/meals/README.md#phase-0a-technical-evidence; web release validation: spec/meals/README.md#web-release-validation</v>
       </c>
       <c r="N203" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O203" s="2"/>
     </row>
@@ -25320,7 +25336,7 @@
         <v>899</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="H204" s="2" t="s">
         <v>43</v>
@@ -25345,7 +25361,7 @@
         <v>0</v>
       </c>
       <c r="N204" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O204" s="2"/>
     </row>
@@ -25369,7 +25385,7 @@
         <v>903</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="H205" s="2" t="s">
         <v>43</v>
@@ -25394,11 +25410,11 @@
         <v>0</v>
       </c>
       <c r="N205" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O205" s="2"/>
     </row>
-    <row r="206" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>905</v>
       </c>
@@ -25418,7 +25434,7 @@
         <v>907</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="H206" s="2" t="s">
         <v>43</v>
@@ -25443,7 +25459,7 @@
         <v>spec/meals/README.md#phase-0a-technical-evidence; web release validation: spec/meals/README.md#web-release-validation</v>
       </c>
       <c r="N206" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O206" s="2"/>
     </row>
@@ -25467,7 +25483,7 @@
         <v>911</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="H207" s="2" t="s">
         <v>43</v>
@@ -25492,13 +25508,13 @@
         <v>0</v>
       </c>
       <c r="N207" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O207" s="2"/>
     </row>
     <row r="208" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="B208" s="2" t="s">
         <v>56</v>
@@ -25507,19 +25523,19 @@
         <v>78</v>
       </c>
       <c r="D208" s="2" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E208" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F208" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="E208" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="F208" s="2" t="s">
-        <v>1091</v>
-      </c>
       <c r="G208" s="2" t="s">
+        <v>1085</v>
+      </c>
+      <c r="H208" s="2" t="s">
         <v>1086</v>
-      </c>
-      <c r="H208" s="2" t="s">
-        <v>1087</v>
       </c>
       <c r="I208" s="2"/>
       <c r="J208" s="2" t="s">
@@ -25535,7 +25551,7 @@
     </row>
     <row r="209" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="B209" s="2" t="s">
         <v>56</v>
@@ -25544,19 +25560,19 @@
         <v>78</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="E209" s="2" t="s">
         <v>98</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="G209" s="2" t="s">
+        <v>1085</v>
+      </c>
+      <c r="H209" s="2" t="s">
         <v>1086</v>
-      </c>
-      <c r="H209" s="2" t="s">
-        <v>1087</v>
       </c>
       <c r="I209" s="2"/>
       <c r="J209" s="2" t="s">
@@ -25572,7 +25588,7 @@
     </row>
     <row r="210" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="B210" s="2" t="s">
         <v>56</v>
@@ -25581,19 +25597,19 @@
         <v>78</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="E210" s="2" t="s">
         <v>98</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="G210" s="2" t="s">
+        <v>1085</v>
+      </c>
+      <c r="H210" s="2" t="s">
         <v>1086</v>
-      </c>
-      <c r="H210" s="2" t="s">
-        <v>1087</v>
       </c>
       <c r="I210" s="2"/>
       <c r="J210" s="2" t="s">
@@ -25609,7 +25625,7 @@
     </row>
     <row r="211" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="B211" s="2" t="s">
         <v>56</v>
@@ -25618,19 +25634,19 @@
         <v>78</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="E211" s="2" t="s">
         <v>98</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="G211" s="2" t="s">
+        <v>1085</v>
+      </c>
+      <c r="H211" s="2" t="s">
         <v>1086</v>
-      </c>
-      <c r="H211" s="2" t="s">
-        <v>1087</v>
       </c>
       <c r="I211" s="2"/>
       <c r="J211" s="2" t="s">
@@ -25646,7 +25662,7 @@
     </row>
     <row r="212" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="B212" s="2" t="s">
         <v>56</v>
@@ -25655,19 +25671,19 @@
         <v>78</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="E212" s="2" t="s">
         <v>98</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="G212" s="2" t="s">
+        <v>1085</v>
+      </c>
+      <c r="H212" s="2" t="s">
         <v>1086</v>
-      </c>
-      <c r="H212" s="2" t="s">
-        <v>1087</v>
       </c>
       <c r="I212" s="2"/>
       <c r="J212" s="2" t="s">
@@ -25683,7 +25699,7 @@
     </row>
     <row r="213" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="B213" s="2" t="s">
         <v>56</v>
@@ -25692,19 +25708,19 @@
         <v>78</v>
       </c>
       <c r="D213" s="2" t="s">
+        <v>1100</v>
+      </c>
+      <c r="E213" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F213" s="2" t="s">
         <v>1101</v>
       </c>
-      <c r="E213" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="F213" s="2" t="s">
-        <v>1102</v>
-      </c>
       <c r="G213" s="2" t="s">
+        <v>1085</v>
+      </c>
+      <c r="H213" s="2" t="s">
         <v>1086</v>
-      </c>
-      <c r="H213" s="2" t="s">
-        <v>1087</v>
       </c>
       <c r="I213" s="2"/>
       <c r="J213" s="2" t="s">
@@ -25720,7 +25736,7 @@
     </row>
     <row r="214" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="B214" s="2" t="s">
         <v>56</v>
@@ -25729,19 +25745,19 @@
         <v>78</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="E214" s="2" t="s">
         <v>98</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="G214" s="2" t="s">
+        <v>1085</v>
+      </c>
+      <c r="H214" s="2" t="s">
         <v>1086</v>
-      </c>
-      <c r="H214" s="2" t="s">
-        <v>1087</v>
       </c>
       <c r="I214" s="2"/>
       <c r="J214" s="2" t="s">
@@ -25757,7 +25773,7 @@
     </row>
     <row r="215" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="B215" s="2" t="s">
         <v>56</v>
@@ -25766,19 +25782,19 @@
         <v>78</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="E215" s="2" t="s">
         <v>98</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="G215" s="2" t="s">
+        <v>1085</v>
+      </c>
+      <c r="H215" s="2" t="s">
         <v>1086</v>
-      </c>
-      <c r="H215" s="2" t="s">
-        <v>1087</v>
       </c>
       <c r="I215" s="2"/>
       <c r="J215" s="2" t="s">
@@ -25794,7 +25810,7 @@
     </row>
     <row r="216" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="B216" s="2" t="s">
         <v>56</v>
@@ -25803,19 +25819,19 @@
         <v>78</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="E216" s="2" t="s">
         <v>98</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="G216" s="2" t="s">
+        <v>1085</v>
+      </c>
+      <c r="H216" s="2" t="s">
         <v>1086</v>
-      </c>
-      <c r="H216" s="2" t="s">
-        <v>1087</v>
       </c>
       <c r="I216" s="2"/>
       <c r="J216" s="2" t="s">
@@ -25831,7 +25847,7 @@
     </row>
     <row r="217" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="B217" s="2" t="s">
         <v>56</v>
@@ -25840,19 +25856,19 @@
         <v>78</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="E217" s="2" t="s">
         <v>98</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="G217" s="2" t="s">
+        <v>1085</v>
+      </c>
+      <c r="H217" s="2" t="s">
         <v>1086</v>
-      </c>
-      <c r="H217" s="2" t="s">
-        <v>1087</v>
       </c>
       <c r="I217" s="2"/>
       <c r="J217" s="2" t="s">
@@ -25886,7 +25902,7 @@
         <v>139</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H218" s="2" t="s">
         <v>41</v>
@@ -25911,7 +25927,7 @@
         <v>0</v>
       </c>
       <c r="N218" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O218" s="2"/>
     </row>
@@ -25935,7 +25951,7 @@
         <v>189</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H219" s="2" t="s">
         <v>41</v>
@@ -25960,7 +25976,7 @@
         <v>0</v>
       </c>
       <c r="N219" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O219" s="2"/>
     </row>
@@ -25984,7 +26000,7 @@
         <v>249</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H220" s="2" t="s">
         <v>41</v>
@@ -26009,7 +26025,7 @@
         <v>0</v>
       </c>
       <c r="N220" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O220" s="2"/>
     </row>
@@ -26033,7 +26049,7 @@
         <v>365</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H221" s="2" t="s">
         <v>41</v>
@@ -26058,11 +26074,11 @@
         <v>0</v>
       </c>
       <c r="N221" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O221" s="2"/>
     </row>
-    <row r="222" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>766</v>
       </c>
@@ -26082,7 +26098,7 @@
         <v>770</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H222" s="2" t="s">
         <v>41</v>
@@ -26092,7 +26108,7 @@
       </c>
       <c r="J222" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I222,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K222" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I222,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -26104,10 +26120,10 @@
       </c>
       <c r="M222" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I222,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>spec/meals/README.md#phase-0a-technical-evidence</v>
+        <v>spec/meals/README.md#phase-0a-technical-evidence; P0-UAT-001: designated owner reported live Life Manager UAT PASS on 2026-10-28; release 8298e2e0797ddff7d2d53cc058fa41fb407ac0ab; recorded by Copilot from owner report, not automated authenticated verification</v>
       </c>
       <c r="N222" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O222" s="2"/>
     </row>
@@ -26131,7 +26147,7 @@
         <v>796</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H223" s="2" t="s">
         <v>41</v>
@@ -26156,7 +26172,7 @@
         <v>0</v>
       </c>
       <c r="N223" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O223" s="2"/>
     </row>

--- a/spec/meals/Meals Acceptance Checklist v1.0.xlsx
+++ b/spec/meals/Meals Acceptance Checklist v1.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wcoop\Documents\HomeMaintenanceApp\spec\meals\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7036922-060B-48E0-A57F-6D69BEA330D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F945ED1C-5F1E-4B5A-AB77-FEDF7CA21501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5032" uniqueCount="1132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5056" uniqueCount="1137">
   <si>
     <t>Meals Acceptance Checklist</t>
   </si>
@@ -3547,6 +3547,21 @@
   </si>
   <si>
     <t>Phase 0A Meals foundation accepted. Live web routing, navigation, owner-auth integration, responsive shell, nested route refresh, and E2E-00 passed. Acceptance includes the Acceptance Workbook update tooling and Phase 0A release/deployment infrastructure. Recipe persistence, Recipe functionality beyond the Phase 0A shell/placeholders (including Add/Edit), Shopping functionality/persistence, meal-plan persistence, Weekly Planner meal integration, Recipe Import, future Meals database objects, and future Meals database-security/catalog verification remain outside this acceptance and are not yet accepted. Owner explicitly authorized this scope-limited acceptance on 2026-10-28 following P0-UAT-001.</t>
+  </si>
+  <si>
+    <t>P0B-PREFLIGHT-001</t>
+  </si>
+  <si>
+    <t>supabase/review/202610280001_meals_recipe_foundation.sql (disabled draft)</t>
+  </si>
+  <si>
+    <t>dev @ 75de46464a3b4eb5c72f4fadb9ac8c0baefde9d7; uncommitted reviewed draft</t>
+  </si>
+  <si>
+    <t>P0B-PREFLIGHT-001: meals-0b-production-preflight-manifest.json; complete catalog/supplement JSON and CSV evidence in session b7458d86-6190-4718-8779-7c2b79a30630/files; Dashboard-verified home-maintenance-app / tawvchmjtkgykwwvnnnn</t>
+  </si>
+  <si>
+    <t>P0B-PREFLIGHT-001 preflight-only: authenticated Dashboard identity, PostgreSQL 17.11, postgres object ownership/CREATE authority, browser-role safety, zero Meals collisions/dependencies and informational defaults captured. Canonical Category/Cuisine draft and local tests updated. No migration or production postflight executed; no database check marked Pass. Status Not Built and stage Both retained; post-deployment object ACL/RLS/owner and broker-independence checks remain required. Disabled reversal prepared, not executed. No Phase 0A UAT/acceptance or future owner decision changed.</t>
   </si>
 </sst>
 </file>
@@ -13875,8 +13890,10 @@
       </c>
       <c r="R2" s="2"/>
     </row>
-    <row r="3" spans="1:18" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
+    <row r="3" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>1132</v>
+      </c>
       <c r="B3" s="2" t="s">
         <v>930</v>
       </c>
@@ -13889,15 +13906,21 @@
       <c r="E3" s="2" t="s">
         <v>814</v>
       </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
+      <c r="F3" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>1134</v>
+      </c>
       <c r="H3" s="2" t="s">
         <v>926</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="J3" s="7"/>
+      <c r="J3" s="7" t="s">
+        <v>1130</v>
+      </c>
       <c r="K3" s="2" t="s">
         <v>927</v>
       </c>
@@ -13910,14 +13933,18 @@
       <c r="N3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="O3" s="2"/>
+      <c r="O3" s="2" t="s">
+        <v>1135</v>
+      </c>
       <c r="P3" s="2" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="Q3" s="2" t="s">
         <v>929</v>
       </c>
-      <c r="R3" s="2"/>
+      <c r="R3" s="2" t="s">
+        <v>1136</v>
+      </c>
     </row>
     <row r="4" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
@@ -14051,8 +14078,10 @@
       </c>
       <c r="R6" s="2"/>
     </row>
-    <row r="7" spans="1:18" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
+    <row r="7" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>1132</v>
+      </c>
       <c r="B7" s="2" t="s">
         <v>936</v>
       </c>
@@ -14065,15 +14094,21 @@
       <c r="E7" s="2" t="s">
         <v>814</v>
       </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
+      <c r="F7" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>1134</v>
+      </c>
       <c r="H7" s="2" t="s">
         <v>926</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="J7" s="7"/>
+      <c r="J7" s="7" t="s">
+        <v>1130</v>
+      </c>
       <c r="K7" s="2" t="s">
         <v>929</v>
       </c>
@@ -14086,14 +14121,18 @@
       <c r="N7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="O7" s="2"/>
+      <c r="O7" s="2" t="s">
+        <v>1135</v>
+      </c>
       <c r="P7" s="2" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>929</v>
       </c>
-      <c r="R7" s="2"/>
+      <c r="R7" s="2" t="s">
+        <v>1136</v>
+      </c>
     </row>
     <row r="8" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
@@ -14667,8 +14706,10 @@
       </c>
       <c r="R20" s="2"/>
     </row>
-    <row r="21" spans="1:18" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
+    <row r="21" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>1132</v>
+      </c>
       <c r="B21" s="2" t="s">
         <v>979</v>
       </c>
@@ -14681,15 +14722,21 @@
       <c r="E21" s="2" t="s">
         <v>980</v>
       </c>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
+      <c r="F21" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>1134</v>
+      </c>
       <c r="H21" s="2" t="s">
         <v>926</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="J21" s="7"/>
+      <c r="J21" s="7" t="s">
+        <v>1130</v>
+      </c>
       <c r="K21" s="2" t="s">
         <v>927</v>
       </c>
@@ -14702,17 +14749,23 @@
       <c r="N21" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="O21" s="2"/>
+      <c r="O21" s="2" t="s">
+        <v>1135</v>
+      </c>
       <c r="P21" s="2" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="Q21" s="2" t="s">
         <v>929</v>
       </c>
-      <c r="R21" s="2"/>
-    </row>
-    <row r="22" spans="1:18" ht="45" x14ac:dyDescent="0.25">
-      <c r="A22" s="2"/>
+      <c r="R21" s="2" t="s">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>1132</v>
+      </c>
       <c r="B22" s="2" t="s">
         <v>983</v>
       </c>
@@ -14725,15 +14778,21 @@
       <c r="E22" s="2" t="s">
         <v>984</v>
       </c>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
+      <c r="F22" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>1134</v>
+      </c>
       <c r="H22" s="2" t="s">
         <v>926</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="J22" s="7"/>
+      <c r="J22" s="7" t="s">
+        <v>1130</v>
+      </c>
       <c r="K22" s="2" t="s">
         <v>929</v>
       </c>
@@ -14746,14 +14805,18 @@
       <c r="N22" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="O22" s="2"/>
+      <c r="O22" s="2" t="s">
+        <v>1135</v>
+      </c>
       <c r="P22" s="2" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="Q22" s="2" t="s">
         <v>929</v>
       </c>
-      <c r="R22" s="2"/>
+      <c r="R22" s="2" t="s">
+        <v>1136</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2:G22">
@@ -16190,14 +16253,14 @@
         <f>IFERROR(INDEX('Database Verification'!$N:$N,MATCH($I16,'Database Verification'!$B:$B,0)),"")</f>
         <v>Not Built</v>
       </c>
-      <c r="K16" s="7">
+      <c r="K16" s="7" t="str">
         <f>IFERROR(INDEX('Database Verification'!$J:$J,MATCH($I16,'Database Verification'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>2026-10-28</v>
       </c>
       <c r="L16" s="2"/>
-      <c r="M16" s="2">
+      <c r="M16" s="2" t="str">
         <f>IFERROR(INDEX('Database Verification'!$O:$O,MATCH($I16,'Database Verification'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P0B-PREFLIGHT-001: meals-0b-production-preflight-manifest.json; complete catalog/supplement JSON and CSV evidence in session b7458d86-6190-4718-8779-7c2b79a30630/files; Dashboard-verified home-maintenance-app / tawvchmjtkgykwwvnnnn</v>
       </c>
       <c r="N16" s="2" t="s">
         <v>1075</v>

--- a/spec/meals/Meals Acceptance Checklist v1.0.xlsx
+++ b/spec/meals/Meals Acceptance Checklist v1.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wcoop\Documents\HomeMaintenanceApp\spec\meals\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F945ED1C-5F1E-4B5A-AB77-FEDF7CA21501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02963D1F-5BC3-40A9-A86C-51F6B2392F42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5056" uniqueCount="1137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5134" uniqueCount="1155">
   <si>
     <t>Meals Acceptance Checklist</t>
   </si>
@@ -3549,19 +3549,78 @@
     <t>Phase 0A Meals foundation accepted. Live web routing, navigation, owner-auth integration, responsive shell, nested route refresh, and E2E-00 passed. Acceptance includes the Acceptance Workbook update tooling and Phase 0A release/deployment infrastructure. Recipe persistence, Recipe functionality beyond the Phase 0A shell/placeholders (including Add/Edit), Shopping functionality/persistence, meal-plan persistence, Weekly Planner meal integration, Recipe Import, future Meals database objects, and future Meals database-security/catalog verification remain outside this acceptance and are not yet accepted. Owner explicitly authorized this scope-limited acceptance on 2026-10-28 following P0-UAT-001.</t>
   </si>
   <si>
-    <t>P0B-PREFLIGHT-001</t>
-  </si>
-  <si>
-    <t>supabase/review/202610280001_meals_recipe_foundation.sql (disabled draft)</t>
-  </si>
-  <si>
-    <t>dev @ 75de46464a3b4eb5c72f4fadb9ac8c0baefde9d7; uncommitted reviewed draft</t>
-  </si>
-  <si>
-    <t>P0B-PREFLIGHT-001: meals-0b-production-preflight-manifest.json; complete catalog/supplement JSON and CSV evidence in session b7458d86-6190-4718-8779-7c2b79a30630/files; Dashboard-verified home-maintenance-app / tawvchmjtkgykwwvnnnn</t>
-  </si>
-  <si>
-    <t>P0B-PREFLIGHT-001 preflight-only: authenticated Dashboard identity, PostgreSQL 17.11, postgres object ownership/CREATE authority, browser-role safety, zero Meals collisions/dependencies and informational defaults captured. Canonical Category/Cuisine draft and local tests updated. No migration or production postflight executed; no database check marked Pass. Status Not Built and stage Both retained; post-deployment object ACL/RLS/owner and broker-independence checks remain required. Disabled reversal prepared, not executed. No Phase 0A UAT/acceptance or future owner decision changed.</t>
+    <t>P0B-DB-001</t>
+  </si>
+  <si>
+    <t>202610280001_meals_recipe_foundation.sql</t>
+  </si>
+  <si>
+    <t>dev @ 0d30359ab5cdd4aa3577c33823de1bbc80a3d4f2</t>
+  </si>
+  <si>
+    <t>P0B-DB-001; package 0d30359ab5cdd4aa3577c33823de1bbc80a3d4f2; spec/meals/Phase 0B Recipe Persistence Design.md section 28; meals-db-final-manifest.json SHA256 4cbbc3eac24c13860d39ee3a0d8c6ae79c638cc5967d5274d1e7ea219091f8da; complete evidence in session b7458d86-6190-4718-8779-7c2b79a30630/files</t>
+  </si>
+  <si>
+    <t>P0B-DB-001 Recipe foundation scope only. Captured production catalog and synthetic SQL SET ROLE/claim evidence, not live JWT/API authentication, owner application UAT or Recipe UI evidence. Future Meals objects require their own verification. No deployment blocker observed; blocker classification field is unchanged. Reversal prepared, not executed; test-only transaction rollback is not migration reversal. effective_anon_denial and function_acl passed; production synthetic anon SELECT/INSERT/UPDATE/DELETE denied on all three tables.</t>
+  </si>
+  <si>
+    <t>P0B-PREFLIGHT-001: meals-0b-production-preflight-manifest.json; complete catalog/supplement JSON and CSV evidence in session b7458d86-6190-4718-8779-7c2b79a30630/files; Dashboard-verified home-maintenance-app / tawvchmjtkgykwwvnnnn
+P0B-DB-001; package 0d30359ab5cdd4aa3577c33823de1bbc80a3d4f2; spec/meals/Phase 0B Recipe Persistence Design.md section 28; meals-db-final-manifest.json SHA256 4cbbc3eac24c13860d39ee3a0d8c6ae79c638cc5967d5274d1e7ea219091f8da; complete evidence in session b7458d86-6190-4718-8779-7c2b79a30630/files</t>
+  </si>
+  <si>
+    <t>P0B-PREFLIGHT-001 preflight-only: authenticated Dashboard identity, PostgreSQL 17.11, postgres object ownership/CREATE authority, browser-role safety, zero Meals collisions/dependencies and informational defaults captured. Canonical Category/Cuisine draft and local tests updated. No migration or production postflight executed; no database check marked Pass. Status Not Built and stage Both retained; post-deployment object ACL/RLS/owner and broker-independence checks remain required. Disabled reversal prepared, not executed. No Phase 0A UAT/acceptance or future owner decision changed.
+P0B-DB-001 Recipe foundation scope only. Captured production catalog and synthetic SQL SET ROLE/claim evidence, not live JWT/API authentication, owner application UAT or Recipe UI evidence. Future Meals objects require their own verification. No deployment blocker observed; blocker classification field is unchanged. Reversal prepared, not executed; test-only transaction rollback is not migration reversal. explicit_table_acl, column_acl, function_acl and browser_role_safety passed; object ACLs explicitly reset; no dependence on managed defaults.</t>
+  </si>
+  <si>
+    <t>P0B-DB-001 Recipe foundation scope only. Captured production catalog and synthetic SQL SET ROLE/claim evidence, not live JWT/API authentication, owner application UAT or Recipe UI evidence. Future Meals objects require their own verification. No deployment blocker observed; blocker classification field is unchanged. Reversal prepared, not executed; test-only transaction rollback is not migration reversal. Exact inventory has direct tables and an internal non-browser trigger only; no CRUD RPC. Production synthetic owner CRUD passed.</t>
+  </si>
+  <si>
+    <t>P0B-PREFLIGHT-001 preflight-only: authenticated Dashboard identity, PostgreSQL 17.11, postgres object ownership/CREATE authority, browser-role safety, zero Meals collisions/dependencies and informational defaults captured. Canonical Category/Cuisine draft and local tests updated. No migration or production postflight executed; no database check marked Pass. Status Not Built and stage Both retained; post-deployment object ACL/RLS/owner and broker-independence checks remain required. Disabled reversal prepared, not executed. No Phase 0A UAT/acceptance or future owner decision changed.
+P0B-DB-001 Recipe foundation scope only. Captured production catalog and synthetic SQL SET ROLE/claim evidence, not live JWT/API authentication, owner application UAT or Recipe UI evidence. Future Meals objects require their own verification. No deployment blocker observed; blocker classification field is unchanged. Reversal prepared, not executed; test-only transaction rollback is not migration reversal. tables_owner_rls and function_security passed: all new tables/function postgres-owned.</t>
+  </si>
+  <si>
+    <t>P0B-DB-001 Recipe foundation scope only. Captured production catalog and synthetic SQL SET ROLE/claim evidence, not live JWT/API authentication, owner application UAT or Recipe UI evidence. Future Meals objects require their own verification. No deployment blocker observed; blocker classification field is unchanged. Reversal prepared, not executed; test-only transaction rollback is not migration reversal. tables_owner_rls passed: RLS enabled on all three browser-accessible Recipe tables.</t>
+  </si>
+  <si>
+    <t>P0B-DB-001 Recipe foundation scope only. Captured production catalog and synthetic SQL SET ROLE/claim evidence, not live JWT/API authentication, owner application UAT or Recipe UI evidence. Future Meals objects require their own verification. No deployment blocker observed; blocker classification field is unchanged. Reversal prepared, not executed; test-only transaction rollback is not migration reversal. explicit_table_acl, effective_anon_denial, function_acl and column_acl passed: no unintended PUBLIC/anon private access.</t>
+  </si>
+  <si>
+    <t>P0B-DB-001 Recipe foundation scope only. Captured production catalog and synthetic SQL SET ROLE/claim evidence, not live JWT/API authentication, owner application UAT or Recipe UI evidence. Future Meals objects require their own verification. No deployment blocker observed; blocker classification field is unchanged. Reversal prepared, not executed; test-only transaction rollback is not migration reversal. Table/column ACL matrix passed: authenticated SELECT/DELETE and reviewed INSERT/UPDATE columns only.</t>
+  </si>
+  <si>
+    <t>P0B-DB-001 Recipe foundation scope only. Captured production catalog and synthetic SQL SET ROLE/claim evidence, not live JWT/API authentication, owner application UAT or Recipe UI evidence. Future Meals objects require their own verification. No deployment blocker observed; blocker classification field is unchanged. Reversal prepared, not executed; test-only transaction rollback is not migration reversal. policy_matrix passed: exactly 12 operation policies, authenticated role, exact-owner UUID, correct USING/WITH CHECK; synthetic non-owner/null subject denied.</t>
+  </si>
+  <si>
+    <t>P0B-DB-001 Recipe foundation scope only. Captured production catalog and synthetic SQL SET ROLE/claim evidence, not live JWT/API authentication, owner application UAT or Recipe UI evidence. Future Meals objects require their own verification. No deployment blocker observed; blocker classification field is unchanged. Reversal prepared, not executed; test-only transaction rollback is not migration reversal. All 20 reviewed postflight checks passed; exact relation/type/column/default/index/constraint/trigger/function/ACL/RLS inventory captured.</t>
+  </si>
+  <si>
+    <t>P0B-DB-001 Recipe foundation scope only. Captured production catalog and synthetic SQL SET ROLE/claim evidence, not live JWT/API authentication, owner application UAT or Recipe UI evidence. Future Meals objects require their own verification. No deployment blocker observed; blocker classification field is unchanged. Reversal prepared, not executed; test-only transaction rollback is not migration reversal. Ownership and explicit/effective ACL checks passed; no unexpected owner or unexplained grant detected.</t>
+  </si>
+  <si>
+    <t>P0B-DB-001 Recipe foundation scope only. Captured production catalog and synthetic SQL SET ROLE/claim evidence, not live JWT/API authentication, owner application UAT or Recipe UI evidence. Future Meals objects require their own verification. No deployment blocker observed; blocker classification field is unchanged. Reversal prepared, not executed; test-only transaction rollback is not migration reversal. Source inspection and no_unreviewed_role_dependencies passed; no Meals broker dependency. Existing unrelated remnants untouched.</t>
+  </si>
+  <si>
+    <t>P0B-DB-001 Recipe foundation scope only. Captured production catalog and synthetic SQL SET ROLE/claim evidence, not live JWT/API authentication, owner application UAT or Recipe UI evidence. Future Meals objects require their own verification. No deployment blocker observed; blocker classification field is unchanged. Reversal prepared, not executed; test-only transaction rollback is not migration reversal. Dashboard URL, title and project link independently verified home-maintenance-app / tawvchmjtkgykwwvnnnn before preflight and execution.</t>
+  </si>
+  <si>
+    <t>P0B-DB-001 Recipe foundation scope only. Captured production catalog and synthetic SQL SET ROLE/claim evidence, not live JWT/API authentication, owner application UAT or Recipe UI evidence. Future Meals objects require their own verification. No deployment blocker observed; blocker classification field is unchanged. Reversal prepared, not executed; test-only transaction rollback is not migration reversal. Catalog defaults/function body and production synthetic server-timestamp/column-write-denial assertions passed.</t>
+  </si>
+  <si>
+    <t>P0B-PREFLIGHT-001 preflight-only: authenticated Dashboard identity, PostgreSQL 17.11, postgres object ownership/CREATE authority, browser-role safety, zero Meals collisions/dependencies and informational defaults captured. Canonical Category/Cuisine draft and local tests updated. No migration or production postflight executed; no database check marked Pass. Status Not Built and stage Both retained; post-deployment object ACL/RLS/owner and broker-independence checks remain required. Disabled reversal prepared, not executed. No Phase 0A UAT/acceptance or future owner decision changed.
+P0B-DB-001 Recipe foundation scope only. Captured production catalog and synthetic SQL SET ROLE/claim evidence, not live JWT/API authentication, owner application UAT or Recipe UI evidence. Future Meals objects require their own verification. No deployment blocker observed; blocker classification field is unchanged. Reversal prepared, not executed; test-only transaction rollback is not migration reversal. Exact Dashboard project identity verified before relying on catalog evidence.</t>
+  </si>
+  <si>
+    <t>P0B-PREFLIGHT-001 preflight-only: authenticated Dashboard identity, PostgreSQL 17.11, postgres object ownership/CREATE authority, browser-role safety, zero Meals collisions/dependencies and informational defaults captured. Canonical Category/Cuisine draft and local tests updated. No migration or production postflight executed; no database check marked Pass. Status Not Built and stage Both retained; post-deployment object ACL/RLS/owner and broker-independence checks remain required. Disabled reversal prepared, not executed. No Phase 0A UAT/acceptance or future owner decision changed.
+P0B-DB-001 Recipe foundation scope only. Captured production catalog and synthetic SQL SET ROLE/claim evidence, not live JWT/API authentication, owner application UAT or Recipe UI evidence. Future Meals objects require their own verification. No deployment blocker observed; blocker classification field is unchanged. Reversal prepared, not executed; test-only transaction rollback is not migration reversal. Catalog/source have no new Meals broker dependency; no broker cleanup performed.</t>
+  </si>
+  <si>
+    <t>P0B-DB-001 Recipe foundation scope only. Captured production catalog and synthetic SQL SET ROLE/claim evidence, not live JWT/API authentication, owner application UAT or Recipe UI evidence. Future Meals objects require their own verification. No deployment blocker observed; blocker classification field is unchanged. Reversal prepared, not executed; test-only transaction rollback is not migration reversal. Owner identity confirmed by preflight and exact UUID in all 12 deployed policies.</t>
+  </si>
+  <si>
+    <t>P0B-DB-001 Recipe foundation scope only. Captured production catalog and synthetic SQL SET ROLE/claim evidence, not live JWT/API authentication, owner application UAT or Recipe UI evidence. Future Meals objects require their own verification. No deployment blocker observed; blocker classification field is unchanged. Reversal prepared, not executed; test-only transaction rollback is not migration reversal. Explicit table/column/function ACLs passed; source and catalog do not rely on defaults.</t>
+  </si>
+  <si>
+    <t>P0B-DB-001 Recipe foundation scope only. Captured production catalog and synthetic SQL SET ROLE/claim evidence, not live JWT/API authentication, owner application UAT or Recipe UI evidence. Future Meals objects require their own verification. No deployment blocker observed; blocker classification field is unchanged. Reversal prepared, not executed; test-only transaction rollback is not migration reversal. Production postflight effective_anon_denial/explicit_table_acl/function_acl/column_acl passed.</t>
   </si>
 </sst>
 </file>
@@ -4531,12 +4590,12 @@
     <col min="2" max="2" width="110" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -4544,7 +4603,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -4552,17 +4611,17 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="2"/>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
@@ -4570,7 +4629,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
@@ -4578,7 +4637,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -4586,7 +4645,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
@@ -4594,7 +4653,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>14</v>
       </c>
@@ -4602,7 +4661,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>16</v>
       </c>
@@ -4610,7 +4669,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>18</v>
       </c>
@@ -4618,7 +4677,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
@@ -4626,15 +4685,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
     </row>
-    <row r="16" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>22</v>
       </c>
@@ -4642,7 +4701,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>24</v>
       </c>
@@ -4650,7 +4709,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>26</v>
       </c>
@@ -4658,7 +4717,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>28</v>
       </c>
@@ -4666,7 +4725,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>30</v>
       </c>
@@ -4674,7 +4733,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>32</v>
       </c>
@@ -4702,7 +4761,7 @@
     <col min="17" max="17" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="131.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="131.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>34</v>
       </c>
@@ -4715,7 +4774,7 @@
       <c r="H1" s="5"/>
       <c r="I1" s="5"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -4726,7 +4785,7 @@
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
     </row>
-    <row r="3" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
@@ -4741,7 +4800,7 @@
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
     </row>
-    <row r="4" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>36</v>
       </c>
@@ -4756,7 +4815,7 @@
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -4767,7 +4826,7 @@
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>37</v>
       </c>
@@ -4796,7 +4855,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>41</v>
       </c>
@@ -4833,7 +4892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>42</v>
       </c>
@@ -4870,7 +4929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>43</v>
       </c>
@@ -4880,7 +4939,7 @@
       </c>
       <c r="C9" s="5">
         <f>COUNTIF('Security Acceptance'!$N:$N,"Pass")</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D9" s="5">
         <f>COUNTIF('Security Acceptance'!$N:$N,"Pass with Known Issue")</f>
@@ -4900,14 +4959,14 @@
       </c>
       <c r="H9" s="5">
         <f>COUNTIF('Security Acceptance'!$N:$N,"Not Built")</f>
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I9" s="5">
         <f>COUNTIF('Security Acceptance'!$N:$N,"Deferred")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>44</v>
       </c>
@@ -4917,7 +4976,7 @@
       </c>
       <c r="C10" s="5">
         <f>COUNTIF('Database Verification'!$N:$N,"Pass")</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D10" s="5">
         <f>COUNTIF('Database Verification'!$N:$N,"Pass with Known Issue")</f>
@@ -4937,14 +4996,14 @@
       </c>
       <c r="H10" s="5">
         <f>COUNTIF('Database Verification'!$N:$N,"Not Built")</f>
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="I10" s="5">
         <f>COUNTIF('Database Verification'!$N:$N,"Deferred")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -4955,7 +5014,7 @@
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -4966,7 +5025,7 @@
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>45</v>
       </c>
@@ -4983,7 +5042,7 @@
       <c r="H13" s="6"/>
       <c r="I13" s="6"/>
     </row>
-    <row r="14" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>48</v>
       </c>
@@ -5001,7 +5060,7 @@
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>50</v>
       </c>
@@ -5019,7 +5078,7 @@
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>52</v>
       </c>
@@ -5037,7 +5096,7 @@
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
     </row>
-    <row r="17" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>54</v>
       </c>
@@ -5055,7 +5114,7 @@
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
     </row>
-    <row r="18" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>56</v>
       </c>
@@ -5073,7 +5132,7 @@
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -5084,7 +5143,7 @@
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
     </row>
-    <row r="22" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>45</v>
       </c>
@@ -5153,7 +5212,7 @@
       </c>
       <c r="E23" s="2">
         <f>COUNTIFS('Functional Acceptance'!D:D,A23,'Functional Acceptance'!L:L,"Pass")+COUNTIFS('Security Acceptance'!D:D,A23,'Security Acceptance'!N:N,"Pass")+COUNTIFS('Database Verification'!D:D,A23,'Database Verification'!N:N,"Pass")+COUNTIFS('End-to-End Tests'!C:C,A23,'End-to-End Tests'!J:J,"Pass")</f>
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F23" s="2">
         <f>COUNTIFS('Functional Acceptance'!D:D,A23,'Functional Acceptance'!L:L,"Pass with Known Issue")+COUNTIFS('Security Acceptance'!D:D,A23,'Security Acceptance'!N:N,"Pass with Known Issue")+COUNTIFS('Database Verification'!D:D,A23,'Database Verification'!N:N,"Pass with Known Issue")+COUNTIFS('End-to-End Tests'!C:C,A23,'End-to-End Tests'!J:J,"Pass with Known Issue")</f>
@@ -5196,7 +5255,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>50</v>
       </c>
@@ -5251,7 +5310,7 @@
       <c r="P24" s="2"/>
       <c r="Q24" s="2"/>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>52</v>
       </c>
@@ -5306,7 +5365,7 @@
       <c r="P25" s="2"/>
       <c r="Q25" s="2"/>
     </row>
-    <row r="26" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>54</v>
       </c>
@@ -5361,7 +5420,7 @@
       <c r="P26" s="2"/>
       <c r="Q26" s="2"/>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>56</v>
       </c>
@@ -5698,7 +5757,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
         <v>116</v>
@@ -5738,7 +5797,7 @@
       <c r="O6" s="2"/>
       <c r="P6" s="2"/>
     </row>
-    <row r="7" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2" t="s">
         <v>120</v>
@@ -5778,7 +5837,7 @@
       <c r="O7" s="2"/>
       <c r="P7" s="2"/>
     </row>
-    <row r="8" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2" t="s">
         <v>124</v>
@@ -5866,7 +5925,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="2" t="s">
         <v>132</v>
@@ -5906,7 +5965,7 @@
       <c r="O10" s="2"/>
       <c r="P10" s="2"/>
     </row>
-    <row r="11" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
         <v>140</v>
@@ -5946,7 +6005,7 @@
       <c r="O11" s="2"/>
       <c r="P11" s="2"/>
     </row>
-    <row r="12" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2" t="s">
         <v>143</v>
@@ -5986,7 +6045,7 @@
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
     </row>
-    <row r="13" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2" t="s">
         <v>147</v>
@@ -6026,7 +6085,7 @@
       <c r="O13" s="2"/>
       <c r="P13" s="2"/>
     </row>
-    <row r="14" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2" t="s">
         <v>151</v>
@@ -6066,7 +6125,7 @@
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
     </row>
-    <row r="15" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2" t="s">
         <v>155</v>
@@ -6106,7 +6165,7 @@
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
     </row>
-    <row r="16" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="2" t="s">
         <v>160</v>
@@ -6146,7 +6205,7 @@
       <c r="O16" s="2"/>
       <c r="P16" s="2"/>
     </row>
-    <row r="17" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2" t="s">
         <v>165</v>
@@ -6186,7 +6245,7 @@
       <c r="O17" s="2"/>
       <c r="P17" s="2"/>
     </row>
-    <row r="18" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2" t="s">
         <v>169</v>
@@ -6226,7 +6285,7 @@
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
     </row>
-    <row r="19" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2" t="s">
         <v>173</v>
@@ -6266,7 +6325,7 @@
       <c r="O19" s="2"/>
       <c r="P19" s="2"/>
     </row>
-    <row r="20" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="2" t="s">
         <v>177</v>
@@ -6306,7 +6365,7 @@
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
     </row>
-    <row r="21" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="2" t="s">
         <v>181</v>
@@ -6346,7 +6405,7 @@
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
     </row>
-    <row r="22" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2" t="s">
         <v>185</v>
@@ -6386,7 +6445,7 @@
       <c r="O22" s="2"/>
       <c r="P22" s="2"/>
     </row>
-    <row r="23" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="2" t="s">
         <v>190</v>
@@ -6426,7 +6485,7 @@
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
     </row>
-    <row r="24" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2" t="s">
         <v>191</v>
@@ -6466,7 +6525,7 @@
       <c r="O24" s="2"/>
       <c r="P24" s="2"/>
     </row>
-    <row r="25" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="2" t="s">
         <v>195</v>
@@ -6506,7 +6565,7 @@
       <c r="O25" s="2"/>
       <c r="P25" s="2"/>
     </row>
-    <row r="26" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="2" t="s">
         <v>199</v>
@@ -6546,7 +6605,7 @@
       <c r="O26" s="2"/>
       <c r="P26" s="2"/>
     </row>
-    <row r="27" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="2" t="s">
         <v>203</v>
@@ -6586,7 +6645,7 @@
       <c r="O27" s="2"/>
       <c r="P27" s="2"/>
     </row>
-    <row r="28" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2" t="s">
         <v>207</v>
@@ -6626,7 +6685,7 @@
       <c r="O28" s="2"/>
       <c r="P28" s="2"/>
     </row>
-    <row r="29" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="2" t="s">
         <v>211</v>
@@ -6666,7 +6725,7 @@
       <c r="O29" s="2"/>
       <c r="P29" s="2"/>
     </row>
-    <row r="30" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="2" t="s">
         <v>215</v>
@@ -6706,7 +6765,7 @@
       <c r="O30" s="2"/>
       <c r="P30" s="2"/>
     </row>
-    <row r="31" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="2" t="s">
         <v>219</v>
@@ -6746,7 +6805,7 @@
       <c r="O31" s="2"/>
       <c r="P31" s="2"/>
     </row>
-    <row r="32" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="2" t="s">
         <v>223</v>
@@ -6786,7 +6845,7 @@
       <c r="O32" s="2"/>
       <c r="P32" s="2"/>
     </row>
-    <row r="33" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="2" t="s">
         <v>228</v>
@@ -6826,7 +6885,7 @@
       <c r="O33" s="2"/>
       <c r="P33" s="2"/>
     </row>
-    <row r="34" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="2" t="s">
         <v>232</v>
@@ -6866,7 +6925,7 @@
       <c r="O34" s="2"/>
       <c r="P34" s="2"/>
     </row>
-    <row r="35" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="2" t="s">
         <v>237</v>
@@ -6906,7 +6965,7 @@
       <c r="O35" s="2"/>
       <c r="P35" s="2"/>
     </row>
-    <row r="36" spans="1:16" ht="105" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="2" t="s">
         <v>241</v>
@@ -6946,7 +7005,7 @@
       <c r="O36" s="2"/>
       <c r="P36" s="2"/>
     </row>
-    <row r="37" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="2" t="s">
         <v>245</v>
@@ -6986,7 +7045,7 @@
       <c r="O37" s="2"/>
       <c r="P37" s="2"/>
     </row>
-    <row r="38" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="2" t="s">
         <v>250</v>
@@ -7026,7 +7085,7 @@
       <c r="O38" s="2"/>
       <c r="P38" s="2"/>
     </row>
-    <row r="39" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="2" t="s">
         <v>251</v>
@@ -7066,7 +7125,7 @@
       <c r="O39" s="2"/>
       <c r="P39" s="2"/>
     </row>
-    <row r="40" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="2" t="s">
         <v>255</v>
@@ -7106,7 +7165,7 @@
       <c r="O40" s="2"/>
       <c r="P40" s="2"/>
     </row>
-    <row r="41" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="2" t="s">
         <v>259</v>
@@ -7146,7 +7205,7 @@
       <c r="O41" s="2"/>
       <c r="P41" s="2"/>
     </row>
-    <row r="42" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="2" t="s">
         <v>263</v>
@@ -7186,7 +7245,7 @@
       <c r="O42" s="2"/>
       <c r="P42" s="2"/>
     </row>
-    <row r="43" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="2" t="s">
         <v>267</v>
@@ -7226,7 +7285,7 @@
       <c r="O43" s="2"/>
       <c r="P43" s="2"/>
     </row>
-    <row r="44" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="2" t="s">
         <v>271</v>
@@ -7266,7 +7325,7 @@
       <c r="O44" s="2"/>
       <c r="P44" s="2"/>
     </row>
-    <row r="45" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="2" t="s">
         <v>275</v>
@@ -7306,7 +7365,7 @@
       <c r="O45" s="2"/>
       <c r="P45" s="2"/>
     </row>
-    <row r="46" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2" t="s">
         <v>279</v>
@@ -7346,7 +7405,7 @@
       <c r="O46" s="2"/>
       <c r="P46" s="2"/>
     </row>
-    <row r="47" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="2" t="s">
         <v>283</v>
@@ -7386,7 +7445,7 @@
       <c r="O47" s="2"/>
       <c r="P47" s="2"/>
     </row>
-    <row r="48" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="2" t="s">
         <v>287</v>
@@ -7426,7 +7485,7 @@
       <c r="O48" s="2"/>
       <c r="P48" s="2"/>
     </row>
-    <row r="49" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="2" t="s">
         <v>291</v>
@@ -7466,7 +7525,7 @@
       <c r="O49" s="2"/>
       <c r="P49" s="2"/>
     </row>
-    <row r="50" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="2" t="s">
         <v>295</v>
@@ -7506,7 +7565,7 @@
       <c r="O50" s="2"/>
       <c r="P50" s="2"/>
     </row>
-    <row r="51" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="2" t="s">
         <v>300</v>
@@ -7546,7 +7605,7 @@
       <c r="O51" s="2"/>
       <c r="P51" s="2"/>
     </row>
-    <row r="52" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="2" t="s">
         <v>305</v>
@@ -7586,7 +7645,7 @@
       <c r="O52" s="2"/>
       <c r="P52" s="2"/>
     </row>
-    <row r="53" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="2" t="s">
         <v>309</v>
@@ -7626,7 +7685,7 @@
       <c r="O53" s="2"/>
       <c r="P53" s="2"/>
     </row>
-    <row r="54" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="2" t="s">
         <v>313</v>
@@ -7666,7 +7725,7 @@
       <c r="O54" s="2"/>
       <c r="P54" s="2"/>
     </row>
-    <row r="55" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2"/>
       <c r="B55" s="2" t="s">
         <v>317</v>
@@ -7706,7 +7765,7 @@
       <c r="O55" s="2"/>
       <c r="P55" s="2"/>
     </row>
-    <row r="56" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
       <c r="B56" s="2" t="s">
         <v>321</v>
@@ -7746,7 +7805,7 @@
       <c r="O56" s="2"/>
       <c r="P56" s="2"/>
     </row>
-    <row r="57" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
       <c r="B57" s="2" t="s">
         <v>325</v>
@@ -7786,7 +7845,7 @@
       <c r="O57" s="2"/>
       <c r="P57" s="2"/>
     </row>
-    <row r="58" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
       <c r="B58" s="2" t="s">
         <v>329</v>
@@ -7826,7 +7885,7 @@
       <c r="O58" s="2"/>
       <c r="P58" s="2"/>
     </row>
-    <row r="59" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2"/>
       <c r="B59" s="2" t="s">
         <v>333</v>
@@ -7866,7 +7925,7 @@
       <c r="O59" s="2"/>
       <c r="P59" s="2"/>
     </row>
-    <row r="60" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
       <c r="B60" s="2" t="s">
         <v>337</v>
@@ -7906,7 +7965,7 @@
       <c r="O60" s="2"/>
       <c r="P60" s="2"/>
     </row>
-    <row r="61" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2"/>
       <c r="B61" s="2" t="s">
         <v>341</v>
@@ -7946,7 +8005,7 @@
       <c r="O61" s="2"/>
       <c r="P61" s="2"/>
     </row>
-    <row r="62" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:16" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
       <c r="B62" s="2" t="s">
         <v>345</v>
@@ -7986,7 +8045,7 @@
       <c r="O62" s="2"/>
       <c r="P62" s="2"/>
     </row>
-    <row r="63" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2"/>
       <c r="B63" s="2" t="s">
         <v>350</v>
@@ -8026,7 +8085,7 @@
       <c r="O63" s="2"/>
       <c r="P63" s="2"/>
     </row>
-    <row r="64" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2"/>
       <c r="B64" s="2" t="s">
         <v>354</v>
@@ -8066,7 +8125,7 @@
       <c r="O64" s="2"/>
       <c r="P64" s="2"/>
     </row>
-    <row r="65" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2"/>
       <c r="B65" s="2" t="s">
         <v>358</v>
@@ -8106,7 +8165,7 @@
       <c r="O65" s="2"/>
       <c r="P65" s="2"/>
     </row>
-    <row r="66" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2"/>
       <c r="B66" s="2" t="s">
         <v>362</v>
@@ -8146,7 +8205,7 @@
       <c r="O66" s="2"/>
       <c r="P66" s="2"/>
     </row>
-    <row r="67" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2"/>
       <c r="B67" s="2" t="s">
         <v>366</v>
@@ -8186,7 +8245,7 @@
       <c r="O67" s="2"/>
       <c r="P67" s="2"/>
     </row>
-    <row r="68" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2"/>
       <c r="B68" s="2" t="s">
         <v>367</v>
@@ -8226,7 +8285,7 @@
       <c r="O68" s="2"/>
       <c r="P68" s="2"/>
     </row>
-    <row r="69" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2"/>
       <c r="B69" s="2" t="s">
         <v>371</v>
@@ -8266,7 +8325,7 @@
       <c r="O69" s="2"/>
       <c r="P69" s="2"/>
     </row>
-    <row r="70" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2"/>
       <c r="B70" s="2" t="s">
         <v>376</v>
@@ -8306,7 +8365,7 @@
       <c r="O70" s="2"/>
       <c r="P70" s="2"/>
     </row>
-    <row r="71" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2"/>
       <c r="B71" s="2" t="s">
         <v>380</v>
@@ -8346,7 +8405,7 @@
       <c r="O71" s="2"/>
       <c r="P71" s="2"/>
     </row>
-    <row r="72" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:16" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2"/>
       <c r="B72" s="2" t="s">
         <v>385</v>
@@ -8386,7 +8445,7 @@
       <c r="O72" s="2"/>
       <c r="P72" s="2"/>
     </row>
-    <row r="73" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2"/>
       <c r="B73" s="2" t="s">
         <v>390</v>
@@ -8426,7 +8485,7 @@
       <c r="O73" s="2"/>
       <c r="P73" s="2"/>
     </row>
-    <row r="74" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2"/>
       <c r="B74" s="2" t="s">
         <v>394</v>
@@ -8466,7 +8525,7 @@
       <c r="O74" s="2"/>
       <c r="P74" s="2"/>
     </row>
-    <row r="75" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2"/>
       <c r="B75" s="2" t="s">
         <v>398</v>
@@ -8506,7 +8565,7 @@
       <c r="O75" s="2"/>
       <c r="P75" s="2"/>
     </row>
-    <row r="76" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2"/>
       <c r="B76" s="2" t="s">
         <v>403</v>
@@ -8546,7 +8605,7 @@
       <c r="O76" s="2"/>
       <c r="P76" s="2"/>
     </row>
-    <row r="77" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2"/>
       <c r="B77" s="2" t="s">
         <v>407</v>
@@ -8586,7 +8645,7 @@
       <c r="O77" s="2"/>
       <c r="P77" s="2"/>
     </row>
-    <row r="78" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2"/>
       <c r="B78" s="2" t="s">
         <v>411</v>
@@ -8626,7 +8685,7 @@
       <c r="O78" s="2"/>
       <c r="P78" s="2"/>
     </row>
-    <row r="79" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2"/>
       <c r="B79" s="2" t="s">
         <v>415</v>
@@ -8666,7 +8725,7 @@
       <c r="O79" s="2"/>
       <c r="P79" s="2"/>
     </row>
-    <row r="80" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2"/>
       <c r="B80" s="2" t="s">
         <v>419</v>
@@ -8706,7 +8765,7 @@
       <c r="O80" s="2"/>
       <c r="P80" s="2"/>
     </row>
-    <row r="81" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2"/>
       <c r="B81" s="2" t="s">
         <v>424</v>
@@ -8746,7 +8805,7 @@
       <c r="O81" s="2"/>
       <c r="P81" s="2"/>
     </row>
-    <row r="82" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2"/>
       <c r="B82" s="2" t="s">
         <v>428</v>
@@ -8786,7 +8845,7 @@
       <c r="O82" s="2"/>
       <c r="P82" s="2"/>
     </row>
-    <row r="83" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2"/>
       <c r="B83" s="2" t="s">
         <v>432</v>
@@ -8826,7 +8885,7 @@
       <c r="O83" s="2"/>
       <c r="P83" s="2"/>
     </row>
-    <row r="84" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2"/>
       <c r="B84" s="2" t="s">
         <v>436</v>
@@ -8866,7 +8925,7 @@
       <c r="O84" s="2"/>
       <c r="P84" s="2"/>
     </row>
-    <row r="85" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2"/>
       <c r="B85" s="2" t="s">
         <v>440</v>
@@ -8906,7 +8965,7 @@
       <c r="O85" s="2"/>
       <c r="P85" s="2"/>
     </row>
-    <row r="86" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2"/>
       <c r="B86" s="2" t="s">
         <v>444</v>
@@ -8946,7 +9005,7 @@
       <c r="O86" s="2"/>
       <c r="P86" s="2"/>
     </row>
-    <row r="87" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2"/>
       <c r="B87" s="2" t="s">
         <v>448</v>
@@ -8986,7 +9045,7 @@
       <c r="O87" s="2"/>
       <c r="P87" s="2"/>
     </row>
-    <row r="88" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2"/>
       <c r="B88" s="2" t="s">
         <v>453</v>
@@ -9026,7 +9085,7 @@
       <c r="O88" s="2"/>
       <c r="P88" s="2"/>
     </row>
-    <row r="89" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2"/>
       <c r="B89" s="2" t="s">
         <v>457</v>
@@ -9066,7 +9125,7 @@
       <c r="O89" s="2"/>
       <c r="P89" s="2"/>
     </row>
-    <row r="90" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2"/>
       <c r="B90" s="2" t="s">
         <v>461</v>
@@ -9106,7 +9165,7 @@
       <c r="O90" s="2"/>
       <c r="P90" s="2"/>
     </row>
-    <row r="91" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2"/>
       <c r="B91" s="2" t="s">
         <v>465</v>
@@ -9146,7 +9205,7 @@
       <c r="O91" s="2"/>
       <c r="P91" s="2"/>
     </row>
-    <row r="92" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2"/>
       <c r="B92" s="2" t="s">
         <v>471</v>
@@ -9186,7 +9245,7 @@
       <c r="O92" s="2"/>
       <c r="P92" s="2"/>
     </row>
-    <row r="93" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2"/>
       <c r="B93" s="2" t="s">
         <v>475</v>
@@ -9226,7 +9285,7 @@
       <c r="O93" s="2"/>
       <c r="P93" s="2"/>
     </row>
-    <row r="94" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2"/>
       <c r="B94" s="2" t="s">
         <v>479</v>
@@ -9266,7 +9325,7 @@
       <c r="O94" s="2"/>
       <c r="P94" s="2"/>
     </row>
-    <row r="95" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2"/>
       <c r="B95" s="2" t="s">
         <v>483</v>
@@ -9306,7 +9365,7 @@
       <c r="O95" s="2"/>
       <c r="P95" s="2"/>
     </row>
-    <row r="96" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2"/>
       <c r="B96" s="2" t="s">
         <v>487</v>
@@ -9346,7 +9405,7 @@
       <c r="O96" s="2"/>
       <c r="P96" s="2"/>
     </row>
-    <row r="97" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2"/>
       <c r="B97" s="2" t="s">
         <v>491</v>
@@ -9386,7 +9445,7 @@
       <c r="O97" s="2"/>
       <c r="P97" s="2"/>
     </row>
-    <row r="98" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2"/>
       <c r="B98" s="2" t="s">
         <v>495</v>
@@ -9426,7 +9485,7 @@
       <c r="O98" s="2"/>
       <c r="P98" s="2"/>
     </row>
-    <row r="99" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2"/>
       <c r="B99" s="2" t="s">
         <v>499</v>
@@ -9466,7 +9525,7 @@
       <c r="O99" s="2"/>
       <c r="P99" s="2"/>
     </row>
-    <row r="100" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2"/>
       <c r="B100" s="2" t="s">
         <v>503</v>
@@ -9506,7 +9565,7 @@
       <c r="O100" s="2"/>
       <c r="P100" s="2"/>
     </row>
-    <row r="101" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2"/>
       <c r="B101" s="2" t="s">
         <v>507</v>
@@ -9546,7 +9605,7 @@
       <c r="O101" s="2"/>
       <c r="P101" s="2"/>
     </row>
-    <row r="102" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2"/>
       <c r="B102" s="2" t="s">
         <v>512</v>
@@ -9586,7 +9645,7 @@
       <c r="O102" s="2"/>
       <c r="P102" s="2"/>
     </row>
-    <row r="103" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2"/>
       <c r="B103" s="2" t="s">
         <v>516</v>
@@ -9626,7 +9685,7 @@
       <c r="O103" s="2"/>
       <c r="P103" s="2"/>
     </row>
-    <row r="104" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2"/>
       <c r="B104" s="2" t="s">
         <v>521</v>
@@ -9666,7 +9725,7 @@
       <c r="O104" s="2"/>
       <c r="P104" s="2"/>
     </row>
-    <row r="105" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2"/>
       <c r="B105" s="2" t="s">
         <v>526</v>
@@ -9706,7 +9765,7 @@
       <c r="O105" s="2"/>
       <c r="P105" s="2"/>
     </row>
-    <row r="106" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2"/>
       <c r="B106" s="2" t="s">
         <v>530</v>
@@ -9746,7 +9805,7 @@
       <c r="O106" s="2"/>
       <c r="P106" s="2"/>
     </row>
-    <row r="107" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2"/>
       <c r="B107" s="2" t="s">
         <v>534</v>
@@ -9786,7 +9845,7 @@
       <c r="O107" s="2"/>
       <c r="P107" s="2"/>
     </row>
-    <row r="108" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2"/>
       <c r="B108" s="2" t="s">
         <v>538</v>
@@ -9826,7 +9885,7 @@
       <c r="O108" s="2"/>
       <c r="P108" s="2"/>
     </row>
-    <row r="109" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2"/>
       <c r="B109" s="2" t="s">
         <v>542</v>
@@ -9866,7 +9925,7 @@
       <c r="O109" s="2"/>
       <c r="P109" s="2"/>
     </row>
-    <row r="110" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2"/>
       <c r="B110" s="2" t="s">
         <v>546</v>
@@ -9906,7 +9965,7 @@
       <c r="O110" s="2"/>
       <c r="P110" s="2"/>
     </row>
-    <row r="111" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2"/>
       <c r="B111" s="2" t="s">
         <v>550</v>
@@ -9946,7 +10005,7 @@
       <c r="O111" s="2"/>
       <c r="P111" s="2"/>
     </row>
-    <row r="112" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2"/>
       <c r="B112" s="2" t="s">
         <v>554</v>
@@ -9986,7 +10045,7 @@
       <c r="O112" s="2"/>
       <c r="P112" s="2"/>
     </row>
-    <row r="113" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2"/>
       <c r="B113" s="2" t="s">
         <v>558</v>
@@ -10026,7 +10085,7 @@
       <c r="O113" s="2"/>
       <c r="P113" s="2"/>
     </row>
-    <row r="114" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2"/>
       <c r="B114" s="2" t="s">
         <v>562</v>
@@ -10066,7 +10125,7 @@
       <c r="O114" s="2"/>
       <c r="P114" s="2"/>
     </row>
-    <row r="115" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2"/>
       <c r="B115" s="2" t="s">
         <v>566</v>
@@ -10106,7 +10165,7 @@
       <c r="O115" s="2"/>
       <c r="P115" s="2"/>
     </row>
-    <row r="116" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2"/>
       <c r="B116" s="2" t="s">
         <v>570</v>
@@ -10146,7 +10205,7 @@
       <c r="O116" s="2"/>
       <c r="P116" s="2"/>
     </row>
-    <row r="117" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2"/>
       <c r="B117" s="2" t="s">
         <v>574</v>
@@ -10186,7 +10245,7 @@
       <c r="O117" s="2"/>
       <c r="P117" s="2"/>
     </row>
-    <row r="118" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2"/>
       <c r="B118" s="2" t="s">
         <v>578</v>
@@ -10226,7 +10285,7 @@
       <c r="O118" s="2"/>
       <c r="P118" s="2"/>
     </row>
-    <row r="119" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:16" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2"/>
       <c r="B119" s="2" t="s">
         <v>582</v>
@@ -10266,7 +10325,7 @@
       <c r="O119" s="2"/>
       <c r="P119" s="2"/>
     </row>
-    <row r="120" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2"/>
       <c r="B120" s="2" t="s">
         <v>586</v>
@@ -10306,7 +10365,7 @@
       <c r="O120" s="2"/>
       <c r="P120" s="2"/>
     </row>
-    <row r="121" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2"/>
       <c r="B121" s="2" t="s">
         <v>591</v>
@@ -10346,7 +10405,7 @@
       <c r="O121" s="2"/>
       <c r="P121" s="2"/>
     </row>
-    <row r="122" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2"/>
       <c r="B122" s="2" t="s">
         <v>595</v>
@@ -10386,7 +10445,7 @@
       <c r="O122" s="2"/>
       <c r="P122" s="2"/>
     </row>
-    <row r="123" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2"/>
       <c r="B123" s="2" t="s">
         <v>599</v>
@@ -10426,7 +10485,7 @@
       <c r="O123" s="2"/>
       <c r="P123" s="2"/>
     </row>
-    <row r="124" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2"/>
       <c r="B124" s="2" t="s">
         <v>603</v>
@@ -10466,7 +10525,7 @@
       <c r="O124" s="2"/>
       <c r="P124" s="2"/>
     </row>
-    <row r="125" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2"/>
       <c r="B125" s="2" t="s">
         <v>607</v>
@@ -10506,7 +10565,7 @@
       <c r="O125" s="2"/>
       <c r="P125" s="2"/>
     </row>
-    <row r="126" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2"/>
       <c r="B126" s="2" t="s">
         <v>611</v>
@@ -10546,7 +10605,7 @@
       <c r="O126" s="2"/>
       <c r="P126" s="2"/>
     </row>
-    <row r="127" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2"/>
       <c r="B127" s="2" t="s">
         <v>615</v>
@@ -10586,7 +10645,7 @@
       <c r="O127" s="2"/>
       <c r="P127" s="2"/>
     </row>
-    <row r="128" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2"/>
       <c r="B128" s="2" t="s">
         <v>619</v>
@@ -10626,7 +10685,7 @@
       <c r="O128" s="2"/>
       <c r="P128" s="2"/>
     </row>
-    <row r="129" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2"/>
       <c r="B129" s="2" t="s">
         <v>623</v>
@@ -10666,7 +10725,7 @@
       <c r="O129" s="2"/>
       <c r="P129" s="2"/>
     </row>
-    <row r="130" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2"/>
       <c r="B130" s="2" t="s">
         <v>627</v>
@@ -10706,7 +10765,7 @@
       <c r="O130" s="2"/>
       <c r="P130" s="2"/>
     </row>
-    <row r="131" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2"/>
       <c r="B131" s="2" t="s">
         <v>631</v>
@@ -10746,7 +10805,7 @@
       <c r="O131" s="2"/>
       <c r="P131" s="2"/>
     </row>
-    <row r="132" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2"/>
       <c r="B132" s="2" t="s">
         <v>635</v>
@@ -10786,7 +10845,7 @@
       <c r="O132" s="2"/>
       <c r="P132" s="2"/>
     </row>
-    <row r="133" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2"/>
       <c r="B133" s="2" t="s">
         <v>640</v>
@@ -10826,7 +10885,7 @@
       <c r="O133" s="2"/>
       <c r="P133" s="2"/>
     </row>
-    <row r="134" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2"/>
       <c r="B134" s="2" t="s">
         <v>645</v>
@@ -10866,7 +10925,7 @@
       <c r="O134" s="2"/>
       <c r="P134" s="2"/>
     </row>
-    <row r="135" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2"/>
       <c r="B135" s="2" t="s">
         <v>649</v>
@@ -10906,7 +10965,7 @@
       <c r="O135" s="2"/>
       <c r="P135" s="2"/>
     </row>
-    <row r="136" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2"/>
       <c r="B136" s="2" t="s">
         <v>653</v>
@@ -10946,7 +11005,7 @@
       <c r="O136" s="2"/>
       <c r="P136" s="2"/>
     </row>
-    <row r="137" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2"/>
       <c r="B137" s="2" t="s">
         <v>657</v>
@@ -10986,7 +11045,7 @@
       <c r="O137" s="2"/>
       <c r="P137" s="2"/>
     </row>
-    <row r="138" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2"/>
       <c r="B138" s="2" t="s">
         <v>661</v>
@@ -11026,7 +11085,7 @@
       <c r="O138" s="2"/>
       <c r="P138" s="2"/>
     </row>
-    <row r="139" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2"/>
       <c r="B139" s="2" t="s">
         <v>665</v>
@@ -11066,7 +11125,7 @@
       <c r="O139" s="2"/>
       <c r="P139" s="2"/>
     </row>
-    <row r="140" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2"/>
       <c r="B140" s="2" t="s">
         <v>669</v>
@@ -11106,7 +11165,7 @@
       <c r="O140" s="2"/>
       <c r="P140" s="2"/>
     </row>
-    <row r="141" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2"/>
       <c r="B141" s="2" t="s">
         <v>673</v>
@@ -11146,7 +11205,7 @@
       <c r="O141" s="2"/>
       <c r="P141" s="2"/>
     </row>
-    <row r="142" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2"/>
       <c r="B142" s="2" t="s">
         <v>677</v>
@@ -11186,7 +11245,7 @@
       <c r="O142" s="2"/>
       <c r="P142" s="2"/>
     </row>
-    <row r="143" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2"/>
       <c r="B143" s="2" t="s">
         <v>681</v>
@@ -11226,7 +11285,7 @@
       <c r="O143" s="2"/>
       <c r="P143" s="2"/>
     </row>
-    <row r="144" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2"/>
       <c r="B144" s="2" t="s">
         <v>685</v>
@@ -11266,7 +11325,7 @@
       <c r="O144" s="2"/>
       <c r="P144" s="2"/>
     </row>
-    <row r="145" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2"/>
       <c r="B145" s="2" t="s">
         <v>689</v>
@@ -11306,7 +11365,7 @@
       <c r="O145" s="2"/>
       <c r="P145" s="2"/>
     </row>
-    <row r="146" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2"/>
       <c r="B146" s="2" t="s">
         <v>693</v>
@@ -11346,7 +11405,7 @@
       <c r="O146" s="2"/>
       <c r="P146" s="2"/>
     </row>
-    <row r="147" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2"/>
       <c r="B147" s="2" t="s">
         <v>697</v>
@@ -11386,7 +11445,7 @@
       <c r="O147" s="2"/>
       <c r="P147" s="2"/>
     </row>
-    <row r="148" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2"/>
       <c r="B148" s="2" t="s">
         <v>701</v>
@@ -11426,7 +11485,7 @@
       <c r="O148" s="2"/>
       <c r="P148" s="2"/>
     </row>
-    <row r="149" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2"/>
       <c r="B149" s="2" t="s">
         <v>706</v>
@@ -11466,7 +11525,7 @@
       <c r="O149" s="2"/>
       <c r="P149" s="2"/>
     </row>
-    <row r="150" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2"/>
       <c r="B150" s="2" t="s">
         <v>710</v>
@@ -11506,7 +11565,7 @@
       <c r="O150" s="2"/>
       <c r="P150" s="2"/>
     </row>
-    <row r="151" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2"/>
       <c r="B151" s="2" t="s">
         <v>714</v>
@@ -11546,7 +11605,7 @@
       <c r="O151" s="2"/>
       <c r="P151" s="2"/>
     </row>
-    <row r="152" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2"/>
       <c r="B152" s="2" t="s">
         <v>719</v>
@@ -11586,7 +11645,7 @@
       <c r="O152" s="2"/>
       <c r="P152" s="2"/>
     </row>
-    <row r="153" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2"/>
       <c r="B153" s="2" t="s">
         <v>723</v>
@@ -11626,7 +11685,7 @@
       <c r="O153" s="2"/>
       <c r="P153" s="2"/>
     </row>
-    <row r="154" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2"/>
       <c r="B154" s="2" t="s">
         <v>727</v>
@@ -11666,7 +11725,7 @@
       <c r="O154" s="2"/>
       <c r="P154" s="2"/>
     </row>
-    <row r="155" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2"/>
       <c r="B155" s="2" t="s">
         <v>731</v>
@@ -11706,7 +11765,7 @@
       <c r="O155" s="2"/>
       <c r="P155" s="2"/>
     </row>
-    <row r="156" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2"/>
       <c r="B156" s="2" t="s">
         <v>735</v>
@@ -11746,7 +11805,7 @@
       <c r="O156" s="2"/>
       <c r="P156" s="2"/>
     </row>
-    <row r="157" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2"/>
       <c r="B157" s="2" t="s">
         <v>740</v>
@@ -11786,7 +11845,7 @@
       <c r="O157" s="2"/>
       <c r="P157" s="2"/>
     </row>
-    <row r="158" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2"/>
       <c r="B158" s="2" t="s">
         <v>744</v>
@@ -11826,7 +11885,7 @@
       <c r="O158" s="2"/>
       <c r="P158" s="2"/>
     </row>
-    <row r="159" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2"/>
       <c r="B159" s="2" t="s">
         <v>749</v>
@@ -11866,7 +11925,7 @@
       <c r="O159" s="2"/>
       <c r="P159" s="2"/>
     </row>
-    <row r="160" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2"/>
       <c r="B160" s="2" t="s">
         <v>753</v>
@@ -11906,7 +11965,7 @@
       <c r="O160" s="2"/>
       <c r="P160" s="2"/>
     </row>
-    <row r="161" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2"/>
       <c r="B161" s="2" t="s">
         <v>757</v>
@@ -11946,7 +12005,7 @@
       <c r="O161" s="2"/>
       <c r="P161" s="2"/>
     </row>
-    <row r="162" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2"/>
       <c r="B162" s="2" t="s">
         <v>761</v>
@@ -12082,7 +12141,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="165" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2"/>
       <c r="B165" s="2" t="s">
         <v>772</v>
@@ -12122,7 +12181,7 @@
       <c r="O165" s="2"/>
       <c r="P165" s="2"/>
     </row>
-    <row r="166" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2"/>
       <c r="B166" s="2" t="s">
         <v>776</v>
@@ -12162,7 +12221,7 @@
       <c r="O166" s="2"/>
       <c r="P166" s="2"/>
     </row>
-    <row r="167" spans="1:16" ht="105" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:16" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2"/>
       <c r="B167" s="2" t="s">
         <v>780</v>
@@ -12202,7 +12261,7 @@
       <c r="O167" s="2"/>
       <c r="P167" s="2"/>
     </row>
-    <row r="168" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2"/>
       <c r="B168" s="2" t="s">
         <v>785</v>
@@ -12242,7 +12301,7 @@
       <c r="O168" s="2"/>
       <c r="P168" s="2"/>
     </row>
-    <row r="169" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2"/>
       <c r="B169" s="2" t="s">
         <v>789</v>
@@ -12282,7 +12341,7 @@
       <c r="O169" s="2"/>
       <c r="P169" s="2"/>
     </row>
-    <row r="170" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2"/>
       <c r="B170" s="2" t="s">
         <v>793</v>
@@ -12322,7 +12381,7 @@
       <c r="O170" s="2"/>
       <c r="P170" s="2"/>
     </row>
-    <row r="171" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2"/>
       <c r="B171" s="2" t="s">
         <v>797</v>
@@ -12362,7 +12421,7 @@
       <c r="O171" s="2"/>
       <c r="P171" s="2"/>
     </row>
-    <row r="172" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2"/>
       <c r="B172" s="2" t="s">
         <v>798</v>
@@ -12402,7 +12461,7 @@
       <c r="O172" s="2"/>
       <c r="P172" s="2"/>
     </row>
-    <row r="173" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2"/>
       <c r="B173" s="2" t="s">
         <v>802</v>
@@ -12442,7 +12501,7 @@
       <c r="O173" s="2"/>
       <c r="P173" s="2"/>
     </row>
-    <row r="174" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2"/>
       <c r="B174" s="2" t="s">
         <v>806</v>
@@ -12684,7 +12743,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="90" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="2" t="s">
         <v>822</v>
@@ -12730,8 +12789,10 @@
       <c r="Q3" s="2"/>
       <c r="R3" s="2"/>
     </row>
-    <row r="4" spans="1:18" ht="60" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
+    <row r="4" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>1132</v>
+      </c>
       <c r="B4" s="2" t="s">
         <v>827</v>
       </c>
@@ -12769,14 +12830,20 @@
         <v>831</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="O4" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="O4" s="7" t="s">
+        <v>1130</v>
+      </c>
       <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
-    </row>
-    <row r="5" spans="1:18" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q4" s="2" t="s">
+        <v>1135</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="2" t="s">
         <v>832</v>
@@ -12822,7 +12889,7 @@
       <c r="Q5" s="2"/>
       <c r="R5" s="2"/>
     </row>
-    <row r="6" spans="1:18" ht="90" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
         <v>836</v>
@@ -13030,8 +13097,10 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="60" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
+    <row r="10" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>1132</v>
+      </c>
       <c r="B10" s="2" t="s">
         <v>853</v>
       </c>
@@ -13054,7 +13123,7 @@
         <v>816</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>817</v>
+        <v>829</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>855</v>
@@ -13069,14 +13138,20 @@
         <v>856</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="O10" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="O10" s="7" t="s">
+        <v>1130</v>
+      </c>
       <c r="P10" s="2"/>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="2"/>
-    </row>
-    <row r="11" spans="1:18" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q10" s="2" t="s">
+        <v>1135</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
         <v>857</v>
@@ -13122,7 +13197,7 @@
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
     </row>
-    <row r="12" spans="1:18" ht="90" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2" t="s">
         <v>861</v>
@@ -13168,7 +13243,7 @@
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
     </row>
-    <row r="13" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2" t="s">
         <v>865</v>
@@ -13214,7 +13289,7 @@
       <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
     </row>
-    <row r="14" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2" t="s">
         <v>869</v>
@@ -13260,7 +13335,7 @@
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
     </row>
-    <row r="15" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2" t="s">
         <v>876</v>
@@ -13306,7 +13381,7 @@
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
     </row>
-    <row r="16" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="2" t="s">
         <v>880</v>
@@ -13352,7 +13427,7 @@
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
     </row>
-    <row r="17" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2" t="s">
         <v>884</v>
@@ -13398,7 +13473,7 @@
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
     </row>
-    <row r="18" spans="1:18" ht="90" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2" t="s">
         <v>888</v>
@@ -13498,7 +13573,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="90" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="2" t="s">
         <v>896</v>
@@ -13544,8 +13619,10 @@
       <c r="Q20" s="2"/>
       <c r="R20" s="2"/>
     </row>
-    <row r="21" spans="1:18" ht="60" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
+    <row r="21" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>1132</v>
+      </c>
       <c r="B21" s="2" t="s">
         <v>900</v>
       </c>
@@ -13568,7 +13645,7 @@
         <v>816</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>817</v>
+        <v>829</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>902</v>
@@ -13583,12 +13660,18 @@
         <v>903</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="O21" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="O21" s="7" t="s">
+        <v>1130</v>
+      </c>
       <c r="P21" s="2"/>
-      <c r="Q21" s="2"/>
-      <c r="R21" s="2"/>
+      <c r="Q21" s="2" t="s">
+        <v>1135</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>1154</v>
+      </c>
     </row>
     <row r="22" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
@@ -13644,7 +13727,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="2" t="s">
         <v>908</v>
@@ -13846,8 +13929,10 @@
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="2"/>
+    <row r="2" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1132</v>
+      </c>
       <c r="B2" s="2" t="s">
         <v>925</v>
       </c>
@@ -13860,15 +13945,21 @@
       <c r="E2" s="2" t="s">
         <v>814</v>
       </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
+      <c r="F2" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>1134</v>
+      </c>
       <c r="H2" s="2" t="s">
         <v>926</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="J2" s="7"/>
+      <c r="J2" s="7" t="s">
+        <v>1130</v>
+      </c>
       <c r="K2" s="2" t="s">
         <v>927</v>
       </c>
@@ -13879,16 +13970,20 @@
         <v>835</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="O2" s="2"/>
+        <v>10</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>1135</v>
+      </c>
       <c r="P2" s="2" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>929</v>
       </c>
-      <c r="R2" s="2"/>
+      <c r="R2" s="2" t="s">
+        <v>1136</v>
+      </c>
     </row>
     <row r="3" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -13931,10 +14026,10 @@
         <v>856</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>927</v>
@@ -13943,10 +14038,10 @@
         <v>929</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>1136</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="2" t="s">
         <v>931</v>
@@ -13990,8 +14085,10 @@
       </c>
       <c r="R4" s="2"/>
     </row>
-    <row r="5" spans="1:18" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
+    <row r="5" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>1132</v>
+      </c>
       <c r="B5" s="2" t="s">
         <v>934</v>
       </c>
@@ -14004,15 +14101,21 @@
       <c r="E5" s="2" t="s">
         <v>814</v>
       </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
+      <c r="F5" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>1134</v>
+      </c>
       <c r="H5" s="2" t="s">
         <v>926</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="J5" s="7"/>
+      <c r="J5" s="7" t="s">
+        <v>1130</v>
+      </c>
       <c r="K5" s="2" t="s">
         <v>927</v>
       </c>
@@ -14023,18 +14126,22 @@
         <v>864</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="O5" s="2"/>
+        <v>10</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>1135</v>
+      </c>
       <c r="P5" s="2" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="Q5" s="2" t="s">
         <v>929</v>
       </c>
-      <c r="R5" s="2"/>
-    </row>
-    <row r="6" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="R5" s="2" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
         <v>935</v>
@@ -14119,10 +14226,10 @@
         <v>938</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>927</v>
@@ -14131,11 +14238,13 @@
         <v>929</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>1136</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>1132</v>
+      </c>
       <c r="B8" s="2" t="s">
         <v>939</v>
       </c>
@@ -14148,15 +14257,21 @@
       <c r="E8" s="2" t="s">
         <v>941</v>
       </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
+      <c r="F8" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>1134</v>
+      </c>
       <c r="H8" s="2" t="s">
         <v>926</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="J8" s="7"/>
+      <c r="J8" s="7" t="s">
+        <v>1130</v>
+      </c>
       <c r="K8" s="2" t="s">
         <v>927</v>
       </c>
@@ -14167,19 +14282,25 @@
         <v>942</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="O8" s="2"/>
+        <v>10</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>1135</v>
+      </c>
       <c r="P8" s="2" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="Q8" s="2" t="s">
         <v>929</v>
       </c>
-      <c r="R8" s="2"/>
-    </row>
-    <row r="9" spans="1:18" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
+      <c r="R8" s="2" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>1132</v>
+      </c>
       <c r="B9" s="2" t="s">
         <v>943</v>
       </c>
@@ -14192,15 +14313,21 @@
       <c r="E9" s="2" t="s">
         <v>941</v>
       </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
+      <c r="F9" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>1134</v>
+      </c>
       <c r="H9" s="2" t="s">
         <v>926</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="J9" s="7"/>
+      <c r="J9" s="7" t="s">
+        <v>1130</v>
+      </c>
       <c r="K9" s="2" t="s">
         <v>927</v>
       </c>
@@ -14211,19 +14338,25 @@
         <v>945</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="O9" s="2"/>
+        <v>10</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>1135</v>
+      </c>
       <c r="P9" s="2" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="Q9" s="2" t="s">
         <v>929</v>
       </c>
-      <c r="R9" s="2"/>
-    </row>
-    <row r="10" spans="1:18" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
+      <c r="R9" s="2" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>1132</v>
+      </c>
       <c r="B10" s="2" t="s">
         <v>946</v>
       </c>
@@ -14236,15 +14369,21 @@
       <c r="E10" s="2" t="s">
         <v>941</v>
       </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
+      <c r="F10" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>1134</v>
+      </c>
       <c r="H10" s="2" t="s">
         <v>926</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="J10" s="7"/>
+      <c r="J10" s="7" t="s">
+        <v>1130</v>
+      </c>
       <c r="K10" s="2" t="s">
         <v>929</v>
       </c>
@@ -14255,19 +14394,25 @@
         <v>948</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="O10" s="2"/>
+        <v>10</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>1135</v>
+      </c>
       <c r="P10" s="2" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="Q10" s="2" t="s">
         <v>929</v>
       </c>
-      <c r="R10" s="2"/>
-    </row>
-    <row r="11" spans="1:18" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
+      <c r="R10" s="2" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>1132</v>
+      </c>
       <c r="B11" s="2" t="s">
         <v>949</v>
       </c>
@@ -14280,15 +14425,21 @@
       <c r="E11" s="2" t="s">
         <v>941</v>
       </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
+      <c r="F11" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>1134</v>
+      </c>
       <c r="H11" s="2" t="s">
         <v>926</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="J11" s="7"/>
+      <c r="J11" s="7" t="s">
+        <v>1130</v>
+      </c>
       <c r="K11" s="2" t="s">
         <v>927</v>
       </c>
@@ -14299,18 +14450,22 @@
         <v>951</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="O11" s="2"/>
+        <v>10</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>1135</v>
+      </c>
       <c r="P11" s="2" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="Q11" s="2" t="s">
         <v>929</v>
       </c>
-      <c r="R11" s="2"/>
-    </row>
-    <row r="12" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="R11" s="2" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2" t="s">
         <v>952</v>
@@ -14354,8 +14509,10 @@
       </c>
       <c r="R12" s="2"/>
     </row>
-    <row r="13" spans="1:18" ht="45" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
+    <row r="13" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>1132</v>
+      </c>
       <c r="B13" s="2" t="s">
         <v>955</v>
       </c>
@@ -14368,15 +14525,21 @@
       <c r="E13" s="2" t="s">
         <v>941</v>
       </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
+      <c r="F13" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>1134</v>
+      </c>
       <c r="H13" s="2" t="s">
         <v>926</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="J13" s="7"/>
+      <c r="J13" s="7" t="s">
+        <v>1130</v>
+      </c>
       <c r="K13" s="2" t="s">
         <v>927</v>
       </c>
@@ -14387,19 +14550,25 @@
         <v>957</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="O13" s="2"/>
+        <v>10</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>1135</v>
+      </c>
       <c r="P13" s="2" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="Q13" s="2" t="s">
         <v>929</v>
       </c>
-      <c r="R13" s="2"/>
-    </row>
-    <row r="14" spans="1:18" ht="45" x14ac:dyDescent="0.25">
-      <c r="A14" s="2"/>
+      <c r="R13" s="2" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>1132</v>
+      </c>
       <c r="B14" s="2" t="s">
         <v>958</v>
       </c>
@@ -14412,15 +14581,21 @@
       <c r="E14" s="2" t="s">
         <v>941</v>
       </c>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
+      <c r="F14" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>1134</v>
+      </c>
       <c r="H14" s="2" t="s">
         <v>926</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="J14" s="7"/>
+      <c r="J14" s="7" t="s">
+        <v>1130</v>
+      </c>
       <c r="K14" s="2" t="s">
         <v>927</v>
       </c>
@@ -14431,18 +14606,22 @@
         <v>960</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="O14" s="2"/>
+        <v>10</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>1135</v>
+      </c>
       <c r="P14" s="2" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="Q14" s="2" t="s">
         <v>929</v>
       </c>
-      <c r="R14" s="2"/>
-    </row>
-    <row r="15" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="R14" s="2" t="s">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2" t="s">
         <v>961</v>
@@ -14486,7 +14665,7 @@
       </c>
       <c r="R15" s="2"/>
     </row>
-    <row r="16" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="2" t="s">
         <v>964</v>
@@ -14530,7 +14709,7 @@
       </c>
       <c r="R16" s="2"/>
     </row>
-    <row r="17" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2" t="s">
         <v>967</v>
@@ -14574,8 +14753,10 @@
       </c>
       <c r="R17" s="2"/>
     </row>
-    <row r="18" spans="1:18" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
+    <row r="18" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>1132</v>
+      </c>
       <c r="B18" s="2" t="s">
         <v>970</v>
       </c>
@@ -14588,15 +14769,21 @@
       <c r="E18" s="2" t="s">
         <v>941</v>
       </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
+      <c r="F18" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>1134</v>
+      </c>
       <c r="H18" s="2" t="s">
         <v>926</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="J18" s="7"/>
+      <c r="J18" s="7" t="s">
+        <v>1130</v>
+      </c>
       <c r="K18" s="2" t="s">
         <v>927</v>
       </c>
@@ -14607,19 +14794,25 @@
         <v>972</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="O18" s="2"/>
+        <v>10</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>1135</v>
+      </c>
       <c r="P18" s="2" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="Q18" s="2" t="s">
         <v>929</v>
       </c>
-      <c r="R18" s="2"/>
-    </row>
-    <row r="19" spans="1:18" ht="45" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
+      <c r="R18" s="2" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>1132</v>
+      </c>
       <c r="B19" s="2" t="s">
         <v>973</v>
       </c>
@@ -14632,15 +14825,21 @@
       <c r="E19" s="2" t="s">
         <v>941</v>
       </c>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
+      <c r="F19" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>1134</v>
+      </c>
       <c r="H19" s="2" t="s">
         <v>926</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="J19" s="7"/>
+      <c r="J19" s="7" t="s">
+        <v>1130</v>
+      </c>
       <c r="K19" s="2" t="s">
         <v>927</v>
       </c>
@@ -14651,19 +14850,25 @@
         <v>975</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="O19" s="2"/>
+        <v>10</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>1135</v>
+      </c>
       <c r="P19" s="2" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="Q19" s="2" t="s">
         <v>929</v>
       </c>
-      <c r="R19" s="2"/>
-    </row>
-    <row r="20" spans="1:18" ht="60" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
+      <c r="R19" s="2" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>1132</v>
+      </c>
       <c r="B20" s="2" t="s">
         <v>976</v>
       </c>
@@ -14676,15 +14881,21 @@
       <c r="E20" s="2" t="s">
         <v>941</v>
       </c>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
+      <c r="F20" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>1134</v>
+      </c>
       <c r="H20" s="2" t="s">
         <v>926</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="J20" s="7"/>
+      <c r="J20" s="7" t="s">
+        <v>1130</v>
+      </c>
       <c r="K20" s="2" t="s">
         <v>929</v>
       </c>
@@ -14695,16 +14906,20 @@
         <v>978</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="O20" s="2"/>
+        <v>10</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>1135</v>
+      </c>
       <c r="P20" s="2" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="Q20" s="2" t="s">
         <v>929</v>
       </c>
-      <c r="R20" s="2"/>
+      <c r="R20" s="2" t="s">
+        <v>1149</v>
+      </c>
     </row>
     <row r="21" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
@@ -14747,10 +14962,10 @@
         <v>982</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>927</v>
@@ -14759,7 +14974,7 @@
         <v>929</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>1136</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="22" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -14803,10 +15018,10 @@
         <v>986</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>927</v>
@@ -14815,7 +15030,7 @@
         <v>929</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>1136</v>
+        <v>1151</v>
       </c>
     </row>
   </sheetData>
@@ -15007,7 +15222,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="105" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="2" t="s">
         <v>998</v>
@@ -15044,7 +15259,7 @@
       </c>
       <c r="O3" s="2"/>
     </row>
-    <row r="4" spans="1:15" ht="60" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="2" t="s">
         <v>1005</v>
@@ -15081,7 +15296,7 @@
       </c>
       <c r="O4" s="2"/>
     </row>
-    <row r="5" spans="1:15" ht="90" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="2" t="s">
         <v>1011</v>
@@ -15118,7 +15333,7 @@
       </c>
       <c r="O5" s="2"/>
     </row>
-    <row r="6" spans="1:15" ht="150" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" ht="150" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
         <v>1017</v>
@@ -15155,7 +15370,7 @@
       </c>
       <c r="O6" s="2"/>
     </row>
-    <row r="7" spans="1:15" ht="60" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2" t="s">
         <v>1023</v>
@@ -15192,7 +15407,7 @@
       </c>
       <c r="O7" s="2"/>
     </row>
-    <row r="8" spans="1:15" ht="60" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2" t="s">
         <v>1029</v>
@@ -15229,7 +15444,7 @@
       </c>
       <c r="O8" s="2"/>
     </row>
-    <row r="9" spans="1:15" ht="60" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2" t="s">
         <v>1035</v>
@@ -15266,7 +15481,7 @@
       </c>
       <c r="O9" s="2"/>
     </row>
-    <row r="10" spans="1:15" ht="60" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="2" t="s">
         <v>1041</v>
@@ -15303,7 +15518,7 @@
       </c>
       <c r="O10" s="2"/>
     </row>
-    <row r="11" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
         <v>1048</v>
@@ -15340,7 +15555,7 @@
       </c>
       <c r="O11" s="2"/>
     </row>
-    <row r="12" spans="1:15" ht="75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2" t="s">
         <v>1052</v>
@@ -15377,7 +15592,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="105" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2" t="s">
         <v>1059</v>
@@ -15552,7 +15767,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>813</v>
       </c>
@@ -15601,7 +15816,7 @@
       </c>
       <c r="O2" s="2"/>
     </row>
-    <row r="3" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>823</v>
       </c>
@@ -15650,7 +15865,7 @@
       </c>
       <c r="O3" s="2"/>
     </row>
-    <row r="4" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>828</v>
       </c>
@@ -15680,26 +15895,26 @@
       </c>
       <c r="J4" s="2" t="str">
         <f>IFERROR(INDEX('Security Acceptance'!$N:$N,MATCH($I4,'Security Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
-      </c>
-      <c r="K4" s="7">
+        <v>Pass</v>
+      </c>
+      <c r="K4" s="7" t="str">
         <f>IFERROR(INDEX('Security Acceptance'!$O:$O,MATCH($I4,'Security Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>2026-10-28</v>
       </c>
       <c r="L4" s="2">
         <f>IFERROR(INDEX('Security Acceptance'!$P:$P,MATCH($I4,'Security Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M4" s="2">
+      <c r="M4" s="2" t="str">
         <f>IFERROR(INDEX('Security Acceptance'!$Q:$Q,MATCH($I4,'Security Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P0B-DB-001; package 0d30359ab5cdd4aa3577c33823de1bbc80a3d4f2; spec/meals/Phase 0B Recipe Persistence Design.md section 28; meals-db-final-manifest.json SHA256 4cbbc3eac24c13860d39ee3a0d8c6ae79c638cc5967d5274d1e7ea219091f8da; complete evidence in session b7458d86-6190-4718-8779-7c2b79a30630/files</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>1075</v>
       </c>
       <c r="O4" s="2"/>
     </row>
-    <row r="5" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>833</v>
       </c>
@@ -15748,7 +15963,7 @@
       </c>
       <c r="O5" s="2"/>
     </row>
-    <row r="6" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>837</v>
       </c>
@@ -15797,7 +16012,7 @@
       </c>
       <c r="O6" s="2"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>841</v>
       </c>
@@ -15846,7 +16061,7 @@
       </c>
       <c r="O7" s="2"/>
     </row>
-    <row r="8" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>846</v>
       </c>
@@ -15895,7 +16110,7 @@
       </c>
       <c r="O8" s="2"/>
     </row>
-    <row r="9" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>850</v>
       </c>
@@ -15944,7 +16159,7 @@
       </c>
       <c r="O9" s="2"/>
     </row>
-    <row r="10" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>854</v>
       </c>
@@ -15974,26 +16189,26 @@
       </c>
       <c r="J10" s="2" t="str">
         <f>IFERROR(INDEX('Security Acceptance'!$N:$N,MATCH($I10,'Security Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
-      </c>
-      <c r="K10" s="7">
+        <v>Pass</v>
+      </c>
+      <c r="K10" s="7" t="str">
         <f>IFERROR(INDEX('Security Acceptance'!$O:$O,MATCH($I10,'Security Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>2026-10-28</v>
       </c>
       <c r="L10" s="2">
         <f>IFERROR(INDEX('Security Acceptance'!$P:$P,MATCH($I10,'Security Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M10" s="2">
+      <c r="M10" s="2" t="str">
         <f>IFERROR(INDEX('Security Acceptance'!$Q:$Q,MATCH($I10,'Security Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P0B-DB-001; package 0d30359ab5cdd4aa3577c33823de1bbc80a3d4f2; spec/meals/Phase 0B Recipe Persistence Design.md section 28; meals-db-final-manifest.json SHA256 4cbbc3eac24c13860d39ee3a0d8c6ae79c638cc5967d5274d1e7ea219091f8da; complete evidence in session b7458d86-6190-4718-8779-7c2b79a30630/files</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>1075</v>
       </c>
       <c r="O10" s="2"/>
     </row>
-    <row r="11" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>932</v>
       </c>
@@ -16039,7 +16254,7 @@
       </c>
       <c r="O11" s="2"/>
     </row>
-    <row r="12" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>1077</v>
       </c>
@@ -16074,7 +16289,7 @@
       </c>
       <c r="O12" s="2"/>
     </row>
-    <row r="13" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>858</v>
       </c>
@@ -16123,7 +16338,7 @@
       </c>
       <c r="O13" s="2"/>
     </row>
-    <row r="14" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>862</v>
       </c>
@@ -16172,7 +16387,7 @@
       </c>
       <c r="O14" s="2"/>
     </row>
-    <row r="15" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>866</v>
       </c>
@@ -16221,7 +16436,7 @@
       </c>
       <c r="O15" s="2"/>
     </row>
-    <row r="16" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>937</v>
       </c>
@@ -16251,7 +16466,7 @@
       </c>
       <c r="J16" s="2" t="str">
         <f>IFERROR(INDEX('Database Verification'!$N:$N,MATCH($I16,'Database Verification'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Pass</v>
       </c>
       <c r="K16" s="7" t="str">
         <f>IFERROR(INDEX('Database Verification'!$J:$J,MATCH($I16,'Database Verification'!$B:$B,0)),"")</f>
@@ -16260,14 +16475,15 @@
       <c r="L16" s="2"/>
       <c r="M16" s="2" t="str">
         <f>IFERROR(INDEX('Database Verification'!$O:$O,MATCH($I16,'Database Verification'!$B:$B,0)),"")</f>
-        <v>P0B-PREFLIGHT-001: meals-0b-production-preflight-manifest.json; complete catalog/supplement JSON and CSV evidence in session b7458d86-6190-4718-8779-7c2b79a30630/files; Dashboard-verified home-maintenance-app / tawvchmjtkgykwwvnnnn</v>
+        <v>P0B-PREFLIGHT-001: meals-0b-production-preflight-manifest.json; complete catalog/supplement JSON and CSV evidence in session b7458d86-6190-4718-8779-7c2b79a30630/files; Dashboard-verified home-maintenance-app / tawvchmjtkgykwwvnnnn
+P0B-DB-001; package 0d30359ab5cdd4aa3577c33823de1bbc80a3d4f2; spec/meals/Phase 0B Recipe Persistence Design.md section 28; meals-db-final-manifest.json SHA256 4cbbc3eac24c13860d39ee3a0d8c6ae79c638cc5967d5274d1e7ea219091f8da; complete evidence in session b7458d86-6190-4718-8779-7c2b79a30630/files</v>
       </c>
       <c r="N16" s="2" t="s">
         <v>1075</v>
       </c>
       <c r="O16" s="2"/>
     </row>
-    <row r="17" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>95</v>
       </c>
@@ -16316,7 +16532,7 @@
       </c>
       <c r="O17" s="2"/>
     </row>
-    <row r="18" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>104</v>
       </c>
@@ -16365,7 +16581,7 @@
       </c>
       <c r="O18" s="2"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>108</v>
       </c>
@@ -16414,7 +16630,7 @@
       </c>
       <c r="O19" s="2"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>113</v>
       </c>
@@ -16463,7 +16679,7 @@
       </c>
       <c r="O20" s="2"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>117</v>
       </c>
@@ -16512,7 +16728,7 @@
       </c>
       <c r="O21" s="2"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>121</v>
       </c>
@@ -16561,7 +16777,7 @@
       </c>
       <c r="O22" s="2"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>125</v>
       </c>
@@ -16610,7 +16826,7 @@
       </c>
       <c r="O23" s="2"/>
     </row>
-    <row r="24" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>1083</v>
       </c>
@@ -16647,7 +16863,7 @@
       </c>
       <c r="O24" s="2"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>129</v>
       </c>
@@ -16696,7 +16912,7 @@
       </c>
       <c r="O25" s="2"/>
     </row>
-    <row r="26" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>133</v>
       </c>
@@ -16745,7 +16961,7 @@
       </c>
       <c r="O26" s="2"/>
     </row>
-    <row r="27" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>144</v>
       </c>
@@ -16794,7 +17010,7 @@
       </c>
       <c r="O27" s="2"/>
     </row>
-    <row r="28" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>148</v>
       </c>
@@ -16843,7 +17059,7 @@
       </c>
       <c r="O28" s="2"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>152</v>
       </c>
@@ -16892,7 +17108,7 @@
       </c>
       <c r="O29" s="2"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>156</v>
       </c>
@@ -16941,7 +17157,7 @@
       </c>
       <c r="O30" s="2"/>
     </row>
-    <row r="31" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>161</v>
       </c>
@@ -16990,7 +17206,7 @@
       </c>
       <c r="O31" s="2"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>166</v>
       </c>
@@ -17039,7 +17255,7 @@
       </c>
       <c r="O32" s="2"/>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>170</v>
       </c>
@@ -17088,7 +17304,7 @@
       </c>
       <c r="O33" s="2"/>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>174</v>
       </c>
@@ -17137,7 +17353,7 @@
       </c>
       <c r="O34" s="2"/>
     </row>
-    <row r="35" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>178</v>
       </c>
@@ -17186,7 +17402,7 @@
       </c>
       <c r="O35" s="2"/>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>182</v>
       </c>
@@ -17235,7 +17451,7 @@
       </c>
       <c r="O36" s="2"/>
     </row>
-    <row r="37" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>186</v>
       </c>
@@ -17284,7 +17500,7 @@
       </c>
       <c r="O37" s="2"/>
     </row>
-    <row r="38" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>192</v>
       </c>
@@ -17333,7 +17549,7 @@
       </c>
       <c r="O38" s="2"/>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>196</v>
       </c>
@@ -17382,7 +17598,7 @@
       </c>
       <c r="O39" s="2"/>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>200</v>
       </c>
@@ -17431,7 +17647,7 @@
       </c>
       <c r="O40" s="2"/>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>204</v>
       </c>
@@ -17480,7 +17696,7 @@
       </c>
       <c r="O41" s="2"/>
     </row>
-    <row r="42" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>208</v>
       </c>
@@ -17529,7 +17745,7 @@
       </c>
       <c r="O42" s="2"/>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>212</v>
       </c>
@@ -17578,7 +17794,7 @@
       </c>
       <c r="O43" s="2"/>
     </row>
-    <row r="44" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>216</v>
       </c>
@@ -17627,7 +17843,7 @@
       </c>
       <c r="O44" s="2"/>
     </row>
-    <row r="45" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>220</v>
       </c>
@@ -17676,7 +17892,7 @@
       </c>
       <c r="O45" s="2"/>
     </row>
-    <row r="46" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>224</v>
       </c>
@@ -17725,7 +17941,7 @@
       </c>
       <c r="O46" s="2"/>
     </row>
-    <row r="47" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>229</v>
       </c>
@@ -17774,7 +17990,7 @@
       </c>
       <c r="O47" s="2"/>
     </row>
-    <row r="48" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>233</v>
       </c>
@@ -17823,7 +18039,7 @@
       </c>
       <c r="O48" s="2"/>
     </row>
-    <row r="49" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>238</v>
       </c>
@@ -17872,7 +18088,7 @@
       </c>
       <c r="O49" s="2"/>
     </row>
-    <row r="50" spans="1:15" ht="60" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>242</v>
       </c>
@@ -17921,7 +18137,7 @@
       </c>
       <c r="O50" s="2"/>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>246</v>
       </c>
@@ -17970,7 +18186,7 @@
       </c>
       <c r="O51" s="2"/>
     </row>
-    <row r="52" spans="1:15" ht="60" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>252</v>
       </c>
@@ -18019,7 +18235,7 @@
       </c>
       <c r="O52" s="2"/>
     </row>
-    <row r="53" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>256</v>
       </c>
@@ -18068,7 +18284,7 @@
       </c>
       <c r="O53" s="2"/>
     </row>
-    <row r="54" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>260</v>
       </c>
@@ -18117,7 +18333,7 @@
       </c>
       <c r="O54" s="2"/>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>264</v>
       </c>
@@ -18166,7 +18382,7 @@
       </c>
       <c r="O55" s="2"/>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>268</v>
       </c>
@@ -18215,7 +18431,7 @@
       </c>
       <c r="O56" s="2"/>
     </row>
-    <row r="57" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>272</v>
       </c>
@@ -18264,7 +18480,7 @@
       </c>
       <c r="O57" s="2"/>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>276</v>
       </c>
@@ -18313,7 +18529,7 @@
       </c>
       <c r="O58" s="2"/>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>280</v>
       </c>
@@ -18362,7 +18578,7 @@
       </c>
       <c r="O59" s="2"/>
     </row>
-    <row r="60" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>284</v>
       </c>
@@ -18411,7 +18627,7 @@
       </c>
       <c r="O60" s="2"/>
     </row>
-    <row r="61" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>288</v>
       </c>
@@ -18460,7 +18676,7 @@
       </c>
       <c r="O61" s="2"/>
     </row>
-    <row r="62" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>292</v>
       </c>
@@ -18509,7 +18725,7 @@
       </c>
       <c r="O62" s="2"/>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>296</v>
       </c>
@@ -18558,7 +18774,7 @@
       </c>
       <c r="O63" s="2"/>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>301</v>
       </c>
@@ -18607,7 +18823,7 @@
       </c>
       <c r="O64" s="2"/>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>306</v>
       </c>
@@ -18656,7 +18872,7 @@
       </c>
       <c r="O65" s="2"/>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>310</v>
       </c>
@@ -18705,7 +18921,7 @@
       </c>
       <c r="O66" s="2"/>
     </row>
-    <row r="67" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>314</v>
       </c>
@@ -18754,7 +18970,7 @@
       </c>
       <c r="O67" s="2"/>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>318</v>
       </c>
@@ -18803,7 +19019,7 @@
       </c>
       <c r="O68" s="2"/>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>322</v>
       </c>
@@ -18852,7 +19068,7 @@
       </c>
       <c r="O69" s="2"/>
     </row>
-    <row r="70" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>326</v>
       </c>
@@ -18901,7 +19117,7 @@
       </c>
       <c r="O70" s="2"/>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>330</v>
       </c>
@@ -18950,7 +19166,7 @@
       </c>
       <c r="O71" s="2"/>
     </row>
-    <row r="72" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>334</v>
       </c>
@@ -18999,7 +19215,7 @@
       </c>
       <c r="O72" s="2"/>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>338</v>
       </c>
@@ -19048,7 +19264,7 @@
       </c>
       <c r="O73" s="2"/>
     </row>
-    <row r="74" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>342</v>
       </c>
@@ -19097,7 +19313,7 @@
       </c>
       <c r="O74" s="2"/>
     </row>
-    <row r="75" spans="1:15" ht="60" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>346</v>
       </c>
@@ -19146,7 +19362,7 @@
       </c>
       <c r="O75" s="2"/>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>351</v>
       </c>
@@ -19195,7 +19411,7 @@
       </c>
       <c r="O76" s="2"/>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>355</v>
       </c>
@@ -19244,7 +19460,7 @@
       </c>
       <c r="O77" s="2"/>
     </row>
-    <row r="78" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>359</v>
       </c>
@@ -19293,7 +19509,7 @@
       </c>
       <c r="O78" s="2"/>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>363</v>
       </c>
@@ -19342,7 +19558,7 @@
       </c>
       <c r="O79" s="2"/>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>368</v>
       </c>
@@ -19391,7 +19607,7 @@
       </c>
       <c r="O80" s="2"/>
     </row>
-    <row r="81" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>372</v>
       </c>
@@ -19440,7 +19656,7 @@
       </c>
       <c r="O81" s="2"/>
     </row>
-    <row r="82" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>377</v>
       </c>
@@ -19489,7 +19705,7 @@
       </c>
       <c r="O82" s="2"/>
     </row>
-    <row r="83" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>381</v>
       </c>
@@ -19538,7 +19754,7 @@
       </c>
       <c r="O83" s="2"/>
     </row>
-    <row r="84" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>386</v>
       </c>
@@ -19587,7 +19803,7 @@
       </c>
       <c r="O84" s="2"/>
     </row>
-    <row r="85" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>391</v>
       </c>
@@ -19636,7 +19852,7 @@
       </c>
       <c r="O85" s="2"/>
     </row>
-    <row r="86" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>395</v>
       </c>
@@ -19685,7 +19901,7 @@
       </c>
       <c r="O86" s="2"/>
     </row>
-    <row r="87" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>399</v>
       </c>
@@ -19734,7 +19950,7 @@
       </c>
       <c r="O87" s="2"/>
     </row>
-    <row r="88" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>404</v>
       </c>
@@ -19783,7 +19999,7 @@
       </c>
       <c r="O88" s="2"/>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>408</v>
       </c>
@@ -19832,7 +20048,7 @@
       </c>
       <c r="O89" s="2"/>
     </row>
-    <row r="90" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>412</v>
       </c>
@@ -19881,7 +20097,7 @@
       </c>
       <c r="O90" s="2"/>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>416</v>
       </c>
@@ -19930,7 +20146,7 @@
       </c>
       <c r="O91" s="2"/>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>420</v>
       </c>
@@ -19979,7 +20195,7 @@
       </c>
       <c r="O92" s="2"/>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>425</v>
       </c>
@@ -20028,7 +20244,7 @@
       </c>
       <c r="O93" s="2"/>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>429</v>
       </c>
@@ -20077,7 +20293,7 @@
       </c>
       <c r="O94" s="2"/>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>433</v>
       </c>
@@ -20126,7 +20342,7 @@
       </c>
       <c r="O95" s="2"/>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>437</v>
       </c>
@@ -20175,7 +20391,7 @@
       </c>
       <c r="O96" s="2"/>
     </row>
-    <row r="97" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>441</v>
       </c>
@@ -20224,7 +20440,7 @@
       </c>
       <c r="O97" s="2"/>
     </row>
-    <row r="98" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>445</v>
       </c>
@@ -20273,7 +20489,7 @@
       </c>
       <c r="O98" s="2"/>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>449</v>
       </c>
@@ -20322,7 +20538,7 @@
       </c>
       <c r="O99" s="2"/>
     </row>
-    <row r="100" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>454</v>
       </c>
@@ -20371,7 +20587,7 @@
       </c>
       <c r="O100" s="2"/>
     </row>
-    <row r="101" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>458</v>
       </c>
@@ -20420,7 +20636,7 @@
       </c>
       <c r="O101" s="2"/>
     </row>
-    <row r="102" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>462</v>
       </c>
@@ -20469,7 +20685,7 @@
       </c>
       <c r="O102" s="2"/>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>466</v>
       </c>
@@ -20518,7 +20734,7 @@
       </c>
       <c r="O103" s="2"/>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>472</v>
       </c>
@@ -20567,7 +20783,7 @@
       </c>
       <c r="O104" s="2"/>
     </row>
-    <row r="105" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>476</v>
       </c>
@@ -20616,7 +20832,7 @@
       </c>
       <c r="O105" s="2"/>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>480</v>
       </c>
@@ -20665,7 +20881,7 @@
       </c>
       <c r="O106" s="2"/>
     </row>
-    <row r="107" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>484</v>
       </c>
@@ -20714,7 +20930,7 @@
       </c>
       <c r="O107" s="2"/>
     </row>
-    <row r="108" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>488</v>
       </c>
@@ -20763,7 +20979,7 @@
       </c>
       <c r="O108" s="2"/>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>492</v>
       </c>
@@ -20812,7 +21028,7 @@
       </c>
       <c r="O109" s="2"/>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>496</v>
       </c>
@@ -20861,7 +21077,7 @@
       </c>
       <c r="O110" s="2"/>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>500</v>
       </c>
@@ -20910,7 +21126,7 @@
       </c>
       <c r="O111" s="2"/>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>504</v>
       </c>
@@ -20959,7 +21175,7 @@
       </c>
       <c r="O112" s="2"/>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>508</v>
       </c>
@@ -21008,7 +21224,7 @@
       </c>
       <c r="O113" s="2"/>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>513</v>
       </c>
@@ -21057,7 +21273,7 @@
       </c>
       <c r="O114" s="2"/>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>517</v>
       </c>
@@ -21106,7 +21322,7 @@
       </c>
       <c r="O115" s="2"/>
     </row>
-    <row r="116" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>522</v>
       </c>
@@ -21155,7 +21371,7 @@
       </c>
       <c r="O116" s="2"/>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>527</v>
       </c>
@@ -21204,7 +21420,7 @@
       </c>
       <c r="O117" s="2"/>
     </row>
-    <row r="118" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>531</v>
       </c>
@@ -21253,7 +21469,7 @@
       </c>
       <c r="O118" s="2"/>
     </row>
-    <row r="119" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>535</v>
       </c>
@@ -21302,7 +21518,7 @@
       </c>
       <c r="O119" s="2"/>
     </row>
-    <row r="120" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>539</v>
       </c>
@@ -21351,7 +21567,7 @@
       </c>
       <c r="O120" s="2"/>
     </row>
-    <row r="121" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>543</v>
       </c>
@@ -21400,7 +21616,7 @@
       </c>
       <c r="O121" s="2"/>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>547</v>
       </c>
@@ -21449,7 +21665,7 @@
       </c>
       <c r="O122" s="2"/>
     </row>
-    <row r="123" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>551</v>
       </c>
@@ -21498,7 +21714,7 @@
       </c>
       <c r="O123" s="2"/>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>555</v>
       </c>
@@ -21547,7 +21763,7 @@
       </c>
       <c r="O124" s="2"/>
     </row>
-    <row r="125" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>559</v>
       </c>
@@ -21596,7 +21812,7 @@
       </c>
       <c r="O125" s="2"/>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>563</v>
       </c>
@@ -21645,7 +21861,7 @@
       </c>
       <c r="O126" s="2"/>
     </row>
-    <row r="127" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>567</v>
       </c>
@@ -21694,7 +21910,7 @@
       </c>
       <c r="O127" s="2"/>
     </row>
-    <row r="128" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>571</v>
       </c>
@@ -21743,7 +21959,7 @@
       </c>
       <c r="O128" s="2"/>
     </row>
-    <row r="129" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>575</v>
       </c>
@@ -21792,7 +22008,7 @@
       </c>
       <c r="O129" s="2"/>
     </row>
-    <row r="130" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>579</v>
       </c>
@@ -21841,7 +22057,7 @@
       </c>
       <c r="O130" s="2"/>
     </row>
-    <row r="131" spans="1:15" ht="60" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>583</v>
       </c>
@@ -21890,7 +22106,7 @@
       </c>
       <c r="O131" s="2"/>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>587</v>
       </c>
@@ -21939,7 +22155,7 @@
       </c>
       <c r="O132" s="2"/>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>592</v>
       </c>
@@ -21988,7 +22204,7 @@
       </c>
       <c r="O133" s="2"/>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>596</v>
       </c>
@@ -22037,7 +22253,7 @@
       </c>
       <c r="O134" s="2"/>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>600</v>
       </c>
@@ -22086,7 +22302,7 @@
       </c>
       <c r="O135" s="2"/>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>604</v>
       </c>
@@ -22135,7 +22351,7 @@
       </c>
       <c r="O136" s="2"/>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>608</v>
       </c>
@@ -22184,7 +22400,7 @@
       </c>
       <c r="O137" s="2"/>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>612</v>
       </c>
@@ -22233,7 +22449,7 @@
       </c>
       <c r="O138" s="2"/>
     </row>
-    <row r="139" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>616</v>
       </c>
@@ -22282,7 +22498,7 @@
       </c>
       <c r="O139" s="2"/>
     </row>
-    <row r="140" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>620</v>
       </c>
@@ -22331,7 +22547,7 @@
       </c>
       <c r="O140" s="2"/>
     </row>
-    <row r="141" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>624</v>
       </c>
@@ -22380,7 +22596,7 @@
       </c>
       <c r="O141" s="2"/>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>628</v>
       </c>
@@ -22429,7 +22645,7 @@
       </c>
       <c r="O142" s="2"/>
     </row>
-    <row r="143" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>632</v>
       </c>
@@ -22478,7 +22694,7 @@
       </c>
       <c r="O143" s="2"/>
     </row>
-    <row r="144" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>636</v>
       </c>
@@ -22527,7 +22743,7 @@
       </c>
       <c r="O144" s="2"/>
     </row>
-    <row r="145" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>641</v>
       </c>
@@ -22576,7 +22792,7 @@
       </c>
       <c r="O145" s="2"/>
     </row>
-    <row r="146" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>646</v>
       </c>
@@ -22625,7 +22841,7 @@
       </c>
       <c r="O146" s="2"/>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>650</v>
       </c>
@@ -22674,7 +22890,7 @@
       </c>
       <c r="O147" s="2"/>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>654</v>
       </c>
@@ -22723,7 +22939,7 @@
       </c>
       <c r="O148" s="2"/>
     </row>
-    <row r="149" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>658</v>
       </c>
@@ -22772,7 +22988,7 @@
       </c>
       <c r="O149" s="2"/>
     </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>662</v>
       </c>
@@ -22821,7 +23037,7 @@
       </c>
       <c r="O150" s="2"/>
     </row>
-    <row r="151" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>666</v>
       </c>
@@ -22870,7 +23086,7 @@
       </c>
       <c r="O151" s="2"/>
     </row>
-    <row r="152" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>670</v>
       </c>
@@ -22919,7 +23135,7 @@
       </c>
       <c r="O152" s="2"/>
     </row>
-    <row r="153" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>674</v>
       </c>
@@ -22968,7 +23184,7 @@
       </c>
       <c r="O153" s="2"/>
     </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>678</v>
       </c>
@@ -23017,7 +23233,7 @@
       </c>
       <c r="O154" s="2"/>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>682</v>
       </c>
@@ -23066,7 +23282,7 @@
       </c>
       <c r="O155" s="2"/>
     </row>
-    <row r="156" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>686</v>
       </c>
@@ -23115,7 +23331,7 @@
       </c>
       <c r="O156" s="2"/>
     </row>
-    <row r="157" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>690</v>
       </c>
@@ -23164,7 +23380,7 @@
       </c>
       <c r="O157" s="2"/>
     </row>
-    <row r="158" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>694</v>
       </c>
@@ -23213,7 +23429,7 @@
       </c>
       <c r="O158" s="2"/>
     </row>
-    <row r="159" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>698</v>
       </c>
@@ -23262,7 +23478,7 @@
       </c>
       <c r="O159" s="2"/>
     </row>
-    <row r="160" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>702</v>
       </c>
@@ -23311,7 +23527,7 @@
       </c>
       <c r="O160" s="2"/>
     </row>
-    <row r="161" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>707</v>
       </c>
@@ -23360,7 +23576,7 @@
       </c>
       <c r="O161" s="2"/>
     </row>
-    <row r="162" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>711</v>
       </c>
@@ -23409,7 +23625,7 @@
       </c>
       <c r="O162" s="2"/>
     </row>
-    <row r="163" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>715</v>
       </c>
@@ -23458,7 +23674,7 @@
       </c>
       <c r="O163" s="2"/>
     </row>
-    <row r="164" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>720</v>
       </c>
@@ -23507,7 +23723,7 @@
       </c>
       <c r="O164" s="2"/>
     </row>
-    <row r="165" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>724</v>
       </c>
@@ -23556,7 +23772,7 @@
       </c>
       <c r="O165" s="2"/>
     </row>
-    <row r="166" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>728</v>
       </c>
@@ -23605,7 +23821,7 @@
       </c>
       <c r="O166" s="2"/>
     </row>
-    <row r="167" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>732</v>
       </c>
@@ -23654,7 +23870,7 @@
       </c>
       <c r="O167" s="2"/>
     </row>
-    <row r="168" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>736</v>
       </c>
@@ -23703,7 +23919,7 @@
       </c>
       <c r="O168" s="2"/>
     </row>
-    <row r="169" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>741</v>
       </c>
@@ -23752,7 +23968,7 @@
       </c>
       <c r="O169" s="2"/>
     </row>
-    <row r="170" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>745</v>
       </c>
@@ -23801,7 +24017,7 @@
       </c>
       <c r="O170" s="2"/>
     </row>
-    <row r="171" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>750</v>
       </c>
@@ -23850,7 +24066,7 @@
       </c>
       <c r="O171" s="2"/>
     </row>
-    <row r="172" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>754</v>
       </c>
@@ -23899,7 +24115,7 @@
       </c>
       <c r="O172" s="2"/>
     </row>
-    <row r="173" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>758</v>
       </c>
@@ -23948,7 +24164,7 @@
       </c>
       <c r="O173" s="2"/>
     </row>
-    <row r="174" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>762</v>
       </c>
@@ -24046,7 +24262,7 @@
       </c>
       <c r="O175" s="2"/>
     </row>
-    <row r="176" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>773</v>
       </c>
@@ -24095,7 +24311,7 @@
       </c>
       <c r="O176" s="2"/>
     </row>
-    <row r="177" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>777</v>
       </c>
@@ -24144,7 +24360,7 @@
       </c>
       <c r="O177" s="2"/>
     </row>
-    <row r="178" spans="1:15" ht="60" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>781</v>
       </c>
@@ -24193,7 +24409,7 @@
       </c>
       <c r="O178" s="2"/>
     </row>
-    <row r="179" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>786</v>
       </c>
@@ -24242,7 +24458,7 @@
       </c>
       <c r="O179" s="2"/>
     </row>
-    <row r="180" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>790</v>
       </c>
@@ -24291,7 +24507,7 @@
       </c>
       <c r="O180" s="2"/>
     </row>
-    <row r="181" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>794</v>
       </c>
@@ -24340,7 +24556,7 @@
       </c>
       <c r="O181" s="2"/>
     </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>799</v>
       </c>
@@ -24389,7 +24605,7 @@
       </c>
       <c r="O182" s="2"/>
     </row>
-    <row r="183" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>803</v>
       </c>
@@ -24438,7 +24654,7 @@
       </c>
       <c r="O183" s="2"/>
     </row>
-    <row r="184" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
         <v>807</v>
       </c>
@@ -24487,7 +24703,7 @@
       </c>
       <c r="O184" s="2"/>
     </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>940</v>
       </c>
@@ -24517,23 +24733,23 @@
       </c>
       <c r="J185" s="2" t="str">
         <f>IFERROR(INDEX('Database Verification'!$N:$N,MATCH($I185,'Database Verification'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
-      </c>
-      <c r="K185" s="7">
+        <v>Pass</v>
+      </c>
+      <c r="K185" s="7" t="str">
         <f>IFERROR(INDEX('Database Verification'!$J:$J,MATCH($I185,'Database Verification'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>2026-10-28</v>
       </c>
       <c r="L185" s="2"/>
-      <c r="M185" s="2">
+      <c r="M185" s="2" t="str">
         <f>IFERROR(INDEX('Database Verification'!$O:$O,MATCH($I185,'Database Verification'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P0B-DB-001; package 0d30359ab5cdd4aa3577c33823de1bbc80a3d4f2; spec/meals/Phase 0B Recipe Persistence Design.md section 28; meals-db-final-manifest.json SHA256 4cbbc3eac24c13860d39ee3a0d8c6ae79c638cc5967d5274d1e7ea219091f8da; complete evidence in session b7458d86-6190-4718-8779-7c2b79a30630/files</v>
       </c>
       <c r="N185" s="2" t="s">
         <v>1075</v>
       </c>
       <c r="O185" s="2"/>
     </row>
-    <row r="186" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>944</v>
       </c>
@@ -24563,23 +24779,23 @@
       </c>
       <c r="J186" s="2" t="str">
         <f>IFERROR(INDEX('Database Verification'!$N:$N,MATCH($I186,'Database Verification'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
-      </c>
-      <c r="K186" s="7">
+        <v>Pass</v>
+      </c>
+      <c r="K186" s="7" t="str">
         <f>IFERROR(INDEX('Database Verification'!$J:$J,MATCH($I186,'Database Verification'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>2026-10-28</v>
       </c>
       <c r="L186" s="2"/>
-      <c r="M186" s="2">
+      <c r="M186" s="2" t="str">
         <f>IFERROR(INDEX('Database Verification'!$O:$O,MATCH($I186,'Database Verification'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P0B-DB-001; package 0d30359ab5cdd4aa3577c33823de1bbc80a3d4f2; spec/meals/Phase 0B Recipe Persistence Design.md section 28; meals-db-final-manifest.json SHA256 4cbbc3eac24c13860d39ee3a0d8c6ae79c638cc5967d5274d1e7ea219091f8da; complete evidence in session b7458d86-6190-4718-8779-7c2b79a30630/files</v>
       </c>
       <c r="N186" s="2" t="s">
         <v>1075</v>
       </c>
       <c r="O186" s="2"/>
     </row>
-    <row r="187" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>947</v>
       </c>
@@ -24609,23 +24825,23 @@
       </c>
       <c r="J187" s="2" t="str">
         <f>IFERROR(INDEX('Database Verification'!$N:$N,MATCH($I187,'Database Verification'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
-      </c>
-      <c r="K187" s="7">
+        <v>Pass</v>
+      </c>
+      <c r="K187" s="7" t="str">
         <f>IFERROR(INDEX('Database Verification'!$J:$J,MATCH($I187,'Database Verification'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>2026-10-28</v>
       </c>
       <c r="L187" s="2"/>
-      <c r="M187" s="2">
+      <c r="M187" s="2" t="str">
         <f>IFERROR(INDEX('Database Verification'!$O:$O,MATCH($I187,'Database Verification'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P0B-DB-001; package 0d30359ab5cdd4aa3577c33823de1bbc80a3d4f2; spec/meals/Phase 0B Recipe Persistence Design.md section 28; meals-db-final-manifest.json SHA256 4cbbc3eac24c13860d39ee3a0d8c6ae79c638cc5967d5274d1e7ea219091f8da; complete evidence in session b7458d86-6190-4718-8779-7c2b79a30630/files</v>
       </c>
       <c r="N187" s="2" t="s">
         <v>1075</v>
       </c>
       <c r="O187" s="2"/>
     </row>
-    <row r="188" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>950</v>
       </c>
@@ -24655,23 +24871,23 @@
       </c>
       <c r="J188" s="2" t="str">
         <f>IFERROR(INDEX('Database Verification'!$N:$N,MATCH($I188,'Database Verification'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
-      </c>
-      <c r="K188" s="7">
+        <v>Pass</v>
+      </c>
+      <c r="K188" s="7" t="str">
         <f>IFERROR(INDEX('Database Verification'!$J:$J,MATCH($I188,'Database Verification'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>2026-10-28</v>
       </c>
       <c r="L188" s="2"/>
-      <c r="M188" s="2">
+      <c r="M188" s="2" t="str">
         <f>IFERROR(INDEX('Database Verification'!$O:$O,MATCH($I188,'Database Verification'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P0B-DB-001; package 0d30359ab5cdd4aa3577c33823de1bbc80a3d4f2; spec/meals/Phase 0B Recipe Persistence Design.md section 28; meals-db-final-manifest.json SHA256 4cbbc3eac24c13860d39ee3a0d8c6ae79c638cc5967d5274d1e7ea219091f8da; complete evidence in session b7458d86-6190-4718-8779-7c2b79a30630/files</v>
       </c>
       <c r="N188" s="2" t="s">
         <v>1075</v>
       </c>
       <c r="O188" s="2"/>
     </row>
-    <row r="189" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>953</v>
       </c>
@@ -24717,7 +24933,7 @@
       </c>
       <c r="O189" s="2"/>
     </row>
-    <row r="190" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>956</v>
       </c>
@@ -24747,23 +24963,23 @@
       </c>
       <c r="J190" s="2" t="str">
         <f>IFERROR(INDEX('Database Verification'!$N:$N,MATCH($I190,'Database Verification'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
-      </c>
-      <c r="K190" s="7">
+        <v>Pass</v>
+      </c>
+      <c r="K190" s="7" t="str">
         <f>IFERROR(INDEX('Database Verification'!$J:$J,MATCH($I190,'Database Verification'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>2026-10-28</v>
       </c>
       <c r="L190" s="2"/>
-      <c r="M190" s="2">
+      <c r="M190" s="2" t="str">
         <f>IFERROR(INDEX('Database Verification'!$O:$O,MATCH($I190,'Database Verification'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P0B-DB-001; package 0d30359ab5cdd4aa3577c33823de1bbc80a3d4f2; spec/meals/Phase 0B Recipe Persistence Design.md section 28; meals-db-final-manifest.json SHA256 4cbbc3eac24c13860d39ee3a0d8c6ae79c638cc5967d5274d1e7ea219091f8da; complete evidence in session b7458d86-6190-4718-8779-7c2b79a30630/files</v>
       </c>
       <c r="N190" s="2" t="s">
         <v>1075</v>
       </c>
       <c r="O190" s="2"/>
     </row>
-    <row r="191" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>959</v>
       </c>
@@ -24793,23 +25009,23 @@
       </c>
       <c r="J191" s="2" t="str">
         <f>IFERROR(INDEX('Database Verification'!$N:$N,MATCH($I191,'Database Verification'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
-      </c>
-      <c r="K191" s="7">
+        <v>Pass</v>
+      </c>
+      <c r="K191" s="7" t="str">
         <f>IFERROR(INDEX('Database Verification'!$J:$J,MATCH($I191,'Database Verification'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>2026-10-28</v>
       </c>
       <c r="L191" s="2"/>
-      <c r="M191" s="2">
+      <c r="M191" s="2" t="str">
         <f>IFERROR(INDEX('Database Verification'!$O:$O,MATCH($I191,'Database Verification'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P0B-DB-001; package 0d30359ab5cdd4aa3577c33823de1bbc80a3d4f2; spec/meals/Phase 0B Recipe Persistence Design.md section 28; meals-db-final-manifest.json SHA256 4cbbc3eac24c13860d39ee3a0d8c6ae79c638cc5967d5274d1e7ea219091f8da; complete evidence in session b7458d86-6190-4718-8779-7c2b79a30630/files</v>
       </c>
       <c r="N191" s="2" t="s">
         <v>1075</v>
       </c>
       <c r="O191" s="2"/>
     </row>
-    <row r="192" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>962</v>
       </c>
@@ -24855,7 +25071,7 @@
       </c>
       <c r="O192" s="2"/>
     </row>
-    <row r="193" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>965</v>
       </c>
@@ -24901,7 +25117,7 @@
       </c>
       <c r="O193" s="2"/>
     </row>
-    <row r="194" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>968</v>
       </c>
@@ -24947,7 +25163,7 @@
       </c>
       <c r="O194" s="2"/>
     </row>
-    <row r="195" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>971</v>
       </c>
@@ -24977,23 +25193,23 @@
       </c>
       <c r="J195" s="2" t="str">
         <f>IFERROR(INDEX('Database Verification'!$N:$N,MATCH($I195,'Database Verification'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
-      </c>
-      <c r="K195" s="7">
+        <v>Pass</v>
+      </c>
+      <c r="K195" s="7" t="str">
         <f>IFERROR(INDEX('Database Verification'!$J:$J,MATCH($I195,'Database Verification'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>2026-10-28</v>
       </c>
       <c r="L195" s="2"/>
-      <c r="M195" s="2">
+      <c r="M195" s="2" t="str">
         <f>IFERROR(INDEX('Database Verification'!$O:$O,MATCH($I195,'Database Verification'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P0B-DB-001; package 0d30359ab5cdd4aa3577c33823de1bbc80a3d4f2; spec/meals/Phase 0B Recipe Persistence Design.md section 28; meals-db-final-manifest.json SHA256 4cbbc3eac24c13860d39ee3a0d8c6ae79c638cc5967d5274d1e7ea219091f8da; complete evidence in session b7458d86-6190-4718-8779-7c2b79a30630/files</v>
       </c>
       <c r="N195" s="2" t="s">
         <v>1075</v>
       </c>
       <c r="O195" s="2"/>
     </row>
-    <row r="196" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>974</v>
       </c>
@@ -25023,23 +25239,23 @@
       </c>
       <c r="J196" s="2" t="str">
         <f>IFERROR(INDEX('Database Verification'!$N:$N,MATCH($I196,'Database Verification'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
-      </c>
-      <c r="K196" s="7">
+        <v>Pass</v>
+      </c>
+      <c r="K196" s="7" t="str">
         <f>IFERROR(INDEX('Database Verification'!$J:$J,MATCH($I196,'Database Verification'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>2026-10-28</v>
       </c>
       <c r="L196" s="2"/>
-      <c r="M196" s="2">
+      <c r="M196" s="2" t="str">
         <f>IFERROR(INDEX('Database Verification'!$O:$O,MATCH($I196,'Database Verification'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P0B-DB-001; package 0d30359ab5cdd4aa3577c33823de1bbc80a3d4f2; spec/meals/Phase 0B Recipe Persistence Design.md section 28; meals-db-final-manifest.json SHA256 4cbbc3eac24c13860d39ee3a0d8c6ae79c638cc5967d5274d1e7ea219091f8da; complete evidence in session b7458d86-6190-4718-8779-7c2b79a30630/files</v>
       </c>
       <c r="N196" s="2" t="s">
         <v>1075</v>
       </c>
       <c r="O196" s="2"/>
     </row>
-    <row r="197" spans="1:15" ht="60" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>977</v>
       </c>
@@ -25069,23 +25285,23 @@
       </c>
       <c r="J197" s="2" t="str">
         <f>IFERROR(INDEX('Database Verification'!$N:$N,MATCH($I197,'Database Verification'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
-      </c>
-      <c r="K197" s="7">
+        <v>Pass</v>
+      </c>
+      <c r="K197" s="7" t="str">
         <f>IFERROR(INDEX('Database Verification'!$J:$J,MATCH($I197,'Database Verification'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>2026-10-28</v>
       </c>
       <c r="L197" s="2"/>
-      <c r="M197" s="2">
+      <c r="M197" s="2" t="str">
         <f>IFERROR(INDEX('Database Verification'!$O:$O,MATCH($I197,'Database Verification'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P0B-DB-001; package 0d30359ab5cdd4aa3577c33823de1bbc80a3d4f2; spec/meals/Phase 0B Recipe Persistence Design.md section 28; meals-db-final-manifest.json SHA256 4cbbc3eac24c13860d39ee3a0d8c6ae79c638cc5967d5274d1e7ea219091f8da; complete evidence in session b7458d86-6190-4718-8779-7c2b79a30630/files</v>
       </c>
       <c r="N197" s="2" t="s">
         <v>1075</v>
       </c>
       <c r="O197" s="2"/>
     </row>
-    <row r="198" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>870</v>
       </c>
@@ -25134,7 +25350,7 @@
       </c>
       <c r="O198" s="2"/>
     </row>
-    <row r="199" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>877</v>
       </c>
@@ -25183,7 +25399,7 @@
       </c>
       <c r="O199" s="2"/>
     </row>
-    <row r="200" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>881</v>
       </c>
@@ -25232,7 +25448,7 @@
       </c>
       <c r="O200" s="2"/>
     </row>
-    <row r="201" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
         <v>885</v>
       </c>
@@ -25281,7 +25497,7 @@
       </c>
       <c r="O201" s="2"/>
     </row>
-    <row r="202" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>889</v>
       </c>
@@ -25379,7 +25595,7 @@
       </c>
       <c r="O203" s="2"/>
     </row>
-    <row r="204" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>897</v>
       </c>
@@ -25428,7 +25644,7 @@
       </c>
       <c r="O204" s="2"/>
     </row>
-    <row r="205" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>901</v>
       </c>
@@ -25458,19 +25674,19 @@
       </c>
       <c r="J205" s="2" t="str">
         <f>IFERROR(INDEX('Security Acceptance'!$N:$N,MATCH($I205,'Security Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
-      </c>
-      <c r="K205" s="7">
+        <v>Pass</v>
+      </c>
+      <c r="K205" s="7" t="str">
         <f>IFERROR(INDEX('Security Acceptance'!$O:$O,MATCH($I205,'Security Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>2026-10-28</v>
       </c>
       <c r="L205" s="2">
         <f>IFERROR(INDEX('Security Acceptance'!$P:$P,MATCH($I205,'Security Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M205" s="2">
+      <c r="M205" s="2" t="str">
         <f>IFERROR(INDEX('Security Acceptance'!$Q:$Q,MATCH($I205,'Security Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P0B-DB-001; package 0d30359ab5cdd4aa3577c33823de1bbc80a3d4f2; spec/meals/Phase 0B Recipe Persistence Design.md section 28; meals-db-final-manifest.json SHA256 4cbbc3eac24c13860d39ee3a0d8c6ae79c638cc5967d5274d1e7ea219091f8da; complete evidence in session b7458d86-6190-4718-8779-7c2b79a30630/files</v>
       </c>
       <c r="N205" s="2" t="s">
         <v>1075</v>
@@ -25526,7 +25742,7 @@
       </c>
       <c r="O206" s="2"/>
     </row>
-    <row r="207" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>909</v>
       </c>
@@ -25575,7 +25791,7 @@
       </c>
       <c r="O207" s="2"/>
     </row>
-    <row r="208" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>1088</v>
       </c>
@@ -25612,7 +25828,7 @@
       </c>
       <c r="O208" s="2"/>
     </row>
-    <row r="209" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>1091</v>
       </c>
@@ -25649,7 +25865,7 @@
       </c>
       <c r="O209" s="2"/>
     </row>
-    <row r="210" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>1093</v>
       </c>
@@ -25686,7 +25902,7 @@
       </c>
       <c r="O210" s="2"/>
     </row>
-    <row r="211" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>1095</v>
       </c>
@@ -25723,7 +25939,7 @@
       </c>
       <c r="O211" s="2"/>
     </row>
-    <row r="212" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>1097</v>
       </c>
@@ -25760,7 +25976,7 @@
       </c>
       <c r="O212" s="2"/>
     </row>
-    <row r="213" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>1099</v>
       </c>
@@ -25797,7 +26013,7 @@
       </c>
       <c r="O213" s="2"/>
     </row>
-    <row r="214" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>1102</v>
       </c>
@@ -25834,7 +26050,7 @@
       </c>
       <c r="O214" s="2"/>
     </row>
-    <row r="215" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>1104</v>
       </c>
@@ -25871,7 +26087,7 @@
       </c>
       <c r="O215" s="2"/>
     </row>
-    <row r="216" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>1106</v>
       </c>
@@ -25908,7 +26124,7 @@
       </c>
       <c r="O216" s="2"/>
     </row>
-    <row r="217" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>1108</v>
       </c>
@@ -25945,7 +26161,7 @@
       </c>
       <c r="O217" s="2"/>
     </row>
-    <row r="218" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>133</v>
       </c>
@@ -25994,7 +26210,7 @@
       </c>
       <c r="O218" s="2"/>
     </row>
-    <row r="219" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>186</v>
       </c>
@@ -26043,7 +26259,7 @@
       </c>
       <c r="O219" s="2"/>
     </row>
-    <row r="220" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>246</v>
       </c>
@@ -26092,7 +26308,7 @@
       </c>
       <c r="O220" s="2"/>
     </row>
-    <row r="221" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>363</v>
       </c>
@@ -26190,7 +26406,7 @@
       </c>
       <c r="O222" s="2"/>
     </row>
-    <row r="223" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>794</v>
       </c>

--- a/spec/meals/Meals Acceptance Checklist v1.0.xlsx
+++ b/spec/meals/Meals Acceptance Checklist v1.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wcoop\Documents\HomeMaintenanceApp\spec\meals\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02963D1F-5BC3-40A9-A86C-51F6B2392F42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91417126-1D94-4337-8CEA-D4028A336DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5134" uniqueCount="1155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5376" uniqueCount="1161">
   <si>
     <t>Meals Acceptance Checklist</t>
   </si>
@@ -3621,6 +3621,24 @@
   </si>
   <si>
     <t>P0B-DB-001 Recipe foundation scope only. Captured production catalog and synthetic SQL SET ROLE/claim evidence, not live JWT/API authentication, owner application UAT or Recipe UI evidence. Future Meals objects require their own verification. No deployment blocker observed; blocker classification field is unchanged. Reversal prepared, not executed; test-only transaction rollback is not migration reversal. Production postflight effective_anon_denial/explicit_table_acl/function_acl/column_acl passed.</t>
+  </si>
+  <si>
+    <t>Local Recipe Core implementation and technical checks complete. Isolated browser/handler/PGlite evidence only; not live owner JWT/API or owner UAT. Await authorized deployment and independent owner desktop/mobile verification. Phase 2/3 actions remain unavailable.</t>
+  </si>
+  <si>
+    <t>P1-TECH-001</t>
+  </si>
+  <si>
+    <t>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</t>
+  </si>
+  <si>
+    <t>Prepared with deterministic run-prefixed IDs and Recipe-before-lookup cleanup in spec/meals/README.md. Local synthetic flow exercised and fixture counts returned to zero. Live owner E2E/UAT remains unexecuted pending authorized deployment. No Shopping/Planner data created.</t>
+  </si>
+  <si>
+    <t>Recipe UI/service ready for post-release owner/API checks. Local source/build, isolated synthetic browser and exact-migration PGlite role tests passed. These do not prove live JWT/PostgREST authorization; composite application/API verification is not marked Pass. Prior production P0B evidence is unchanged.</t>
+  </si>
+  <si>
+    <t>Executed local source/build inspection and unchanged-migration PGlite catalog tests: direct table service, no application-callable Recipe RPC/function and no SECURITY DEFINER introduced. Existing internal trigger remains invoker and not browser-callable. Local technical scope only, not owner application/API authentication proof.</t>
   </si>
 </sst>
 </file>
@@ -4881,11 +4899,11 @@
       </c>
       <c r="G7" s="5">
         <f>COUNTIF('Functional Acceptance'!$L:$L,"Ready to Test")</f>
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="H7" s="5">
         <f>COUNTIF('Functional Acceptance'!$L:$L,"Not Built")</f>
-        <v>166</v>
+        <v>98</v>
       </c>
       <c r="I7" s="5">
         <f>COUNTIF('Functional Acceptance'!$L:$L,"Deferred")</f>
@@ -4918,11 +4936,11 @@
       </c>
       <c r="G8" s="5">
         <f>COUNTIF('End-to-End Tests'!$J:$J,"Ready to Test")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H8" s="5">
         <f>COUNTIF('End-to-End Tests'!$J:$J,"Not Built")</f>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I8" s="5">
         <f>COUNTIF('End-to-End Tests'!$J:$J,"Deferred")</f>
@@ -4939,7 +4957,7 @@
       </c>
       <c r="C9" s="5">
         <f>COUNTIF('Security Acceptance'!$N:$N,"Pass")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" s="5">
         <f>COUNTIF('Security Acceptance'!$N:$N,"Pass with Known Issue")</f>
@@ -4955,11 +4973,11 @@
       </c>
       <c r="G9" s="5">
         <f>COUNTIF('Security Acceptance'!$N:$N,"Ready to Test")</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H9" s="5">
         <f>COUNTIF('Security Acceptance'!$N:$N,"Not Built")</f>
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I9" s="5">
         <f>COUNTIF('Security Acceptance'!$N:$N,"Deferred")</f>
@@ -5212,7 +5230,7 @@
       </c>
       <c r="E23" s="2">
         <f>COUNTIFS('Functional Acceptance'!D:D,A23,'Functional Acceptance'!L:L,"Pass")+COUNTIFS('Security Acceptance'!D:D,A23,'Security Acceptance'!N:N,"Pass")+COUNTIFS('Database Verification'!D:D,A23,'Database Verification'!N:N,"Pass")+COUNTIFS('End-to-End Tests'!C:C,A23,'End-to-End Tests'!J:J,"Pass")</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F23" s="2">
         <f>COUNTIFS('Functional Acceptance'!D:D,A23,'Functional Acceptance'!L:L,"Pass with Known Issue")+COUNTIFS('Security Acceptance'!D:D,A23,'Security Acceptance'!N:N,"Pass with Known Issue")+COUNTIFS('Database Verification'!D:D,A23,'Database Verification'!N:N,"Pass with Known Issue")+COUNTIFS('End-to-End Tests'!C:C,A23,'End-to-End Tests'!J:J,"Pass with Known Issue")</f>
@@ -5758,7 +5776,9 @@
       </c>
     </row>
     <row r="6" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
+      <c r="A6" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B6" s="2" t="s">
         <v>116</v>
       </c>
@@ -5790,15 +5810,21 @@
         <v>119</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M6" s="7"/>
       <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2"/>
+      <c r="O6" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="7" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
+      <c r="A7" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B7" s="2" t="s">
         <v>120</v>
       </c>
@@ -5830,12 +5856,16 @@
         <v>123</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M7" s="7"/>
       <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
+      <c r="O7" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="8" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
@@ -5926,7 +5956,9 @@
       </c>
     </row>
     <row r="10" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
+      <c r="A10" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B10" s="2" t="s">
         <v>132</v>
       </c>
@@ -5958,15 +5990,21 @@
         <v>139</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M10" s="7"/>
       <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
+      <c r="O10" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="11" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
+      <c r="A11" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B11" s="2" t="s">
         <v>140</v>
       </c>
@@ -5998,15 +6036,21 @@
         <v>139</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M11" s="7"/>
       <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
+      <c r="O11" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="12" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
+      <c r="A12" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B12" s="2" t="s">
         <v>143</v>
       </c>
@@ -6038,15 +6082,21 @@
         <v>146</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M12" s="7"/>
       <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2"/>
+      <c r="O12" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="13" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
+      <c r="A13" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B13" s="2" t="s">
         <v>147</v>
       </c>
@@ -6078,15 +6128,21 @@
         <v>150</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M13" s="7"/>
       <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2"/>
+      <c r="O13" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="14" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2"/>
+      <c r="A14" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B14" s="2" t="s">
         <v>151</v>
       </c>
@@ -6118,15 +6174,21 @@
         <v>154</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M14" s="7"/>
       <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2"/>
+      <c r="O14" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="15" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2"/>
+      <c r="A15" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B15" s="2" t="s">
         <v>155</v>
       </c>
@@ -6158,15 +6220,21 @@
         <v>159</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M15" s="7"/>
       <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
-      <c r="P15" s="2"/>
+      <c r="O15" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="16" spans="1:16" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2"/>
+      <c r="A16" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B16" s="2" t="s">
         <v>160</v>
       </c>
@@ -6198,15 +6266,21 @@
         <v>164</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M16" s="7"/>
       <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
-      <c r="P16" s="2"/>
+      <c r="O16" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="17" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
+      <c r="A17" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B17" s="2" t="s">
         <v>165</v>
       </c>
@@ -6238,15 +6312,21 @@
         <v>168</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M17" s="7"/>
       <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
-      <c r="P17" s="2"/>
+      <c r="O17" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="18" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
+      <c r="A18" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B18" s="2" t="s">
         <v>169</v>
       </c>
@@ -6278,15 +6358,21 @@
         <v>172</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M18" s="7"/>
       <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
-      <c r="P18" s="2"/>
+      <c r="O18" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="19" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
+      <c r="A19" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B19" s="2" t="s">
         <v>173</v>
       </c>
@@ -6318,15 +6404,21 @@
         <v>176</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M19" s="7"/>
       <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
-      <c r="P19" s="2"/>
+      <c r="O19" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="20" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
+      <c r="A20" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B20" s="2" t="s">
         <v>177</v>
       </c>
@@ -6358,15 +6450,21 @@
         <v>180</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M20" s="7"/>
       <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
-      <c r="P20" s="2"/>
+      <c r="O20" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="21" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
+      <c r="A21" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B21" s="2" t="s">
         <v>181</v>
       </c>
@@ -6398,15 +6496,21 @@
         <v>184</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M21" s="7"/>
       <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
-      <c r="P21" s="2"/>
+      <c r="O21" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="22" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2"/>
+      <c r="A22" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B22" s="2" t="s">
         <v>185</v>
       </c>
@@ -6438,15 +6542,21 @@
         <v>189</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M22" s="7"/>
       <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
-      <c r="P22" s="2"/>
+      <c r="O22" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="23" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2"/>
+      <c r="A23" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B23" s="2" t="s">
         <v>190</v>
       </c>
@@ -6478,15 +6588,21 @@
         <v>189</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M23" s="7"/>
       <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
-      <c r="P23" s="2"/>
+      <c r="O23" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="24" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2"/>
+      <c r="A24" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B24" s="2" t="s">
         <v>191</v>
       </c>
@@ -6518,15 +6634,21 @@
         <v>194</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M24" s="7"/>
       <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
-      <c r="P24" s="2"/>
+      <c r="O24" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="25" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2"/>
+      <c r="A25" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B25" s="2" t="s">
         <v>195</v>
       </c>
@@ -6558,15 +6680,21 @@
         <v>198</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M25" s="7"/>
       <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
-      <c r="P25" s="2"/>
+      <c r="O25" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="26" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
+      <c r="A26" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B26" s="2" t="s">
         <v>199</v>
       </c>
@@ -6598,12 +6726,16 @@
         <v>202</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M26" s="7"/>
       <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
-      <c r="P26" s="2"/>
+      <c r="O26" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P26" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="27" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
@@ -6726,7 +6858,9 @@
       <c r="P29" s="2"/>
     </row>
     <row r="30" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2"/>
+      <c r="A30" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B30" s="2" t="s">
         <v>215</v>
       </c>
@@ -6758,15 +6892,21 @@
         <v>218</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M30" s="7"/>
       <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
-      <c r="P30" s="2"/>
+      <c r="O30" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="31" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2"/>
+      <c r="A31" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B31" s="2" t="s">
         <v>219</v>
       </c>
@@ -6798,15 +6938,21 @@
         <v>222</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M31" s="7"/>
       <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
-      <c r="P31" s="2"/>
+      <c r="O31" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P31" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="32" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2"/>
+      <c r="A32" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B32" s="2" t="s">
         <v>223</v>
       </c>
@@ -6838,15 +6984,21 @@
         <v>227</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M32" s="7"/>
       <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
-      <c r="P32" s="2"/>
+      <c r="O32" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P32" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="33" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="2"/>
+      <c r="A33" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B33" s="2" t="s">
         <v>228</v>
       </c>
@@ -6878,15 +7030,21 @@
         <v>231</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M33" s="7"/>
       <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
-      <c r="P33" s="2"/>
+      <c r="O33" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P33" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="34" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="2"/>
+      <c r="A34" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B34" s="2" t="s">
         <v>232</v>
       </c>
@@ -6918,15 +7076,21 @@
         <v>236</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M34" s="7"/>
       <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
-      <c r="P34" s="2"/>
+      <c r="O34" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P34" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="35" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="2"/>
+      <c r="A35" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B35" s="2" t="s">
         <v>237</v>
       </c>
@@ -6958,12 +7122,16 @@
         <v>240</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M35" s="7"/>
       <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
-      <c r="P35" s="2"/>
+      <c r="O35" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P35" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="36" spans="1:16" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
@@ -7006,7 +7174,9 @@
       <c r="P36" s="2"/>
     </row>
     <row r="37" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="2"/>
+      <c r="A37" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B37" s="2" t="s">
         <v>245</v>
       </c>
@@ -7038,15 +7208,21 @@
         <v>249</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M37" s="7"/>
       <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
-      <c r="P37" s="2"/>
+      <c r="O37" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P37" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="38" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="2"/>
+      <c r="A38" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B38" s="2" t="s">
         <v>250</v>
       </c>
@@ -7078,15 +7254,21 @@
         <v>249</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M38" s="7"/>
       <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
-      <c r="P38" s="2"/>
+      <c r="O38" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P38" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="39" spans="1:16" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="2"/>
+      <c r="A39" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B39" s="2" t="s">
         <v>251</v>
       </c>
@@ -7118,15 +7300,21 @@
         <v>254</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M39" s="7"/>
       <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
-      <c r="P39" s="2"/>
+      <c r="O39" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P39" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="40" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="2"/>
+      <c r="A40" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B40" s="2" t="s">
         <v>255</v>
       </c>
@@ -7158,15 +7346,21 @@
         <v>258</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M40" s="7"/>
       <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
-      <c r="P40" s="2"/>
+      <c r="O40" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P40" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="41" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="2"/>
+      <c r="A41" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B41" s="2" t="s">
         <v>259</v>
       </c>
@@ -7198,12 +7392,16 @@
         <v>262</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M41" s="7"/>
       <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
-      <c r="P41" s="2"/>
+      <c r="O41" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P41" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="42" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
@@ -7286,7 +7484,9 @@
       <c r="P43" s="2"/>
     </row>
     <row r="44" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="2"/>
+      <c r="A44" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B44" s="2" t="s">
         <v>271</v>
       </c>
@@ -7318,15 +7518,21 @@
         <v>274</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M44" s="7"/>
       <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
-      <c r="P44" s="2"/>
+      <c r="O44" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P44" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="45" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="2"/>
+      <c r="A45" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B45" s="2" t="s">
         <v>275</v>
       </c>
@@ -7358,15 +7564,21 @@
         <v>278</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M45" s="7"/>
       <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
-      <c r="P45" s="2"/>
+      <c r="O45" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P45" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="46" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="2"/>
+      <c r="A46" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B46" s="2" t="s">
         <v>279</v>
       </c>
@@ -7398,15 +7610,21 @@
         <v>282</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M46" s="7"/>
       <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
-      <c r="P46" s="2"/>
+      <c r="O46" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P46" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="47" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="2"/>
+      <c r="A47" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B47" s="2" t="s">
         <v>283</v>
       </c>
@@ -7438,12 +7656,16 @@
         <v>286</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M47" s="7"/>
       <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
-      <c r="P47" s="2"/>
+      <c r="O47" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P47" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="48" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
@@ -7526,7 +7748,9 @@
       <c r="P49" s="2"/>
     </row>
     <row r="50" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="2"/>
+      <c r="A50" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B50" s="2" t="s">
         <v>295</v>
       </c>
@@ -7558,15 +7782,21 @@
         <v>299</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M50" s="7"/>
       <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
-      <c r="P50" s="2"/>
+      <c r="O50" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P50" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="51" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="2"/>
+      <c r="A51" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B51" s="2" t="s">
         <v>300</v>
       </c>
@@ -7598,15 +7828,21 @@
         <v>304</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M51" s="7"/>
       <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
-      <c r="P51" s="2"/>
+      <c r="O51" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P51" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="52" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="2"/>
+      <c r="A52" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B52" s="2" t="s">
         <v>305</v>
       </c>
@@ -7638,15 +7874,21 @@
         <v>308</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M52" s="7"/>
       <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
-      <c r="P52" s="2"/>
+      <c r="O52" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P52" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="53" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="2"/>
+      <c r="A53" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B53" s="2" t="s">
         <v>309</v>
       </c>
@@ -7678,15 +7920,21 @@
         <v>312</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M53" s="7"/>
       <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
-      <c r="P53" s="2"/>
+      <c r="O53" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P53" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="54" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="2"/>
+      <c r="A54" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B54" s="2" t="s">
         <v>313</v>
       </c>
@@ -7718,15 +7966,21 @@
         <v>316</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M54" s="7"/>
       <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
-      <c r="P54" s="2"/>
+      <c r="O54" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P54" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="55" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="2"/>
+      <c r="A55" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B55" s="2" t="s">
         <v>317</v>
       </c>
@@ -7758,15 +8012,21 @@
         <v>320</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M55" s="7"/>
       <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
-      <c r="P55" s="2"/>
+      <c r="O55" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P55" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="56" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="2"/>
+      <c r="A56" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B56" s="2" t="s">
         <v>321</v>
       </c>
@@ -7798,15 +8058,21 @@
         <v>324</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M56" s="7"/>
       <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
-      <c r="P56" s="2"/>
+      <c r="O56" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P56" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="57" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="2"/>
+      <c r="A57" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B57" s="2" t="s">
         <v>325</v>
       </c>
@@ -7838,15 +8104,21 @@
         <v>328</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M57" s="7"/>
       <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
-      <c r="P57" s="2"/>
+      <c r="O57" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P57" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="58" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="2"/>
+      <c r="A58" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B58" s="2" t="s">
         <v>329</v>
       </c>
@@ -7878,15 +8150,21 @@
         <v>332</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M58" s="7"/>
       <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
-      <c r="P58" s="2"/>
+      <c r="O58" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P58" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="59" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="2"/>
+      <c r="A59" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B59" s="2" t="s">
         <v>333</v>
       </c>
@@ -7918,15 +8196,21 @@
         <v>336</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M59" s="7"/>
       <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
-      <c r="P59" s="2"/>
+      <c r="O59" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P59" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="60" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="2"/>
+      <c r="A60" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B60" s="2" t="s">
         <v>337</v>
       </c>
@@ -7958,15 +8242,21 @@
         <v>340</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M60" s="7"/>
       <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
-      <c r="P60" s="2"/>
+      <c r="O60" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P60" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="61" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="2"/>
+      <c r="A61" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B61" s="2" t="s">
         <v>341</v>
       </c>
@@ -7998,15 +8288,21 @@
         <v>344</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M61" s="7"/>
       <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
-      <c r="P61" s="2"/>
+      <c r="O61" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P61" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="62" spans="1:16" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="2"/>
+      <c r="A62" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B62" s="2" t="s">
         <v>345</v>
       </c>
@@ -8038,15 +8334,21 @@
         <v>349</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M62" s="7"/>
       <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
-      <c r="P62" s="2"/>
+      <c r="O62" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P62" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="63" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="2"/>
+      <c r="A63" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B63" s="2" t="s">
         <v>350</v>
       </c>
@@ -8078,15 +8380,21 @@
         <v>353</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M63" s="7"/>
       <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
-      <c r="P63" s="2"/>
+      <c r="O63" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P63" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="64" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="2"/>
+      <c r="A64" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B64" s="2" t="s">
         <v>354</v>
       </c>
@@ -8118,15 +8426,21 @@
         <v>357</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M64" s="7"/>
       <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
-      <c r="P64" s="2"/>
+      <c r="O64" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P64" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="65" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="2"/>
+      <c r="A65" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B65" s="2" t="s">
         <v>358</v>
       </c>
@@ -8158,15 +8472,21 @@
         <v>361</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M65" s="7"/>
       <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
-      <c r="P65" s="2"/>
+      <c r="O65" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P65" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="66" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="2"/>
+      <c r="A66" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B66" s="2" t="s">
         <v>362</v>
       </c>
@@ -8198,15 +8518,21 @@
         <v>365</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M66" s="7"/>
       <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
-      <c r="P66" s="2"/>
+      <c r="O66" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P66" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="67" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="2"/>
+      <c r="A67" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B67" s="2" t="s">
         <v>366</v>
       </c>
@@ -8238,15 +8564,21 @@
         <v>365</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M67" s="7"/>
       <c r="N67" s="2"/>
-      <c r="O67" s="2"/>
-      <c r="P67" s="2"/>
+      <c r="O67" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P67" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="68" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="2"/>
+      <c r="A68" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B68" s="2" t="s">
         <v>367</v>
       </c>
@@ -8278,15 +8610,21 @@
         <v>370</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M68" s="7"/>
       <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
-      <c r="P68" s="2"/>
+      <c r="O68" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P68" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="69" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="2"/>
+      <c r="A69" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B69" s="2" t="s">
         <v>371</v>
       </c>
@@ -8318,15 +8656,21 @@
         <v>375</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M69" s="7"/>
       <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
-      <c r="P69" s="2"/>
+      <c r="O69" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P69" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="70" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="2"/>
+      <c r="A70" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B70" s="2" t="s">
         <v>376</v>
       </c>
@@ -8358,15 +8702,21 @@
         <v>379</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M70" s="7"/>
       <c r="N70" s="2"/>
-      <c r="O70" s="2"/>
-      <c r="P70" s="2"/>
+      <c r="O70" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P70" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="71" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="2"/>
+      <c r="A71" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B71" s="2" t="s">
         <v>380</v>
       </c>
@@ -8398,15 +8748,21 @@
         <v>384</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M71" s="7"/>
       <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
-      <c r="P71" s="2"/>
+      <c r="O71" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P71" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="72" spans="1:16" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="2"/>
+      <c r="A72" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B72" s="2" t="s">
         <v>385</v>
       </c>
@@ -8438,15 +8794,21 @@
         <v>389</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M72" s="7"/>
       <c r="N72" s="2"/>
-      <c r="O72" s="2"/>
-      <c r="P72" s="2"/>
+      <c r="O72" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P72" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="73" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="2"/>
+      <c r="A73" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B73" s="2" t="s">
         <v>390</v>
       </c>
@@ -8478,15 +8840,21 @@
         <v>393</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M73" s="7"/>
       <c r="N73" s="2"/>
-      <c r="O73" s="2"/>
-      <c r="P73" s="2"/>
+      <c r="O73" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P73" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="74" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="2"/>
+      <c r="A74" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B74" s="2" t="s">
         <v>394</v>
       </c>
@@ -8518,12 +8886,16 @@
         <v>397</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M74" s="7"/>
       <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
-      <c r="P74" s="2"/>
+      <c r="O74" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P74" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="75" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2"/>
@@ -12142,7 +12514,9 @@
       </c>
     </row>
     <row r="165" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="2"/>
+      <c r="A165" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B165" s="2" t="s">
         <v>772</v>
       </c>
@@ -12174,15 +12548,21 @@
         <v>775</v>
       </c>
       <c r="L165" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M165" s="7"/>
       <c r="N165" s="2"/>
-      <c r="O165" s="2"/>
-      <c r="P165" s="2"/>
+      <c r="O165" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P165" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="166" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="2"/>
+      <c r="A166" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B166" s="2" t="s">
         <v>776</v>
       </c>
@@ -12214,15 +12594,21 @@
         <v>779</v>
       </c>
       <c r="L166" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M166" s="7"/>
       <c r="N166" s="2"/>
-      <c r="O166" s="2"/>
-      <c r="P166" s="2"/>
+      <c r="O166" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P166" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="167" spans="1:16" ht="105" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="2"/>
+      <c r="A167" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B167" s="2" t="s">
         <v>780</v>
       </c>
@@ -12254,15 +12640,21 @@
         <v>784</v>
       </c>
       <c r="L167" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M167" s="7"/>
       <c r="N167" s="2"/>
-      <c r="O167" s="2"/>
-      <c r="P167" s="2"/>
+      <c r="O167" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P167" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="168" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A168" s="2"/>
+      <c r="A168" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B168" s="2" t="s">
         <v>785</v>
       </c>
@@ -12294,15 +12686,21 @@
         <v>788</v>
       </c>
       <c r="L168" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M168" s="7"/>
       <c r="N168" s="2"/>
-      <c r="O168" s="2"/>
-      <c r="P168" s="2"/>
+      <c r="O168" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P168" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="169" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="2"/>
+      <c r="A169" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B169" s="2" t="s">
         <v>789</v>
       </c>
@@ -12334,15 +12732,21 @@
         <v>792</v>
       </c>
       <c r="L169" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M169" s="7"/>
       <c r="N169" s="2"/>
-      <c r="O169" s="2"/>
-      <c r="P169" s="2"/>
+      <c r="O169" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P169" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="170" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A170" s="2"/>
+      <c r="A170" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B170" s="2" t="s">
         <v>793</v>
       </c>
@@ -12374,15 +12778,21 @@
         <v>796</v>
       </c>
       <c r="L170" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M170" s="7"/>
       <c r="N170" s="2"/>
-      <c r="O170" s="2"/>
-      <c r="P170" s="2"/>
+      <c r="O170" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P170" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="171" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A171" s="2"/>
+      <c r="A171" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B171" s="2" t="s">
         <v>797</v>
       </c>
@@ -12414,15 +12824,21 @@
         <v>796</v>
       </c>
       <c r="L171" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M171" s="7"/>
       <c r="N171" s="2"/>
-      <c r="O171" s="2"/>
-      <c r="P171" s="2"/>
+      <c r="O171" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P171" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="172" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A172" s="2"/>
+      <c r="A172" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B172" s="2" t="s">
         <v>798</v>
       </c>
@@ -12454,12 +12870,16 @@
         <v>801</v>
       </c>
       <c r="L172" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M172" s="7"/>
       <c r="N172" s="2"/>
-      <c r="O172" s="2"/>
-      <c r="P172" s="2"/>
+      <c r="O172" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P172" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="173" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2"/>
@@ -12502,7 +12922,9 @@
       <c r="P173" s="2"/>
     </row>
     <row r="174" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A174" s="2"/>
+      <c r="A174" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B174" s="2" t="s">
         <v>806</v>
       </c>
@@ -12534,12 +12956,16 @@
         <v>809</v>
       </c>
       <c r="L174" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M174" s="7"/>
       <c r="N174" s="2"/>
-      <c r="O174" s="2"/>
-      <c r="P174" s="2"/>
+      <c r="O174" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P174" s="2" t="s">
+        <v>1155</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="K2:K168">
@@ -12744,7 +13170,9 @@
       </c>
     </row>
     <row r="3" spans="1:18" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
+      <c r="A3" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B3" s="2" t="s">
         <v>822</v>
       </c>
@@ -12782,12 +13210,16 @@
         <v>826</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O3" s="7"/>
       <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2"/>
+      <c r="Q3" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>1159</v>
+      </c>
     </row>
     <row r="4" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -12844,7 +13276,9 @@
       </c>
     </row>
     <row r="5" spans="1:18" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
+      <c r="A5" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B5" s="2" t="s">
         <v>832</v>
       </c>
@@ -12882,15 +13316,21 @@
         <v>835</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O5" s="7"/>
       <c r="P5" s="2"/>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2"/>
+      <c r="Q5" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>1159</v>
+      </c>
     </row>
     <row r="6" spans="1:18" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
+      <c r="A6" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B6" s="2" t="s">
         <v>836</v>
       </c>
@@ -12928,12 +13368,16 @@
         <v>839</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O6" s="7"/>
       <c r="P6" s="2"/>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2"/>
+      <c r="Q6" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>1159</v>
+      </c>
     </row>
     <row r="7" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
@@ -13152,7 +13596,9 @@
       </c>
     </row>
     <row r="11" spans="1:18" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
+      <c r="A11" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B11" s="2" t="s">
         <v>857</v>
       </c>
@@ -13190,15 +13636,21 @@
         <v>860</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O11" s="7"/>
       <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2"/>
+      <c r="Q11" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>1159</v>
+      </c>
     </row>
     <row r="12" spans="1:18" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
+      <c r="A12" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B12" s="2" t="s">
         <v>861</v>
       </c>
@@ -13236,15 +13688,21 @@
         <v>864</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O12" s="7"/>
       <c r="P12" s="2"/>
-      <c r="Q12" s="2"/>
-      <c r="R12" s="2"/>
+      <c r="Q12" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>1159</v>
+      </c>
     </row>
     <row r="13" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
+      <c r="A13" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B13" s="2" t="s">
         <v>865</v>
       </c>
@@ -13282,15 +13740,23 @@
         <v>868</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="O13" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="O13" s="7">
+        <v>46324</v>
+      </c>
       <c r="P13" s="2"/>
-      <c r="Q13" s="2"/>
-      <c r="R13" s="2"/>
+      <c r="Q13" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>1160</v>
+      </c>
     </row>
     <row r="14" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2"/>
+      <c r="A14" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B14" s="2" t="s">
         <v>869</v>
       </c>
@@ -13328,15 +13794,21 @@
         <v>875</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O14" s="7"/>
       <c r="P14" s="2"/>
-      <c r="Q14" s="2"/>
-      <c r="R14" s="2"/>
+      <c r="Q14" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>1159</v>
+      </c>
     </row>
     <row r="15" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2"/>
+      <c r="A15" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B15" s="2" t="s">
         <v>876</v>
       </c>
@@ -13374,12 +13846,16 @@
         <v>879</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O15" s="7"/>
       <c r="P15" s="2"/>
-      <c r="Q15" s="2"/>
-      <c r="R15" s="2"/>
+      <c r="Q15" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>1159</v>
+      </c>
     </row>
     <row r="16" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
@@ -13428,7 +13904,9 @@
       <c r="R16" s="2"/>
     </row>
     <row r="17" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
+      <c r="A17" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B17" s="2" t="s">
         <v>884</v>
       </c>
@@ -13466,15 +13944,21 @@
         <v>887</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O17" s="7"/>
       <c r="P17" s="2"/>
-      <c r="Q17" s="2"/>
-      <c r="R17" s="2"/>
+      <c r="Q17" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>1159</v>
+      </c>
     </row>
     <row r="18" spans="1:18" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
+      <c r="A18" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B18" s="2" t="s">
         <v>888</v>
       </c>
@@ -13512,12 +13996,16 @@
         <v>891</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O18" s="7"/>
       <c r="P18" s="2"/>
-      <c r="Q18" s="2"/>
-      <c r="R18" s="2"/>
+      <c r="Q18" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>1159</v>
+      </c>
     </row>
     <row r="19" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
@@ -15223,7 +15711,9 @@
       </c>
     </row>
     <row r="3" spans="1:15" ht="105" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
+      <c r="A3" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B3" s="2" t="s">
         <v>998</v>
       </c>
@@ -15249,18 +15739,24 @@
         <v>1003</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K3" s="7"/>
       <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
+      <c r="M3" s="2" t="s">
+        <v>1157</v>
+      </c>
       <c r="N3" s="2" t="s">
         <v>1004</v>
       </c>
-      <c r="O3" s="2"/>
+      <c r="O3" s="2" t="s">
+        <v>1158</v>
+      </c>
     </row>
     <row r="4" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
+      <c r="A4" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B4" s="2" t="s">
         <v>1005</v>
       </c>
@@ -15286,15 +15782,19 @@
         <v>1010</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K4" s="7"/>
       <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
+      <c r="M4" s="2" t="s">
+        <v>1157</v>
+      </c>
       <c r="N4" s="2" t="s">
         <v>1004</v>
       </c>
-      <c r="O4" s="2"/>
+      <c r="O4" s="2" t="s">
+        <v>1158</v>
+      </c>
     </row>
     <row r="5" spans="1:15" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
@@ -15556,7 +16056,9 @@
       <c r="O11" s="2"/>
     </row>
     <row r="12" spans="1:15" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
+      <c r="A12" s="2" t="s">
+        <v>1156</v>
+      </c>
       <c r="B12" s="2" t="s">
         <v>1052</v>
       </c>
@@ -15582,11 +16084,13 @@
         <v>1057</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K12" s="7"/>
       <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
+      <c r="M12" s="2" t="s">
+        <v>1157</v>
+      </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2" t="s">
         <v>1058</v>
@@ -15846,7 +16350,7 @@
       </c>
       <c r="J3" s="2" t="str">
         <f>IFERROR(INDEX('Security Acceptance'!$N:$N,MATCH($I3,'Security Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K3" s="7">
         <f>IFERROR(INDEX('Security Acceptance'!$O:$O,MATCH($I3,'Security Acceptance'!$B:$B,0)),"")</f>
@@ -15856,9 +16360,9 @@
         <f>IFERROR(INDEX('Security Acceptance'!$P:$P,MATCH($I3,'Security Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M3" s="2">
+      <c r="M3" s="2" t="str">
         <f>IFERROR(INDEX('Security Acceptance'!$Q:$Q,MATCH($I3,'Security Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>1075</v>
@@ -15944,7 +16448,7 @@
       </c>
       <c r="J5" s="2" t="str">
         <f>IFERROR(INDEX('Security Acceptance'!$N:$N,MATCH($I5,'Security Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K5" s="7">
         <f>IFERROR(INDEX('Security Acceptance'!$O:$O,MATCH($I5,'Security Acceptance'!$B:$B,0)),"")</f>
@@ -15954,9 +16458,9 @@
         <f>IFERROR(INDEX('Security Acceptance'!$P:$P,MATCH($I5,'Security Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M5" s="2">
+      <c r="M5" s="2" t="str">
         <f>IFERROR(INDEX('Security Acceptance'!$Q:$Q,MATCH($I5,'Security Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>1075</v>
@@ -15993,7 +16497,7 @@
       </c>
       <c r="J6" s="2" t="str">
         <f>IFERROR(INDEX('Security Acceptance'!$N:$N,MATCH($I6,'Security Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K6" s="7">
         <f>IFERROR(INDEX('Security Acceptance'!$O:$O,MATCH($I6,'Security Acceptance'!$B:$B,0)),"")</f>
@@ -16003,9 +16507,9 @@
         <f>IFERROR(INDEX('Security Acceptance'!$P:$P,MATCH($I6,'Security Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M6" s="2">
+      <c r="M6" s="2" t="str">
         <f>IFERROR(INDEX('Security Acceptance'!$Q:$Q,MATCH($I6,'Security Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>1075</v>
@@ -16319,7 +16823,7 @@
       </c>
       <c r="J13" s="2" t="str">
         <f>IFERROR(INDEX('Security Acceptance'!$N:$N,MATCH($I13,'Security Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K13" s="7">
         <f>IFERROR(INDEX('Security Acceptance'!$O:$O,MATCH($I13,'Security Acceptance'!$B:$B,0)),"")</f>
@@ -16329,9 +16833,9 @@
         <f>IFERROR(INDEX('Security Acceptance'!$P:$P,MATCH($I13,'Security Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M13" s="2">
+      <c r="M13" s="2" t="str">
         <f>IFERROR(INDEX('Security Acceptance'!$Q:$Q,MATCH($I13,'Security Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N13" s="2" t="s">
         <v>1075</v>
@@ -16368,7 +16872,7 @@
       </c>
       <c r="J14" s="2" t="str">
         <f>IFERROR(INDEX('Security Acceptance'!$N:$N,MATCH($I14,'Security Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K14" s="7">
         <f>IFERROR(INDEX('Security Acceptance'!$O:$O,MATCH($I14,'Security Acceptance'!$B:$B,0)),"")</f>
@@ -16378,9 +16882,9 @@
         <f>IFERROR(INDEX('Security Acceptance'!$P:$P,MATCH($I14,'Security Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M14" s="2">
+      <c r="M14" s="2" t="str">
         <f>IFERROR(INDEX('Security Acceptance'!$Q:$Q,MATCH($I14,'Security Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N14" s="2" t="s">
         <v>1075</v>
@@ -16417,19 +16921,19 @@
       </c>
       <c r="J15" s="2" t="str">
         <f>IFERROR(INDEX('Security Acceptance'!$N:$N,MATCH($I15,'Security Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Pass</v>
       </c>
       <c r="K15" s="7">
         <f>IFERROR(INDEX('Security Acceptance'!$O:$O,MATCH($I15,'Security Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L15" s="2">
         <f>IFERROR(INDEX('Security Acceptance'!$P:$P,MATCH($I15,'Security Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M15" s="2">
+      <c r="M15" s="2" t="str">
         <f>IFERROR(INDEX('Security Acceptance'!$Q:$Q,MATCH($I15,'Security Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N15" s="2" t="s">
         <v>1075</v>
@@ -16709,7 +17213,7 @@
       </c>
       <c r="J21" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I21,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K21" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I21,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -16719,9 +17223,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I21,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M21" s="2">
+      <c r="M21" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I21,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>1075</v>
@@ -16758,7 +17262,7 @@
       </c>
       <c r="J22" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I22,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K22" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I22,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -16768,9 +17272,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I22,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M22" s="2">
+      <c r="M22" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I22,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N22" s="2" t="s">
         <v>1075</v>
@@ -16942,7 +17446,7 @@
       </c>
       <c r="J26" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I26,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K26" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I26,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -16952,9 +17456,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I26,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M26" s="2">
+      <c r="M26" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I26,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>1075</v>
@@ -16991,7 +17495,7 @@
       </c>
       <c r="J27" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I27,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K27" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I27,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -17001,9 +17505,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I27,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M27" s="2">
+      <c r="M27" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I27,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N27" s="2" t="s">
         <v>1075</v>
@@ -17040,7 +17544,7 @@
       </c>
       <c r="J28" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I28,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K28" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I28,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -17050,9 +17554,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I28,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M28" s="2">
+      <c r="M28" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I28,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>1075</v>
@@ -17089,7 +17593,7 @@
       </c>
       <c r="J29" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I29,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K29" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I29,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -17099,9 +17603,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I29,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M29" s="2">
+      <c r="M29" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I29,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N29" s="2" t="s">
         <v>1075</v>
@@ -17138,7 +17642,7 @@
       </c>
       <c r="J30" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I30,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K30" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I30,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -17148,9 +17652,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I30,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M30" s="2">
+      <c r="M30" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I30,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N30" s="2" t="s">
         <v>1075</v>
@@ -17187,7 +17691,7 @@
       </c>
       <c r="J31" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I31,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K31" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I31,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -17197,9 +17701,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I31,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M31" s="2">
+      <c r="M31" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I31,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N31" s="2" t="s">
         <v>1075</v>
@@ -17236,7 +17740,7 @@
       </c>
       <c r="J32" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I32,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K32" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I32,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -17246,9 +17750,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I32,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M32" s="2">
+      <c r="M32" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I32,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N32" s="2" t="s">
         <v>1075</v>
@@ -17285,7 +17789,7 @@
       </c>
       <c r="J33" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I33,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K33" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I33,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -17295,9 +17799,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I33,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M33" s="2">
+      <c r="M33" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I33,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N33" s="2" t="s">
         <v>1075</v>
@@ -17334,7 +17838,7 @@
       </c>
       <c r="J34" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I34,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K34" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I34,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -17344,9 +17848,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I34,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M34" s="2">
+      <c r="M34" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I34,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N34" s="2" t="s">
         <v>1075</v>
@@ -17383,7 +17887,7 @@
       </c>
       <c r="J35" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I35,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K35" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I35,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -17393,9 +17897,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I35,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M35" s="2">
+      <c r="M35" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I35,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N35" s="2" t="s">
         <v>1075</v>
@@ -17432,7 +17936,7 @@
       </c>
       <c r="J36" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I36,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K36" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I36,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -17442,9 +17946,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I36,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M36" s="2">
+      <c r="M36" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I36,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N36" s="2" t="s">
         <v>1075</v>
@@ -17481,7 +17985,7 @@
       </c>
       <c r="J37" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I37,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K37" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I37,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -17491,9 +17995,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I37,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M37" s="2">
+      <c r="M37" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I37,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N37" s="2" t="s">
         <v>1075</v>
@@ -17530,7 +18034,7 @@
       </c>
       <c r="J38" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I38,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K38" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I38,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -17540,9 +18044,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I38,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M38" s="2">
+      <c r="M38" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I38,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N38" s="2" t="s">
         <v>1075</v>
@@ -17579,7 +18083,7 @@
       </c>
       <c r="J39" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I39,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K39" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I39,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -17589,9 +18093,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I39,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M39" s="2">
+      <c r="M39" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I39,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N39" s="2" t="s">
         <v>1075</v>
@@ -17628,7 +18132,7 @@
       </c>
       <c r="J40" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I40,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K40" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I40,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -17638,9 +18142,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I40,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M40" s="2">
+      <c r="M40" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I40,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N40" s="2" t="s">
         <v>1075</v>
@@ -17824,7 +18328,7 @@
       </c>
       <c r="J44" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I44,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K44" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I44,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -17834,9 +18338,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I44,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M44" s="2">
+      <c r="M44" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I44,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N44" s="2" t="s">
         <v>1075</v>
@@ -17873,7 +18377,7 @@
       </c>
       <c r="J45" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I45,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K45" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I45,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -17883,9 +18387,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I45,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M45" s="2">
+      <c r="M45" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I45,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N45" s="2" t="s">
         <v>1075</v>
@@ -17922,7 +18426,7 @@
       </c>
       <c r="J46" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I46,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K46" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I46,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -17932,9 +18436,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I46,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M46" s="2">
+      <c r="M46" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I46,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N46" s="2" t="s">
         <v>1075</v>
@@ -17971,7 +18475,7 @@
       </c>
       <c r="J47" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I47,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K47" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I47,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -17981,9 +18485,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I47,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M47" s="2">
+      <c r="M47" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I47,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N47" s="2" t="s">
         <v>1075</v>
@@ -18020,7 +18524,7 @@
       </c>
       <c r="J48" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I48,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K48" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I48,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -18030,9 +18534,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I48,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M48" s="2">
+      <c r="M48" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I48,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N48" s="2" t="s">
         <v>1075</v>
@@ -18069,7 +18573,7 @@
       </c>
       <c r="J49" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I49,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K49" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I49,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -18079,9 +18583,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I49,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M49" s="2">
+      <c r="M49" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I49,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N49" s="2" t="s">
         <v>1075</v>
@@ -18167,7 +18671,7 @@
       </c>
       <c r="J51" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I51,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K51" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I51,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -18177,9 +18681,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I51,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M51" s="2">
+      <c r="M51" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I51,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N51" s="2" t="s">
         <v>1075</v>
@@ -18216,7 +18720,7 @@
       </c>
       <c r="J52" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I52,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K52" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I52,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -18226,9 +18730,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I52,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M52" s="2">
+      <c r="M52" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I52,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N52" s="2" t="s">
         <v>1075</v>
@@ -18265,7 +18769,7 @@
       </c>
       <c r="J53" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I53,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K53" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I53,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -18275,9 +18779,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I53,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M53" s="2">
+      <c r="M53" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I53,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N53" s="2" t="s">
         <v>1075</v>
@@ -18314,7 +18818,7 @@
       </c>
       <c r="J54" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I54,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K54" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I54,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -18324,9 +18828,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I54,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M54" s="2">
+      <c r="M54" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I54,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N54" s="2" t="s">
         <v>1075</v>
@@ -18461,7 +18965,7 @@
       </c>
       <c r="J57" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I57,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K57" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I57,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -18471,9 +18975,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I57,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M57" s="2">
+      <c r="M57" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I57,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N57" s="2" t="s">
         <v>1075</v>
@@ -18510,7 +19014,7 @@
       </c>
       <c r="J58" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I58,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K58" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I58,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -18520,9 +19024,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I58,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M58" s="2">
+      <c r="M58" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I58,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N58" s="2" t="s">
         <v>1075</v>
@@ -18559,7 +19063,7 @@
       </c>
       <c r="J59" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I59,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K59" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I59,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -18569,9 +19073,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I59,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M59" s="2">
+      <c r="M59" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I59,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N59" s="2" t="s">
         <v>1075</v>
@@ -18608,7 +19112,7 @@
       </c>
       <c r="J60" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I60,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K60" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I60,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -18618,9 +19122,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I60,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M60" s="2">
+      <c r="M60" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I60,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N60" s="2" t="s">
         <v>1075</v>
@@ -18755,7 +19259,7 @@
       </c>
       <c r="J63" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I63,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K63" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I63,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -18765,9 +19269,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I63,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M63" s="2">
+      <c r="M63" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I63,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N63" s="2" t="s">
         <v>1075</v>
@@ -18804,7 +19308,7 @@
       </c>
       <c r="J64" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I64,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K64" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I64,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -18814,9 +19318,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I64,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M64" s="2">
+      <c r="M64" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I64,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N64" s="2" t="s">
         <v>1075</v>
@@ -18853,7 +19357,7 @@
       </c>
       <c r="J65" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I65,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K65" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I65,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -18863,9 +19367,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I65,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M65" s="2">
+      <c r="M65" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I65,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N65" s="2" t="s">
         <v>1075</v>
@@ -18902,7 +19406,7 @@
       </c>
       <c r="J66" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I66,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K66" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I66,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -18912,9 +19416,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I66,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M66" s="2">
+      <c r="M66" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I66,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N66" s="2" t="s">
         <v>1075</v>
@@ -18951,7 +19455,7 @@
       </c>
       <c r="J67" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I67,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K67" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I67,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -18961,9 +19465,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I67,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M67" s="2">
+      <c r="M67" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I67,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N67" s="2" t="s">
         <v>1075</v>
@@ -19000,7 +19504,7 @@
       </c>
       <c r="J68" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I68,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K68" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I68,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -19010,9 +19514,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I68,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M68" s="2">
+      <c r="M68" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I68,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N68" s="2" t="s">
         <v>1075</v>
@@ -19049,7 +19553,7 @@
       </c>
       <c r="J69" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I69,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K69" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I69,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -19059,9 +19563,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I69,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M69" s="2">
+      <c r="M69" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I69,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N69" s="2" t="s">
         <v>1075</v>
@@ -19098,7 +19602,7 @@
       </c>
       <c r="J70" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I70,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K70" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I70,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -19108,9 +19612,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I70,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M70" s="2">
+      <c r="M70" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I70,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N70" s="2" t="s">
         <v>1075</v>
@@ -19147,7 +19651,7 @@
       </c>
       <c r="J71" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I71,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K71" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I71,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -19157,9 +19661,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I71,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M71" s="2">
+      <c r="M71" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I71,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N71" s="2" t="s">
         <v>1075</v>
@@ -19196,7 +19700,7 @@
       </c>
       <c r="J72" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I72,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K72" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I72,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -19206,9 +19710,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I72,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M72" s="2">
+      <c r="M72" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I72,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N72" s="2" t="s">
         <v>1075</v>
@@ -19245,7 +19749,7 @@
       </c>
       <c r="J73" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I73,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K73" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I73,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -19255,9 +19759,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I73,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M73" s="2">
+      <c r="M73" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I73,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N73" s="2" t="s">
         <v>1075</v>
@@ -19294,7 +19798,7 @@
       </c>
       <c r="J74" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I74,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K74" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I74,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -19304,9 +19808,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I74,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M74" s="2">
+      <c r="M74" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I74,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N74" s="2" t="s">
         <v>1075</v>
@@ -19343,7 +19847,7 @@
       </c>
       <c r="J75" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I75,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K75" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I75,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -19353,9 +19857,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I75,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M75" s="2">
+      <c r="M75" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I75,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N75" s="2" t="s">
         <v>1075</v>
@@ -19392,7 +19896,7 @@
       </c>
       <c r="J76" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I76,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K76" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I76,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -19402,9 +19906,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I76,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M76" s="2">
+      <c r="M76" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I76,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N76" s="2" t="s">
         <v>1075</v>
@@ -19441,7 +19945,7 @@
       </c>
       <c r="J77" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I77,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K77" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I77,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -19451,9 +19955,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I77,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M77" s="2">
+      <c r="M77" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I77,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N77" s="2" t="s">
         <v>1075</v>
@@ -19490,7 +19994,7 @@
       </c>
       <c r="J78" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I78,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K78" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I78,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -19500,9 +20004,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I78,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M78" s="2">
+      <c r="M78" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I78,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N78" s="2" t="s">
         <v>1075</v>
@@ -19539,7 +20043,7 @@
       </c>
       <c r="J79" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I79,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K79" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I79,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -19549,9 +20053,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I79,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M79" s="2">
+      <c r="M79" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I79,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N79" s="2" t="s">
         <v>1075</v>
@@ -19588,7 +20092,7 @@
       </c>
       <c r="J80" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I80,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K80" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I80,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -19598,9 +20102,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I80,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M80" s="2">
+      <c r="M80" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I80,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N80" s="2" t="s">
         <v>1075</v>
@@ -19637,7 +20141,7 @@
       </c>
       <c r="J81" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I81,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K81" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I81,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -19647,9 +20151,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I81,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M81" s="2">
+      <c r="M81" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I81,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N81" s="2" t="s">
         <v>1075</v>
@@ -19686,7 +20190,7 @@
       </c>
       <c r="J82" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I82,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K82" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I82,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -19696,9 +20200,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I82,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M82" s="2">
+      <c r="M82" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I82,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N82" s="2" t="s">
         <v>1075</v>
@@ -19735,7 +20239,7 @@
       </c>
       <c r="J83" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I83,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K83" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I83,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -19745,9 +20249,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I83,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M83" s="2">
+      <c r="M83" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I83,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N83" s="2" t="s">
         <v>1075</v>
@@ -19784,7 +20288,7 @@
       </c>
       <c r="J84" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I84,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K84" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I84,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -19794,9 +20298,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I84,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M84" s="2">
+      <c r="M84" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I84,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N84" s="2" t="s">
         <v>1075</v>
@@ -19833,7 +20337,7 @@
       </c>
       <c r="J85" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I85,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K85" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I85,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -19843,9 +20347,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I85,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M85" s="2">
+      <c r="M85" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I85,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N85" s="2" t="s">
         <v>1075</v>
@@ -19882,7 +20386,7 @@
       </c>
       <c r="J86" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I86,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K86" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I86,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -19892,9 +20396,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I86,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M86" s="2">
+      <c r="M86" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I86,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N86" s="2" t="s">
         <v>1075</v>
@@ -24292,7 +24796,7 @@
       </c>
       <c r="J176" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I176,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K176" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I176,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -24302,9 +24806,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I176,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M176" s="2">
+      <c r="M176" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I176,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N176" s="2" t="s">
         <v>1075</v>
@@ -24341,7 +24845,7 @@
       </c>
       <c r="J177" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I177,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K177" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I177,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -24351,9 +24855,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I177,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M177" s="2">
+      <c r="M177" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I177,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N177" s="2" t="s">
         <v>1075</v>
@@ -24390,7 +24894,7 @@
       </c>
       <c r="J178" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I178,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K178" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I178,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -24400,9 +24904,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I178,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M178" s="2">
+      <c r="M178" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I178,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N178" s="2" t="s">
         <v>1075</v>
@@ -24439,7 +24943,7 @@
       </c>
       <c r="J179" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I179,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K179" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I179,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -24449,9 +24953,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I179,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M179" s="2">
+      <c r="M179" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I179,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N179" s="2" t="s">
         <v>1075</v>
@@ -24488,7 +24992,7 @@
       </c>
       <c r="J180" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I180,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K180" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I180,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -24498,9 +25002,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I180,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M180" s="2">
+      <c r="M180" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I180,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N180" s="2" t="s">
         <v>1075</v>
@@ -24537,7 +25041,7 @@
       </c>
       <c r="J181" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I181,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K181" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I181,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -24547,9 +25051,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I181,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M181" s="2">
+      <c r="M181" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I181,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N181" s="2" t="s">
         <v>1075</v>
@@ -24586,7 +25090,7 @@
       </c>
       <c r="J182" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I182,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K182" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I182,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -24596,9 +25100,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I182,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M182" s="2">
+      <c r="M182" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I182,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N182" s="2" t="s">
         <v>1075</v>
@@ -24684,7 +25188,7 @@
       </c>
       <c r="J184" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I184,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K184" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I184,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -24694,9 +25198,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I184,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M184" s="2">
+      <c r="M184" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I184,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N184" s="2" t="s">
         <v>1075</v>
@@ -25331,7 +25835,7 @@
       </c>
       <c r="J198" s="2" t="str">
         <f>IFERROR(INDEX('Security Acceptance'!$N:$N,MATCH($I198,'Security Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K198" s="7">
         <f>IFERROR(INDEX('Security Acceptance'!$O:$O,MATCH($I198,'Security Acceptance'!$B:$B,0)),"")</f>
@@ -25341,9 +25845,9 @@
         <f>IFERROR(INDEX('Security Acceptance'!$P:$P,MATCH($I198,'Security Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M198" s="2">
+      <c r="M198" s="2" t="str">
         <f>IFERROR(INDEX('Security Acceptance'!$Q:$Q,MATCH($I198,'Security Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N198" s="2" t="s">
         <v>1075</v>
@@ -25380,7 +25884,7 @@
       </c>
       <c r="J199" s="2" t="str">
         <f>IFERROR(INDEX('Security Acceptance'!$N:$N,MATCH($I199,'Security Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K199" s="7">
         <f>IFERROR(INDEX('Security Acceptance'!$O:$O,MATCH($I199,'Security Acceptance'!$B:$B,0)),"")</f>
@@ -25390,9 +25894,9 @@
         <f>IFERROR(INDEX('Security Acceptance'!$P:$P,MATCH($I199,'Security Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M199" s="2">
+      <c r="M199" s="2" t="str">
         <f>IFERROR(INDEX('Security Acceptance'!$Q:$Q,MATCH($I199,'Security Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N199" s="2" t="s">
         <v>1075</v>
@@ -25478,7 +25982,7 @@
       </c>
       <c r="J201" s="2" t="str">
         <f>IFERROR(INDEX('Security Acceptance'!$N:$N,MATCH($I201,'Security Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K201" s="7">
         <f>IFERROR(INDEX('Security Acceptance'!$O:$O,MATCH($I201,'Security Acceptance'!$B:$B,0)),"")</f>
@@ -25488,9 +25992,9 @@
         <f>IFERROR(INDEX('Security Acceptance'!$P:$P,MATCH($I201,'Security Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M201" s="2">
+      <c r="M201" s="2" t="str">
         <f>IFERROR(INDEX('Security Acceptance'!$Q:$Q,MATCH($I201,'Security Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N201" s="2" t="s">
         <v>1075</v>
@@ -25527,7 +26031,7 @@
       </c>
       <c r="J202" s="2" t="str">
         <f>IFERROR(INDEX('Security Acceptance'!$N:$N,MATCH($I202,'Security Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K202" s="7">
         <f>IFERROR(INDEX('Security Acceptance'!$O:$O,MATCH($I202,'Security Acceptance'!$B:$B,0)),"")</f>
@@ -25537,9 +26041,9 @@
         <f>IFERROR(INDEX('Security Acceptance'!$P:$P,MATCH($I202,'Security Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M202" s="2">
+      <c r="M202" s="2" t="str">
         <f>IFERROR(INDEX('Security Acceptance'!$Q:$Q,MATCH($I202,'Security Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N202" s="2" t="s">
         <v>1075</v>
@@ -26191,7 +26695,7 @@
       </c>
       <c r="J218" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I218,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K218" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I218,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -26201,9 +26705,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I218,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M218" s="2">
+      <c r="M218" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I218,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N218" s="2" t="s">
         <v>1075</v>
@@ -26240,7 +26744,7 @@
       </c>
       <c r="J219" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I219,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K219" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I219,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -26250,9 +26754,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I219,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M219" s="2">
+      <c r="M219" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I219,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N219" s="2" t="s">
         <v>1075</v>
@@ -26289,7 +26793,7 @@
       </c>
       <c r="J220" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I220,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K220" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I220,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -26299,9 +26803,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I220,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M220" s="2">
+      <c r="M220" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I220,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N220" s="2" t="s">
         <v>1075</v>
@@ -26338,7 +26842,7 @@
       </c>
       <c r="J221" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I221,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K221" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I221,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -26348,9 +26852,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I221,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M221" s="2">
+      <c r="M221" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I221,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N221" s="2" t="s">
         <v>1075</v>
@@ -26436,7 +26940,7 @@
       </c>
       <c r="J223" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I223,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Not Built</v>
+        <v>Ready to Test</v>
       </c>
       <c r="K223" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I223,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -26446,9 +26950,9 @@
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I223,'Functional Acceptance'!$B:$B,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="M223" s="2">
+      <c r="M223" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I223,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N223" s="2" t="s">
         <v>1075</v>

--- a/spec/meals/Meals Acceptance Checklist v1.0.xlsx
+++ b/spec/meals/Meals Acceptance Checklist v1.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wcoop\Documents\HomeMaintenanceApp\spec\meals\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91417126-1D94-4337-8CEA-D4028A336DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A814EB3D-B945-43A2-B137-0C00F0884776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Read Me" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5376" uniqueCount="1161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5377" uniqueCount="1212">
   <si>
     <t>Meals Acceptance Checklist</t>
   </si>
@@ -3322,9 +3322,6 @@
     <t>Reusable classification values persist, rename consistently, and cannot be deleted while in use.</t>
   </si>
   <si>
-    <t>Delete test Recipe and unused test classification values.</t>
-  </si>
-  <si>
     <t>E2E-11</t>
   </si>
   <si>
@@ -3623,22 +3620,248 @@
     <t>P0B-DB-001 Recipe foundation scope only. Captured production catalog and synthetic SQL SET ROLE/claim evidence, not live JWT/API authentication, owner application UAT or Recipe UI evidence. Future Meals objects require their own verification. No deployment blocker observed; blocker classification field is unchanged. Reversal prepared, not executed; test-only transaction rollback is not migration reversal. Production postflight effective_anon_denial/explicit_table_acl/function_acl/column_acl passed.</t>
   </si>
   <si>
-    <t>Local Recipe Core implementation and technical checks complete. Isolated browser/handler/PGlite evidence only; not live owner JWT/API or owner UAT. Await authorized deployment and independent owner desktop/mobile verification. Phase 2/3 actions remain unavailable.</t>
-  </si>
-  <si>
     <t>P1-TECH-001</t>
   </si>
   <si>
     <t>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</t>
   </si>
   <si>
-    <t>Prepared with deterministic run-prefixed IDs and Recipe-before-lookup cleanup in spec/meals/README.md. Local synthetic flow exercised and fixture counts returned to zero. Live owner E2E/UAT remains unexecuted pending authorized deployment. No Shopping/Planner data created.</t>
-  </si>
-  <si>
     <t>Recipe UI/service ready for post-release owner/API checks. Local source/build, isolated synthetic browser and exact-migration PGlite role tests passed. These do not prove live JWT/PostgREST authorization; composite application/API verification is not marked Pass. Prior production P0B evidence is unchanged.</t>
   </si>
   <si>
     <t>Executed local source/build inspection and unchanged-migration PGlite catalog tests: direct table service, no application-callable Recipe RPC/function and no SECURITY DEFINER introduced. Existing internal trigger remains invoker and not browser-callable. Local technical scope only, not owner application/API authentication proof.</t>
+  </si>
+  <si>
+    <t>P1-TECH-001; P1-UAT-001</t>
+  </si>
+  <si>
+    <t>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md</t>
+  </si>
+  <si>
+    <t>Local Recipe Core implementation and technical checks complete. Isolated browser/handler/PGlite evidence only; not live owner JWT/API or owner UAT. Await authorized deployment and independent owner desktop/mobile verification. Phase 2/3 actions remain unavailable.
+Owner-reported PASS against the current approved criterion (P1-UAT-001; 2026-10-29). Proposed product changes are tracked separately and do not change this Expected Result; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md.</t>
+  </si>
+  <si>
+    <t>P1-TECH-001; P1-UAT-002</t>
+  </si>
+  <si>
+    <t>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-002; owner-reported live-web UAT; 2026-10-29; see Phase 1 Owner UAT Findings and Requirements Change Requests.md</t>
+  </si>
+  <si>
+    <t>Local Recipe Core implementation and technical checks complete. Isolated browser/handler/PGlite evidence only; not live owner JWT/API or owner UAT. Await authorized deployment and independent owner desktop/mobile verification. Phase 2/3 actions remain unavailable._x000D_
+P1-UAT-002 Sec. 5: Owner PASS for desktop sorting.</t>
+  </si>
+  <si>
+    <t>Local Recipe Core implementation and technical checks complete. Isolated browser/handler/PGlite evidence only; not live owner JWT/API or owner UAT. Await authorized deployment and independent owner desktop/mobile verification. Phase 2/3 actions remain unavailable._x000D_
+P1-UAT-002 Sec. 2: Owner PASS for remaining Add Recipe/Editor checks.</t>
+  </si>
+  <si>
+    <t>Local Recipe Core implementation and technical checks complete. Isolated browser/handler/PGlite evidence only; not live owner JWT/API or owner UAT. Await authorized deployment and independent owner desktop/mobile verification. Phase 2/3 actions remain unavailable._x000D_
+P1-UAT-002 Sec. 2: Owner PASS for remaining Add Recipe/Editor checks; desktop Save/Cancel row.</t>
+  </si>
+  <si>
+    <t>Local Recipe Core implementation and technical checks complete. Isolated browser/handler/PGlite evidence only; not live owner JWT/API or owner UAT. Await authorized deployment and independent owner desktop/mobile verification. Phase 2/3 actions remain unavailable._x000D_
+P1-UAT-002 Sec. 2: Owner PASS for remaining Add Recipe/Editor checks; mobile Save/Cancel row.</t>
+  </si>
+  <si>
+    <t>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; Executed: node --test tests/meals-recipe-interaction.test.cjs tests/meals-recipe-service.test.cjs tests/meals-recipe-persistence.test.cjs (19 passed, 0 failed; 2026-10-29)</t>
+  </si>
+  <si>
+    <t>Local Recipe Core implementation and technical checks complete. Isolated browser/handler/PGlite evidence only; not live owner JWT/API or owner UAT. Await authorized deployment and independent owner desktop/mobile verification. Phase 2/3 actions remain unavailable._x000D_
+P1-UAT-002 Sec. 3: PASS from executed automated failure/retention/retry evidence; redundant owner failure injection is unnecessary.</t>
+  </si>
+  <si>
+    <t>Local Recipe Core implementation and technical checks complete. Isolated browser/handler/PGlite evidence only; not live owner JWT/API or owner UAT. Await authorized deployment and independent owner desktop/mobile verification. Phase 2/3 actions remain unavailable._x000D_
+P1-UAT-002 Sec. 8: Owner PASS for mobile Recipe Detail presentation; CR-7 is separate.</t>
+  </si>
+  <si>
+    <t>Local Recipe Core implementation and technical checks complete. Isolated browser/handler/PGlite evidence only; not live owner JWT/API or owner UAT. Await authorized deployment and independent owner desktop/mobile verification. Phase 2/3 actions remain unavailable._x000D_
+P1-UAT-002 Sec. 10: Owner PASS for true-empty versus no-match Library behavior; automated empty/zero-result recovery assertions also passed.</t>
+  </si>
+  <si>
+    <t>Local Recipe Core implementation and technical checks complete. Isolated browser/handler/PGlite evidence only; not live owner JWT/API or owner UAT. Await authorized deployment and independent owner desktop/mobile verification. Phase 2/3 actions remain unavailable._x000D_
+P1-UAT-002 Sec. 4: Owner PASS for normal loading; automated Library test verifies loading and no misleading empty state while pending.</t>
+  </si>
+  <si>
+    <t>Local Recipe Core implementation and technical checks complete. Isolated browser/handler/PGlite evidence only; not live owner JWT/API or owner UAT. Await authorized deployment and independent owner desktop/mobile verification. Phase 2/3 actions remain unavailable._x000D_
+P1-UAT-002 Sec. 11: Owner PASS; executed editor test also confirms duplicate submits during a pending save are guarded.</t>
+  </si>
+  <si>
+    <t>P1-TECH-001; P1-UAT-001; P1-UAT-002</t>
+  </si>
+  <si>
+    <t>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md; P1-UAT-002; owner-reported live-web UAT; 2026-10-29; see Phase 1 Owner UAT Findings and Requirements Change Requests.md</t>
+  </si>
+  <si>
+    <t>Local Recipe Core implementation and technical checks complete. Isolated browser/handler/PGlite evidence only; not live owner JWT/API or owner UAT. Await authorized deployment and independent owner desktop/mobile verification. Phase 2/3 actions remain unavailable.
+Owner-reported PASS against the current approved criterion (P1-UAT-001; 2026-10-29). Proposed product changes are tracked separately and do not change this Expected Result; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md._x000D_
+P1-UAT-002 Sec. 6: Owner PASS for desktop Recipe Library layout.</t>
+  </si>
+  <si>
+    <t>Local Recipe Core implementation and technical checks complete. Isolated browser/handler/PGlite evidence only; not live owner JWT/API or owner UAT. Await authorized deployment and independent owner desktop/mobile verification. Phase 2/3 actions remain unavailable.
+Owner-reported PASS against the current approved criterion (P1-UAT-001; 2026-10-29). Proposed product changes are tracked separately and do not change this Expected Result; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md._x000D_
+P1-UAT-002 Secs. 6 and 17: Owner PASS for desktop layout/responsive check; Sec. 17 PASS / interpreted as PASS, with no contradictory failure note.</t>
+  </si>
+  <si>
+    <t>Local Recipe Core implementation and technical checks complete. Isolated browser/handler/PGlite evidence only; not live owner JWT/API or owner UAT. Await authorized deployment and independent owner desktop/mobile verification. Phase 2/3 actions remain unavailable.
+Owner-reported PASS against the current approved criterion (P1-UAT-001; 2026-10-29). Proposed product changes are tracked separately and do not change this Expected Result; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md._x000D_
+P1-UAT-002 Sec. 7: Owner PASS for mobile Recipe Library presentation; CR-8 is separate.</t>
+  </si>
+  <si>
+    <t>Local Recipe Core implementation and technical checks complete. Isolated browser/handler/PGlite evidence only; not live owner JWT/API or owner UAT. Await authorized deployment and independent owner desktop/mobile verification. Phase 2/3 actions remain unavailable.
+Owner-reported PASS against the current approved criterion (P1-UAT-001; 2026-10-29). Proposed product changes are tracked separately and do not change this Expected Result; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md._x000D_
+P1-UAT-002 Secs. 7 and 18: Owner PASS for mobile presentation/responsive check.</t>
+  </si>
+  <si>
+    <t>Local Recipe Core implementation and technical checks complete. Isolated browser/handler/PGlite evidence only; not live owner JWT/API or owner UAT. Await authorized deployment and independent owner desktop/mobile verification. Phase 2/3 actions remain unavailable.
+Owner-reported PASS against the current approved criterion (P1-UAT-001; 2026-10-29). Proposed product changes are tracked separately and do not change this Expected Result; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md._x000D_
+P1-UAT-002 Sec. 9: Owner PASS for opening Detail from the Recipe row, distinguished from Favorite activation.</t>
+  </si>
+  <si>
+    <t>Local Recipe Core implementation and technical checks complete. Isolated browser/handler/PGlite evidence only; not live owner JWT/API or owner UAT. Await authorized deployment and independent owner desktop/mobile verification. Phase 2/3 actions remain unavailable.
+Owner-reported PASS against the current approved criterion (P1-UAT-001; 2026-10-29). Proposed product changes are tracked separately and do not change this Expected Result; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md._x000D_
+P1-UAT-002 Sec. 13: Owner PASS for single-Recipe Detail deletion.</t>
+  </si>
+  <si>
+    <t>Local Recipe Core implementation and technical checks complete. Isolated browser/handler/PGlite evidence only; not live owner JWT/API or owner UAT. Await authorized deployment and independent owner desktop/mobile verification. Phase 2/3 actions remain unavailable.
+Owner-reported PASS against the current approved criterion (P1-UAT-001; 2026-10-29). Proposed product changes are tracked separately and do not change this Expected Result; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md._x000D_
+P1-UAT-002 Sec. 13: Owner PASS for explicit confirmation before single-Recipe deletion.</t>
+  </si>
+  <si>
+    <t>Local Recipe Core implementation and technical checks complete. Isolated browser/handler/PGlite evidence only; not live owner JWT/API or owner UAT. Await authorized deployment and independent owner desktop/mobile verification. Phase 2/3 actions remain unavailable.
+Owner-reported PASS against the current approved criterion (P1-UAT-001; 2026-10-29). Proposed product changes are tracked separately and do not change this Expected Result; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md._x000D_
+P1-UAT-002 Sec. 14: Owner PASS for multi-selection management.</t>
+  </si>
+  <si>
+    <t>Local Recipe Core implementation and technical checks complete. Isolated browser/handler/PGlite evidence only; not live owner JWT/API or owner UAT. Await authorized deployment and independent owner desktop/mobile verification. Phase 2/3 actions remain unavailable.
+Owner-reported PASS against the current approved criterion (P1-UAT-001; 2026-10-29). Proposed product changes are tracked separately and do not change this Expected Result; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md._x000D_
+P1-UAT-002 Sec. 14: Owner PASS for management actions on multiple selected Recipes.</t>
+  </si>
+  <si>
+    <t>Local Recipe Core implementation and technical checks complete. Isolated browser/handler/PGlite evidence only; not live owner JWT/API or owner UAT. Await authorized deployment and independent owner desktop/mobile verification. Phase 2/3 actions remain unavailable.
+Owner-reported PASS against the current approved criterion (P1-UAT-001; 2026-10-29). Proposed product changes are tracked separately and do not change this Expected Result; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md._x000D_
+P1-UAT-002 Secs. 13-14: Owner PASS for explicit confirmation of Recipe deletion.</t>
+  </si>
+  <si>
+    <t>Local Recipe Core implementation and technical checks complete. Isolated browser/handler/PGlite evidence only; not live owner JWT/API or owner UAT. Await authorized deployment and independent owner desktop/mobile verification. Phase 2/3 actions remain unavailable.
+Owner-reported PASS against the current approved criterion (P1-UAT-001; 2026-10-29). Proposed product changes are tracked separately and do not change this Expected Result; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md._x000D_
+P1-UAT-002 Sec. 15: Owner PASS for selecting an existing Category value; CR-4/5/6 are separate.</t>
+  </si>
+  <si>
+    <t>Local Recipe Core implementation and technical checks complete. Isolated browser/handler/PGlite evidence only; not live owner JWT/API or owner UAT. Await authorized deployment and independent owner desktop/mobile verification. Phase 2/3 actions remain unavailable.
+Owner-reported PASS against the current approved criterion (P1-UAT-001; 2026-10-29). Proposed product changes are tracked separately and do not change this Expected Result; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md._x000D_
+P1-UAT-002 Sec. 15: Owner PASS for selecting an existing Cuisine value; CR-4/5/6 are separate.</t>
+  </si>
+  <si>
+    <t>Local Recipe Core implementation and technical checks complete. Isolated browser/handler/PGlite evidence only; not live owner JWT/API or owner UAT. Await authorized deployment and independent owner desktop/mobile verification. Phase 2/3 actions remain unavailable.
+Owner-reported PASS against the current approved criterion (P1-UAT-001; 2026-10-29). Proposed product changes are tracked separately and do not change this Expected Result; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md._x000D_
+P1-UAT-002 Sec. 16: Owner PASS for current valid-URL versus ordinary-text Source display; CR-7 is separate.</t>
+  </si>
+  <si>
+    <t>Local Recipe Core implementation and technical checks complete. Isolated browser/handler/PGlite evidence only; not live owner JWT/API or owner UAT. Await authorized deployment and independent owner desktop/mobile verification. Phase 2/3 actions remain unavailable.
+Owner-reported PASS against the current approved criterion (P1-UAT-001; 2026-10-29). Proposed product changes are tracked separately and do not change this Expected Result; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md._x000D_
+P1-UAT-002 Sec. 4: Owner PASS for normal Recipe Library loading.</t>
+  </si>
+  <si>
+    <t>P1-TECH-001; P1-UAT-002; P1-UAT-003</t>
+  </si>
+  <si>
+    <t>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-002; owner-reported live-web UAT; 2026-10-29; see Phase 1 Owner UAT Findings and Requirements Change Requests.md; P1-UAT-003; owner-reported live-web UAT; 2026-10-29; see Phase 1 Owner UAT Findings and Requirements Change Requests.md</t>
+  </si>
+  <si>
+    <t>Local Recipe Core implementation and technical checks complete. Isolated browser/handler/PGlite evidence only; not live owner JWT/API or owner UAT. Await authorized deployment and independent owner desktop/mobile verification. Phase 2/3 actions remain unavailable._x000D_
+P1-UAT-002 Sec. 9 reports Favorite activation PASS, but desktop execution and this row refresh/persistence check are not established; retain Ready to Test._x000D_
+P1-UAT-003 Sec. 1: Owner PASS on desktop: Favorite toggled in Library without Detail navigation, state changed, browser refreshed, and the same Recipe retained the changed state.</t>
+  </si>
+  <si>
+    <t>Local Recipe Core implementation and technical checks complete. Isolated browser/handler/PGlite evidence only; not live owner JWT/API or owner UAT. Await authorized deployment and independent owner desktop/mobile verification. Phase 2/3 actions remain unavailable._x000D_
+P1-UAT-002 Sec. 9 reports Favorite activation PASS, but mobile execution and this row refresh/persistence check are not established; retain Ready to Test._x000D_
+P1-UAT-003 Sec. 2: Owner PASS on mobile: Favorite toggled in Library without Detail navigation, state changed, page refreshed, and the same Recipe retained the changed state.</t>
+  </si>
+  <si>
+    <t>P1-TECH-001; P1-UAT-003</t>
+  </si>
+  <si>
+    <t>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-003; owner-reported live-web UAT; 2026-10-29; see Phase 1 Owner UAT Findings and Requirements Change Requests.md</t>
+  </si>
+  <si>
+    <t>Local Recipe Core implementation and technical checks complete. Isolated browser/handler/PGlite evidence only; not live owner JWT/API or owner UAT. Await authorized deployment and independent owner desktop/mobile verification. Phase 2/3 actions remain unavailable._x000D_
+P1-UAT-003 Sec. 3: Owner PASS: Recipe Detail is one continuous scrolling page without content tabs; required Recipe content remains accessible.</t>
+  </si>
+  <si>
+    <t>Local Recipe Core implementation and technical checks complete. Isolated browser/handler/PGlite evidence only; not live owner JWT/API or owner UAT. Await authorized deployment and independent owner desktop/mobile verification. Phase 2/3 actions remain unavailable._x000D_
+P1-UAT-003 Sec. 6A: Owner-approved Phase 1 deferral. Shopping and Plan Meal actions are later-phase clauses and are NOT Pass. Phase 1 Recipe actions are covered by separate accepted tests. Reassess Shopping in Phase 2 and Plan Meal in Phase 3; do not make those clauses block Phase 1.</t>
+  </si>
+  <si>
+    <t>P1-TECH-001; P1-UAT-001; P1-UAT-002; P1-UAT-003</t>
+  </si>
+  <si>
+    <t>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported partial Phase 1 verification; Shopping not tested; P1-UAT-002; owner-reported live-web UAT; 2026-10-29; see Phase 1 Owner UAT Findings and Requirements Change Requests.md; P1-UAT-003; owner-reported live-web UAT; 2026-10-29; see Phase 1 Owner UAT Findings and Requirements Change Requests.md</t>
+  </si>
+  <si>
+    <t>Local Recipe Core implementation and technical checks complete. Isolated browser/handler/PGlite evidence only; not live owner JWT/API or owner UAT. Await authorized deployment and independent owner desktop/mobile verification. Phase 2/3 actions remain unavailable.
+Owner reports Phase 1 blank-line preservation passed. The same Expected Result also requires a Shopping checklist check, which was not tested and is outside Phase 1; therefore the composite row remains Ready to Test and Shopping is not accepted. CR-1 is tracked separately._x000D_
+P1-UAT-002 Sec. 1: owner confirms approved blank-line preservation PASS. Shopping checklist clause was not tested/in Phase 1; composite row remains Ready to Test. CR-1 stays separate._x000D_
+P1-UAT-003 Sec. 6B: Owner-approved controlled split/deferral. Phase 1 multiline ingredient entry and blank-line preservation are owner-accepted (P1-UAT-001/002/003); the Shopping checklist clause is NOT Pass and remains Phase 2. Composite row deferred pending controlled test-design split/correction; preserve Test ID/Expected Result until authorized. Phase 2 traceability retained.</t>
+  </si>
+  <si>
+    <t>P1-TECH-001; P1-UAT-002; P1-TECH-002</t>
+  </si>
+  <si>
+    <t>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; Executed: node --test tests/meals-recipe-interaction.test.cjs tests/meals-recipe-service.test.cjs tests/meals-recipe-persistence.test.cjs (19 passed, 0 failed; 2026-10-29); P1-TECH-002; node --test tests/meals-recipe-interaction.test.cjs tests/meals-recipe-service.test.cjs tests/meals-recipe-persistence.test.cjs (21 passed, 0 failed); tests/meals-recipe-interaction.test.cjs: rendered STATE-002 error/Retry/recovery across Library, Detail, Editor; persisted Favorite failure/state-preservation/retry; empty/no-match recovery assertions; Local/Test deterministic mocks; 2026-10-29</t>
+  </si>
+  <si>
+    <t>Local Recipe Core implementation and technical checks complete. Isolated browser/handler/PGlite evidence only; not live owner JWT/API or owner UAT. Await authorized deployment and independent owner desktop/mobile verification. Phase 2/3 actions remain unavailable._x000D_
+P1-UAT-002 evidence review: automated Library load-error/retry path passed, but Detail/Editor error UI and rendered retry control are not asserted; retain Ready. Use only a deterministic local/Test mock, never production connectivity._x000D_
+P1-TECH-002: Deterministic local UI test verifies rendered role=alert and usable Retry followed by successful content recovery on Recipe Library, Recipe Detail, and Recipe Editor. No production connectivity changed.</t>
+  </si>
+  <si>
+    <t>Local Recipe Core implementation and technical checks complete. Isolated browser/handler/PGlite evidence only; not live owner JWT/API or owner UAT. Await authorized deployment and independent owner desktop/mobile verification. Phase 2/3 actions remain unavailable._x000D_
+P1-UAT-002 evidence review: failed create values/error/retry and service rejection are tested, but persisted Favorite/Delete UI failure, preserved visible state, and retry are not; retain Ready. Local/Test mock only._x000D_
+P1-TECH-002: Deterministic persisted-Recipe Favorite UI test verifies failed mutation is clearly unconfirmed, prior visible state remains, no navigation occurs, and retry changes visible state only after the mock persists successfully.</t>
+  </si>
+  <si>
+    <t>Prepared with deterministic run-prefixed IDs and Recipe-before-lookup cleanup in spec/meals/README.md. Local synthetic flow exercised and fixture counts returned to zero. Live owner E2E/UAT remains unexecuted pending authorized deployment. No Shopping/Planner data created.
+Owner-reported PASS in P1-UAT-001 (2026-10-29). CR-1/CR-2 remain proposed changes; Shopping was not accepted. Existing Cleanup / Reset instructions and notes are retained._x000D_
+P1-UAT-002 (2026-10-29): Owner reports UAT cleanup completed. Prior E2E status, date, and Cleanup / Reset instructions are unchanged; no production data was changed in this task._x000D_
+P1-UAT-003 (2026-10-29): Owner reports Round 3 UAT cleanup complete. Existing E2E Pass status, tested date, and Cleanup / Reset instructions are unchanged; no production data was changed in this task.</t>
+  </si>
+  <si>
+    <t>Prepared with deterministic run-prefixed IDs and Recipe-before-lookup cleanup in spec/meals/README.md. Local synthetic flow exercised and fixture counts returned to zero. Live owner E2E/UAT remains unexecuted pending authorized deployment. No Shopping/Planner data created.
+Owner-reported PASS in P1-UAT-001 (2026-10-29). CR-3 is a proposed filter enhancement; current approved filter behavior passed. Existing Cleanup / Reset instructions and notes are retained._x000D_
+P1-UAT-002 (2026-10-29): Owner reports UAT cleanup completed. Prior E2E status, date, and Cleanup / Reset instructions are unchanged; no production data was changed in this task._x000D_
+P1-UAT-003 (2026-10-29): Owner reports Round 3 UAT cleanup complete. Existing E2E Pass status, tested date, and Cleanup / Reset instructions are unchanged; no production data was changed in this task.</t>
+  </si>
+  <si>
+    <t>Delete test Recipe and unused test classification values.
+Owner-reported PASS in P1-UAT-001 (2026-10-29) against current referenced-delete requirements. CR-4/CR-5/CR-6 are proposals; CR-6 is optional. Existing Cleanup / Reset instructions and notes are retained._x000D_
+P1-UAT-002 (2026-10-29): Owner reports UAT cleanup completed. Prior E2E status, date, and Cleanup / Reset instructions are unchanged; no production data was changed in this task._x000D_
+P1-UAT-003 (2026-10-29): Owner reports Round 3 UAT cleanup complete. Existing E2E Pass status, tested date, and Cleanup / Reset instructions are unchanged; no production data was changed in this task.</t>
+  </si>
+  <si>
+    <t>P1-TECH-001; P1-UAT-002; P1-UAT-003; P1-UAT-004</t>
+  </si>
+  <si>
+    <t>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-002; owner-reported live-web UAT; 2026-10-29; see Phase 1 Owner UAT Findings and Requirements Change Requests.md; P1-UAT-003; owner-reported live-web UAT; 2026-10-29; see Phase 1 Owner UAT Findings and Requirements Change Requests.md; P1-UAT-004; owner-reported true-empty Recipe Library PASS; 2026-10-29; Round 4 record in Phase 1 Owner UAT Findings and Requirements Change Requests.md</t>
+  </si>
+  <si>
+    <t>Local Recipe Core implementation and technical checks complete. Isolated browser/handler/PGlite evidence only; not live owner JWT/API or owner UAT. Await authorized deployment and independent owner desktop/mobile verification. Phase 2/3 actions remain unavailable._x000D_
+P1-UAT-002 Sec. 10 reports empty/no-match PASS, but desktop execution of both states/recovery is not identified; automation does not test viewport. Retain Ready to Test._x000D_
+P1-UAT-003 Sec. 4: Owner PARTIAL; desktop zero-match state/recovery PASS; true-empty visual state was not tested. Executed local automation proves true-empty message, Add Recipe recovery, distinction from zero-match, and clear-filter recovery. Desktop true-empty visual confirmation remains._x000D_
+P1-UAT-004 (2026-10-29): Owner verified the Recipe Library was genuinely empty; the desktop true-empty state was clearly presented; Add Recipe was available; the true-empty state was distinct from the previously tested desktop zero-match state; desktop presentation remained usable. Combined with preserved P1-UAT-003 viewport-specific zero-match/recovery and previously executed technical true-empty/Add Recipe/distinction/clear-filter evidence, the complete unchanged Expected Result is proven. Owner result PASS.</t>
+  </si>
+  <si>
+    <t>Local Recipe Core implementation and technical checks complete. Isolated browser/handler/PGlite evidence only; not live owner JWT/API or owner UAT. Await authorized deployment and independent owner desktop/mobile verification. Phase 2/3 actions remain unavailable._x000D_
+P1-UAT-002 Sec. 10 reports empty/no-match PASS, but mobile execution of both states/recovery is not identified; automation does not test viewport. Retain Ready to Test._x000D_
+P1-UAT-003 Sec. 5: Owner PARTIAL; mobile zero-match state/recovery PASS; true-empty visual state was not tested. Executed local automation proves true-empty message, Add Recipe recovery, distinction from zero-match, and clear-filter recovery. Mobile true-empty visual confirmation remains._x000D_
+P1-UAT-004 (2026-10-29): Owner verified the Recipe Library was genuinely empty; the mobile true-empty state was clearly presented; Add Recipe was visible and touch-usable; the true-empty state was distinct from the previously tested mobile zero-match state; mobile presentation remained usable. Combined with preserved P1-UAT-003 viewport-specific zero-match/recovery and previously executed technical true-empty/Add Recipe/distinction/clear-filter evidence, the complete unchanged Expected Result is proven. Owner result PASS.</t>
+  </si>
+  <si>
+    <t>P1-UAT-001 (2026-10-29): Owner-reported PASS for Phase 0 routing/existing-module regression. The owner report did not identify specific regression Test IDs or attach separate evidence.
+P1-UAT-002 (2026-10-29): Owner-reported overall PASS; no owner-reported issues/untested items. Evidence-specific Ready-to-Test rows and CR-1 through CR-8 are documented separately. Final Decision remains Not Started.
+P1-UAT-003 (2026-10-29): Owner overall result PARTIAL; no owner-observed issues. Desktop and mobile true-empty visual presentation were untested. Zero-match passed on both viewports. Mixed-scope rows Deferred with owner approval; Phase 1 Final Decision remains Not Started.
+P1-UAT-004 (2026-10-29): PHASE 1 OWNER UAT ROUND 4. Desktop true-empty Recipe Library: PASS (STATE-004-T01-D). Mobile true-empty Recipe Library: PASS (STATE-004-T01-M). Combined with preserved prior zero-match and technical empty-state evidence, both complete Expected Results are proven and both rows are Pass. Overall owner result: PASS. Remaining owner-observed issues: None. Cleanup completed: YES. No Phase 1 Ready-to-Test, Fail, or Blocked rows remain. RD-UI-005-T01 and RE-FUNC-006-T01 remain Deferred; RL-FUNC-020-T01 Recipe Import remains Not Built and outside Phase 1 acceptance. CR-1 through CR-8 remain unchanged and non-blocking. Phase 1 Final Decision remains Not Started and owner-controlled.
+Owner authorized 2026-10-29: Phase 1 Accepted for the current approved Recipe Core scope, based on preserved P1-UAT-001 through P1-UAT-004, P1-TECH-002, passing required E2E and Regression evidence, and no in-scope Ready-to-Test, Fail, or Blocked rows. Shopping, Plan Meal, Planner, and Recipe Import remain excluded. RD-UI-005-T01 and RE-FUNC-006-T01 remain Deferred. CR-1 through CR-8 remain separately documented future work.</t>
   </si>
 </sst>
 </file>
@@ -3699,7 +3922,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3723,6 +3946,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4743,6 +4967,7 @@
         <v>29</v>
       </c>
     </row>
+    <row r="20" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="21" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>30</v>
@@ -4769,9 +4994,9 @@
   <dimension ref="A1:Q27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="1" max="1" width="47.5703125" customWidth="1"/>
     <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="3" max="3" width="31.85546875" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="12" width="16" customWidth="1"/>
     <col min="13" max="13" width="37" customWidth="1"/>
@@ -4883,7 +5108,7 @@
       </c>
       <c r="C7" s="5">
         <f>COUNTIF('Functional Acceptance'!$L:$L,"Pass")</f>
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="D7" s="5">
         <f>COUNTIF('Functional Acceptance'!$L:$L,"Pass with Known Issue")</f>
@@ -4899,7 +5124,7 @@
       </c>
       <c r="G7" s="5">
         <f>COUNTIF('Functional Acceptance'!$L:$L,"Ready to Test")</f>
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="H7" s="5">
         <f>COUNTIF('Functional Acceptance'!$L:$L,"Not Built")</f>
@@ -4907,7 +5132,7 @@
       </c>
       <c r="I7" s="5">
         <f>COUNTIF('Functional Acceptance'!$L:$L,"Deferred")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4920,7 +5145,7 @@
       </c>
       <c r="C8" s="5">
         <f>COUNTIF('End-to-End Tests'!$J:$J,"Pass")</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D8" s="5">
         <f>COUNTIF('End-to-End Tests'!$J:$J,"Pass with Known Issue")</f>
@@ -4936,7 +5161,7 @@
       </c>
       <c r="G8" s="5">
         <f>COUNTIF('End-to-End Tests'!$J:$J,"Ready to Test")</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H8" s="5">
         <f>COUNTIF('End-to-End Tests'!$J:$J,"Not Built")</f>
@@ -5161,6 +5386,8 @@
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
     </row>
+    <row r="20" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="22" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>45</v>
@@ -5264,13 +5491,13 @@
         <v>70</v>
       </c>
       <c r="O23" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="P23" s="2" t="s">
         <v>1129</v>
       </c>
-      <c r="P23" s="2" t="s">
+      <c r="Q23" s="2" t="s">
         <v>1130</v>
-      </c>
-      <c r="Q23" s="2" t="s">
-        <v>1131</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5289,7 +5516,7 @@
       </c>
       <c r="E24" s="2">
         <f>COUNTIFS('Functional Acceptance'!D:D,A24,'Functional Acceptance'!L:L,"Pass")+COUNTIFS('Security Acceptance'!D:D,A24,'Security Acceptance'!N:N,"Pass")+COUNTIFS('Database Verification'!D:D,A24,'Database Verification'!N:N,"Pass")+COUNTIFS('End-to-End Tests'!C:C,A24,'End-to-End Tests'!J:J,"Pass")</f>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="F24" s="2">
         <f>COUNTIFS('Functional Acceptance'!D:D,A24,'Functional Acceptance'!L:L,"Pass with Known Issue")+COUNTIFS('Security Acceptance'!D:D,A24,'Security Acceptance'!N:N,"Pass with Known Issue")+COUNTIFS('Database Verification'!D:D,A24,'Database Verification'!N:N,"Pass with Known Issue")+COUNTIFS('End-to-End Tests'!C:C,A24,'End-to-End Tests'!J:J,"Pass with Known Issue")</f>
@@ -5305,7 +5532,7 @@
       </c>
       <c r="I24" s="2">
         <f>COUNTIFS('Functional Acceptance'!D:D,A24,'Functional Acceptance'!L:L,"Deferred")+COUNTIFS('Security Acceptance'!D:D,A24,'Security Acceptance'!N:N,"Deferred")+COUNTIFS('Database Verification'!D:D,A24,'Database Verification'!N:N,"Deferred")+COUNTIFS('End-to-End Tests'!C:C,A24,'End-to-End Tests'!J:J,"Deferred")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>70</v>
@@ -5320,13 +5547,17 @@
         <v>73</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="P24" s="2"/>
-      <c r="Q24" s="2"/>
+        <v>1128</v>
+      </c>
+      <c r="P24" s="9">
+        <v>46324</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>1211</v>
+      </c>
     </row>
     <row r="25" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
@@ -5583,7 +5814,7 @@
     </row>
     <row r="2" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>94</v>
@@ -5622,18 +5853,18 @@
         <v>46323</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="O2" s="2" t="s">
+        <v>1119</v>
+      </c>
+      <c r="P2" s="2" t="s">
         <v>1120</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>1121</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>103</v>
@@ -5673,15 +5904,15 @@
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>107</v>
@@ -5721,15 +5952,15 @@
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>112</v>
@@ -5769,15 +6000,15 @@
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>116</v>
@@ -5810,20 +6041,22 @@
         <v>119</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M6" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M6" s="7">
+        <v>46324</v>
+      </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>120</v>
@@ -5856,15 +6089,17 @@
         <v>123</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M7" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M7" s="7">
+        <v>46324</v>
+      </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -5909,7 +6144,7 @@
     </row>
     <row r="9" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>128</v>
@@ -5949,15 +6184,15 @@
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>132</v>
@@ -5990,20 +6225,22 @@
         <v>139</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M10" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M10" s="7">
+        <v>46324</v>
+      </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>140</v>
@@ -6036,20 +6273,22 @@
         <v>139</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M11" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M11" s="7">
+        <v>46324</v>
+      </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>1156</v>
+        <v>1173</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>143</v>
@@ -6082,20 +6321,22 @@
         <v>146</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M12" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M12" s="7">
+        <v>46324</v>
+      </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>1155</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>1156</v>
+        <v>1173</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>147</v>
@@ -6128,20 +6369,22 @@
         <v>150</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M13" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M13" s="7">
+        <v>46324</v>
+      </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>1155</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>151</v>
@@ -6174,20 +6417,22 @@
         <v>154</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M14" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M14" s="7">
+        <v>46324</v>
+      </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>155</v>
@@ -6220,20 +6465,22 @@
         <v>159</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M15" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M15" s="7">
+        <v>46324</v>
+      </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>160</v>
@@ -6266,20 +6513,22 @@
         <v>164</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M16" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M16" s="7">
+        <v>46324</v>
+      </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>165</v>
@@ -6312,20 +6561,22 @@
         <v>168</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M17" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M17" s="7">
+        <v>46324</v>
+      </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>169</v>
@@ -6358,20 +6609,22 @@
         <v>172</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M18" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M18" s="7">
+        <v>46324</v>
+      </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="19" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>173</v>
@@ -6404,20 +6657,22 @@
         <v>176</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M19" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M19" s="7">
+        <v>46324</v>
+      </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>1156</v>
+        <v>1161</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>177</v>
@@ -6450,20 +6705,22 @@
         <v>180</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M20" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M20" s="7">
+        <v>46324</v>
+      </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2" t="s">
-        <v>1157</v>
+        <v>1162</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>1155</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="21" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>181</v>
@@ -6496,20 +6753,22 @@
         <v>184</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M21" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M21" s="7">
+        <v>46324</v>
+      </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>1156</v>
+        <v>1189</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>185</v>
@@ -6542,20 +6801,22 @@
         <v>189</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M22" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M22" s="7">
+        <v>46324</v>
+      </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2" t="s">
-        <v>1157</v>
+        <v>1190</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>1155</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>1156</v>
+        <v>1189</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>190</v>
@@ -6588,20 +6849,22 @@
         <v>189</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M23" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M23" s="7">
+        <v>46324</v>
+      </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2" t="s">
-        <v>1157</v>
+        <v>1190</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>1155</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>1156</v>
+        <v>1173</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>191</v>
@@ -6634,20 +6897,22 @@
         <v>194</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M24" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M24" s="7">
+        <v>46324</v>
+      </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>1155</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>1156</v>
+        <v>1173</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>195</v>
@@ -6680,20 +6945,22 @@
         <v>198</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M25" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M25" s="7">
+        <v>46324</v>
+      </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>1155</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>1156</v>
+        <v>1173</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>199</v>
@@ -6726,15 +6993,17 @@
         <v>202</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M26" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M26" s="7">
+        <v>46324</v>
+      </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>1155</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -6859,7 +7128,7 @@
     </row>
     <row r="30" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>215</v>
@@ -6892,20 +7161,22 @@
         <v>218</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M30" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M30" s="7">
+        <v>46324</v>
+      </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="31" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>219</v>
@@ -6938,20 +7209,22 @@
         <v>222</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M31" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M31" s="7">
+        <v>46324</v>
+      </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="32" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>223</v>
@@ -6984,20 +7257,22 @@
         <v>227</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M32" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M32" s="7">
+        <v>46324</v>
+      </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="33" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>1156</v>
+        <v>1173</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>228</v>
@@ -7030,20 +7305,22 @@
         <v>231</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M33" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M33" s="7">
+        <v>46324</v>
+      </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>1155</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="34" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>1156</v>
+        <v>1173</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>232</v>
@@ -7076,20 +7353,22 @@
         <v>236</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M34" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M34" s="7">
+        <v>46324</v>
+      </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>1155</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="35" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>1156</v>
+        <v>1161</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>237</v>
@@ -7122,15 +7401,17 @@
         <v>240</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M35" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M35" s="7">
+        <v>46324</v>
+      </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2" t="s">
-        <v>1157</v>
+        <v>1162</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>1155</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="36" spans="1:16" ht="105" customHeight="1" x14ac:dyDescent="0.25">
@@ -7175,7 +7456,7 @@
     </row>
     <row r="37" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>1156</v>
+        <v>1193</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>245</v>
@@ -7208,20 +7489,22 @@
         <v>249</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M37" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M37" s="7">
+        <v>46324</v>
+      </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2" t="s">
-        <v>1157</v>
+        <v>1194</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>1155</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="38" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>1156</v>
+        <v>1161</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>250</v>
@@ -7254,20 +7537,22 @@
         <v>249</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M38" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M38" s="7">
+        <v>46324</v>
+      </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2" t="s">
-        <v>1157</v>
+        <v>1162</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="39" spans="1:16" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>1156</v>
+        <v>1173</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>251</v>
@@ -7300,20 +7585,22 @@
         <v>254</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M39" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M39" s="7">
+        <v>46324</v>
+      </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>1155</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="40" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>255</v>
@@ -7346,20 +7633,22 @@
         <v>258</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M40" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M40" s="7">
+        <v>46324</v>
+      </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="41" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>259</v>
@@ -7392,15 +7681,17 @@
         <v>262</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M41" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M41" s="7">
+        <v>46324</v>
+      </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="42" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -7485,7 +7776,7 @@
     </row>
     <row r="44" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>271</v>
@@ -7518,20 +7809,22 @@
         <v>274</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M44" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M44" s="7">
+        <v>46324</v>
+      </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="P44" s="2" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="45" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>275</v>
@@ -7564,20 +7857,22 @@
         <v>278</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M45" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M45" s="7">
+        <v>46324</v>
+      </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="46" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>1156</v>
+        <v>1173</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>279</v>
@@ -7610,20 +7905,22 @@
         <v>282</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M46" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M46" s="7">
+        <v>46324</v>
+      </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>1155</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="47" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>1156</v>
+        <v>1193</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>283</v>
@@ -7656,15 +7953,17 @@
         <v>286</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M47" s="7"/>
+        <v>16</v>
+      </c>
+      <c r="M47" s="7">
+        <v>46324</v>
+      </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2" t="s">
-        <v>1157</v>
+        <v>1194</v>
       </c>
       <c r="P47" s="2" t="s">
-        <v>1155</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="48" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7749,7 +8048,7 @@
     </row>
     <row r="50" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>295</v>
@@ -7782,20 +8081,22 @@
         <v>299</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M50" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M50" s="7">
+        <v>46324</v>
+      </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="51" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>300</v>
@@ -7828,20 +8129,22 @@
         <v>304</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M51" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M51" s="7">
+        <v>46324</v>
+      </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="52" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>305</v>
@@ -7874,20 +8177,22 @@
         <v>308</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M52" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M52" s="7">
+        <v>46324</v>
+      </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="P52" s="2" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="53" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>309</v>
@@ -7920,20 +8225,22 @@
         <v>312</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M53" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M53" s="7">
+        <v>46324</v>
+      </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="P53" s="2" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="54" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>313</v>
@@ -7966,20 +8273,22 @@
         <v>316</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M54" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M54" s="7">
+        <v>46324</v>
+      </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="55" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>317</v>
@@ -8012,20 +8321,22 @@
         <v>320</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M55" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M55" s="7">
+        <v>46324</v>
+      </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="P55" s="2" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="56" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>1156</v>
+        <v>1173</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>321</v>
@@ -8058,20 +8369,22 @@
         <v>324</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M56" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M56" s="7">
+        <v>46324</v>
+      </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>1155</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="57" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>325</v>
@@ -8104,20 +8417,22 @@
         <v>328</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M57" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M57" s="7">
+        <v>46324</v>
+      </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="58" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>1156</v>
+        <v>1173</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>329</v>
@@ -8150,20 +8465,22 @@
         <v>332</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M58" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M58" s="7">
+        <v>46324</v>
+      </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>1155</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="59" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>333</v>
@@ -8196,20 +8513,22 @@
         <v>336</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M59" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M59" s="7">
+        <v>46324</v>
+      </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="P59" s="2" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="60" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>337</v>
@@ -8242,20 +8561,22 @@
         <v>340</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M60" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M60" s="7">
+        <v>46324</v>
+      </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="P60" s="2" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="61" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>341</v>
@@ -8288,20 +8609,22 @@
         <v>344</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M61" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M61" s="7">
+        <v>46324</v>
+      </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="P61" s="2" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="62" spans="1:16" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>1156</v>
+        <v>1197</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>345</v>
@@ -8334,20 +8657,22 @@
         <v>349</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M62" s="7"/>
+        <v>16</v>
+      </c>
+      <c r="M62" s="7">
+        <v>46324</v>
+      </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2" t="s">
-        <v>1157</v>
+        <v>1198</v>
       </c>
       <c r="P62" s="2" t="s">
-        <v>1155</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="63" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>350</v>
@@ -8380,20 +8705,22 @@
         <v>353</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M63" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M63" s="7">
+        <v>46324</v>
+      </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="P63" s="2" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="64" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>1156</v>
+        <v>1161</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>354</v>
@@ -8426,20 +8753,22 @@
         <v>357</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M64" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M64" s="7">
+        <v>46324</v>
+      </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2" t="s">
-        <v>1157</v>
+        <v>1162</v>
       </c>
       <c r="P64" s="2" t="s">
-        <v>1155</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="65" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>358</v>
@@ -8472,20 +8801,22 @@
         <v>361</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M65" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M65" s="7">
+        <v>46324</v>
+      </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="P65" s="2" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="66" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>1156</v>
+        <v>1161</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>362</v>
@@ -8518,20 +8849,22 @@
         <v>365</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M66" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M66" s="7">
+        <v>46324</v>
+      </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2" t="s">
-        <v>1157</v>
+        <v>1162</v>
       </c>
       <c r="P66" s="2" t="s">
-        <v>1155</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="67" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>1156</v>
+        <v>1161</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>366</v>
@@ -8564,20 +8897,22 @@
         <v>365</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M67" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M67" s="7">
+        <v>46324</v>
+      </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2" t="s">
-        <v>1157</v>
+        <v>1162</v>
       </c>
       <c r="P67" s="2" t="s">
-        <v>1155</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="68" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>367</v>
@@ -8610,20 +8945,22 @@
         <v>370</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M68" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M68" s="7">
+        <v>46324</v>
+      </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="P68" s="2" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="69" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>1156</v>
+        <v>1161</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>371</v>
@@ -8656,20 +8993,22 @@
         <v>375</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M69" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M69" s="7">
+        <v>46324</v>
+      </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2" t="s">
-        <v>1157</v>
+        <v>1162</v>
       </c>
       <c r="P69" s="2" t="s">
-        <v>1155</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="70" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>1156</v>
+        <v>1161</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>376</v>
@@ -8702,20 +9041,22 @@
         <v>379</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M70" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M70" s="7">
+        <v>46324</v>
+      </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2" t="s">
-        <v>1157</v>
+        <v>1162</v>
       </c>
       <c r="P70" s="2" t="s">
-        <v>1155</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="71" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>1156</v>
+        <v>1161</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>380</v>
@@ -8748,20 +9089,22 @@
         <v>384</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M71" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M71" s="7">
+        <v>46324</v>
+      </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2" t="s">
-        <v>1157</v>
+        <v>1167</v>
       </c>
       <c r="P71" s="2" t="s">
-        <v>1155</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="72" spans="1:16" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>385</v>
@@ -8794,20 +9137,22 @@
         <v>389</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M72" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M72" s="7">
+        <v>46324</v>
+      </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="P72" s="2" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="73" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>390</v>
@@ -8840,20 +9185,22 @@
         <v>393</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M73" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M73" s="7">
+        <v>46324</v>
+      </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="P73" s="2" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="74" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>394</v>
@@ -8886,15 +9233,17 @@
         <v>397</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M74" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M74" s="7">
+        <v>46324</v>
+      </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="P74" s="2" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="75" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -12419,7 +12768,7 @@
     </row>
     <row r="163" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>765</v>
@@ -12459,15 +12808,15 @@
       </c>
       <c r="N163" s="2"/>
       <c r="O163" s="2" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="P163" s="2" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="164" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>771</v>
@@ -12507,15 +12856,15 @@
       </c>
       <c r="N164" s="2"/>
       <c r="O164" s="2" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="P164" s="2" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="165" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
-        <v>1156</v>
+        <v>1173</v>
       </c>
       <c r="B165" s="2" t="s">
         <v>772</v>
@@ -12548,20 +12897,22 @@
         <v>775</v>
       </c>
       <c r="L165" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M165" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M165" s="7">
+        <v>46324</v>
+      </c>
       <c r="N165" s="2"/>
       <c r="O165" s="2" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="P165" s="2" t="s">
-        <v>1155</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="166" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
-        <v>1156</v>
+        <v>1173</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>776</v>
@@ -12594,20 +12945,22 @@
         <v>779</v>
       </c>
       <c r="L166" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M166" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M166" s="7">
+        <v>46324</v>
+      </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="P166" s="2" t="s">
-        <v>1155</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="167" spans="1:16" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
-        <v>1156</v>
+        <v>1161</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>780</v>
@@ -12640,20 +12993,22 @@
         <v>784</v>
       </c>
       <c r="L167" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M167" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M167" s="7">
+        <v>46324</v>
+      </c>
       <c r="N167" s="2"/>
       <c r="O167" s="2" t="s">
-        <v>1157</v>
+        <v>1162</v>
       </c>
       <c r="P167" s="2" t="s">
-        <v>1155</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="168" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
-        <v>1156</v>
+        <v>1200</v>
       </c>
       <c r="B168" s="2" t="s">
         <v>785</v>
@@ -12686,20 +13041,22 @@
         <v>788</v>
       </c>
       <c r="L168" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M168" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M168" s="7">
+        <v>46324</v>
+      </c>
       <c r="N168" s="2"/>
       <c r="O168" s="2" t="s">
-        <v>1157</v>
+        <v>1201</v>
       </c>
       <c r="P168" s="2" t="s">
-        <v>1155</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="169" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>1156</v>
+        <v>1161</v>
       </c>
       <c r="B169" s="2" t="s">
         <v>789</v>
@@ -12732,20 +13089,22 @@
         <v>792</v>
       </c>
       <c r="L169" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M169" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M169" s="7">
+        <v>46324</v>
+      </c>
       <c r="N169" s="2"/>
       <c r="O169" s="2" t="s">
-        <v>1157</v>
+        <v>1167</v>
       </c>
       <c r="P169" s="2" t="s">
-        <v>1155</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="170" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
-        <v>1156</v>
+        <v>1207</v>
       </c>
       <c r="B170" s="2" t="s">
         <v>793</v>
@@ -12778,20 +13137,22 @@
         <v>796</v>
       </c>
       <c r="L170" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M170" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M170" s="7">
+        <v>46324</v>
+      </c>
       <c r="N170" s="2"/>
       <c r="O170" s="2" t="s">
-        <v>1157</v>
+        <v>1208</v>
       </c>
       <c r="P170" s="2" t="s">
-        <v>1155</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="171" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
-        <v>1156</v>
+        <v>1207</v>
       </c>
       <c r="B171" s="2" t="s">
         <v>797</v>
@@ -12824,20 +13185,22 @@
         <v>796</v>
       </c>
       <c r="L171" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M171" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M171" s="7">
+        <v>46324</v>
+      </c>
       <c r="N171" s="2"/>
       <c r="O171" s="2" t="s">
-        <v>1157</v>
+        <v>1208</v>
       </c>
       <c r="P171" s="2" t="s">
-        <v>1155</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="172" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
-        <v>1156</v>
+        <v>1173</v>
       </c>
       <c r="B172" s="2" t="s">
         <v>798</v>
@@ -12870,15 +13233,17 @@
         <v>801</v>
       </c>
       <c r="L172" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M172" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M172" s="7">
+        <v>46324</v>
+      </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="P172" s="2" t="s">
-        <v>1155</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="173" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12923,7 +13288,7 @@
     </row>
     <row r="174" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
-        <v>1156</v>
+        <v>1200</v>
       </c>
       <c r="B174" s="2" t="s">
         <v>806</v>
@@ -12956,15 +13321,17 @@
         <v>809</v>
       </c>
       <c r="L174" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M174" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="M174" s="7">
+        <v>46324</v>
+      </c>
       <c r="N174" s="2"/>
       <c r="O174" s="2" t="s">
-        <v>1157</v>
+        <v>1201</v>
       </c>
       <c r="P174" s="2" t="s">
-        <v>1155</v>
+        <v>1203</v>
       </c>
     </row>
   </sheetData>
@@ -13117,7 +13484,7 @@
     </row>
     <row r="2" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>812</v>
@@ -13163,15 +13530,15 @@
       </c>
       <c r="P2" s="2"/>
       <c r="Q2" s="2" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>822</v>
@@ -13215,15 +13582,15 @@
       <c r="O3" s="7"/>
       <c r="P3" s="2"/>
       <c r="Q3" s="2" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>827</v>
@@ -13265,19 +13632,19 @@
         <v>10</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="P4" s="2"/>
       <c r="Q4" s="2" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>832</v>
@@ -13321,15 +13688,15 @@
       <c r="O5" s="7"/>
       <c r="P5" s="2"/>
       <c r="Q5" s="2" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>836</v>
@@ -13373,15 +13740,15 @@
       <c r="O6" s="7"/>
       <c r="P6" s="2"/>
       <c r="Q6" s="2" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>840</v>
@@ -13427,15 +13794,15 @@
       </c>
       <c r="P7" s="2"/>
       <c r="Q7" s="2" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>845</v>
@@ -13481,15 +13848,15 @@
       </c>
       <c r="P8" s="2"/>
       <c r="Q8" s="2" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>849</v>
@@ -13535,15 +13902,15 @@
       </c>
       <c r="P9" s="2"/>
       <c r="Q9" s="2" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>853</v>
@@ -13585,19 +13952,19 @@
         <v>10</v>
       </c>
       <c r="O10" s="7" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="P10" s="2"/>
       <c r="Q10" s="2" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>857</v>
@@ -13641,15 +14008,15 @@
       <c r="O11" s="7"/>
       <c r="P11" s="2"/>
       <c r="Q11" s="2" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>861</v>
@@ -13693,15 +14060,15 @@
       <c r="O12" s="7"/>
       <c r="P12" s="2"/>
       <c r="Q12" s="2" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>865</v>
@@ -13747,15 +14114,15 @@
       </c>
       <c r="P13" s="2"/>
       <c r="Q13" s="2" t="s">
+        <v>1155</v>
+      </c>
+      <c r="R13" s="2" t="s">
         <v>1157</v>
-      </c>
-      <c r="R13" s="2" t="s">
-        <v>1160</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>869</v>
@@ -13799,15 +14166,15 @@
       <c r="O14" s="7"/>
       <c r="P14" s="2"/>
       <c r="Q14" s="2" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>876</v>
@@ -13851,10 +14218,10 @@
       <c r="O15" s="7"/>
       <c r="P15" s="2"/>
       <c r="Q15" s="2" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -13905,7 +14272,7 @@
     </row>
     <row r="17" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>884</v>
@@ -13949,15 +14316,15 @@
       <c r="O17" s="7"/>
       <c r="P17" s="2"/>
       <c r="Q17" s="2" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>888</v>
@@ -14001,15 +14368,15 @@
       <c r="O18" s="7"/>
       <c r="P18" s="2"/>
       <c r="Q18" s="2" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>892</v>
@@ -14055,10 +14422,10 @@
       </c>
       <c r="P19" s="2"/>
       <c r="Q19" s="2" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="20" spans="1:18" ht="90" customHeight="1" x14ac:dyDescent="0.25">
@@ -14109,7 +14476,7 @@
     </row>
     <row r="21" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>900</v>
@@ -14151,19 +14518,19 @@
         <v>10</v>
       </c>
       <c r="O21" s="7" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="P21" s="2"/>
       <c r="Q21" s="2" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="22" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>904</v>
@@ -14209,10 +14576,10 @@
       </c>
       <c r="P22" s="2"/>
       <c r="Q22" s="2" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="23" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -14419,7 +14786,7 @@
     </row>
     <row r="2" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>925</v>
@@ -14434,10 +14801,10 @@
         <v>814</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>1133</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>1134</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>926</v>
@@ -14446,7 +14813,7 @@
         <v>98</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>927</v>
@@ -14461,7 +14828,7 @@
         <v>10</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>927</v>
@@ -14470,12 +14837,12 @@
         <v>929</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>930</v>
@@ -14490,10 +14857,10 @@
         <v>814</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>1133</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>1134</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>926</v>
@@ -14502,7 +14869,7 @@
         <v>98</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>927</v>
@@ -14517,7 +14884,7 @@
         <v>10</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>927</v>
@@ -14526,7 +14893,7 @@
         <v>929</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -14575,7 +14942,7 @@
     </row>
     <row r="5" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>934</v>
@@ -14590,10 +14957,10 @@
         <v>814</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>1133</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>1134</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>926</v>
@@ -14602,7 +14969,7 @@
         <v>98</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>927</v>
@@ -14617,7 +14984,7 @@
         <v>10</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>927</v>
@@ -14626,7 +14993,7 @@
         <v>929</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -14675,7 +15042,7 @@
     </row>
     <row r="7" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>936</v>
@@ -14690,10 +15057,10 @@
         <v>814</v>
       </c>
       <c r="F7" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>1133</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>1134</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>926</v>
@@ -14702,7 +15069,7 @@
         <v>98</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>929</v>
@@ -14717,7 +15084,7 @@
         <v>10</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>927</v>
@@ -14726,12 +15093,12 @@
         <v>929</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>939</v>
@@ -14746,10 +15113,10 @@
         <v>941</v>
       </c>
       <c r="F8" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>1133</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>1134</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>926</v>
@@ -14758,7 +15125,7 @@
         <v>98</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>927</v>
@@ -14773,7 +15140,7 @@
         <v>10</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>927</v>
@@ -14782,12 +15149,12 @@
         <v>929</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>943</v>
@@ -14802,10 +15169,10 @@
         <v>941</v>
       </c>
       <c r="F9" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>1133</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>1134</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>926</v>
@@ -14814,7 +15181,7 @@
         <v>98</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>927</v>
@@ -14829,7 +15196,7 @@
         <v>10</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>927</v>
@@ -14838,12 +15205,12 @@
         <v>929</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>946</v>
@@ -14858,10 +15225,10 @@
         <v>941</v>
       </c>
       <c r="F10" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>1133</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>1134</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>926</v>
@@ -14870,7 +15237,7 @@
         <v>98</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>929</v>
@@ -14885,7 +15252,7 @@
         <v>10</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>927</v>
@@ -14894,12 +15261,12 @@
         <v>929</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>949</v>
@@ -14914,10 +15281,10 @@
         <v>941</v>
       </c>
       <c r="F11" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>1133</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>1134</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>926</v>
@@ -14926,7 +15293,7 @@
         <v>98</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>927</v>
@@ -14941,7 +15308,7 @@
         <v>10</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>927</v>
@@ -14950,7 +15317,7 @@
         <v>929</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -14999,7 +15366,7 @@
     </row>
     <row r="13" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>955</v>
@@ -15014,10 +15381,10 @@
         <v>941</v>
       </c>
       <c r="F13" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>1133</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>1134</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>926</v>
@@ -15026,7 +15393,7 @@
         <v>98</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>927</v>
@@ -15041,7 +15408,7 @@
         <v>10</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>927</v>
@@ -15050,12 +15417,12 @@
         <v>929</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>958</v>
@@ -15070,10 +15437,10 @@
         <v>941</v>
       </c>
       <c r="F14" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>1133</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>1134</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>926</v>
@@ -15082,7 +15449,7 @@
         <v>98</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>927</v>
@@ -15097,7 +15464,7 @@
         <v>10</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>927</v>
@@ -15106,7 +15473,7 @@
         <v>929</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -15243,7 +15610,7 @@
     </row>
     <row r="18" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>970</v>
@@ -15258,10 +15625,10 @@
         <v>941</v>
       </c>
       <c r="F18" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>1133</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>1134</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>926</v>
@@ -15270,7 +15637,7 @@
         <v>98</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>927</v>
@@ -15285,7 +15652,7 @@
         <v>10</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>927</v>
@@ -15294,12 +15661,12 @@
         <v>929</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>973</v>
@@ -15314,10 +15681,10 @@
         <v>941</v>
       </c>
       <c r="F19" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="G19" s="2" t="s">
         <v>1133</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>1134</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>926</v>
@@ -15326,7 +15693,7 @@
         <v>98</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>927</v>
@@ -15341,7 +15708,7 @@
         <v>10</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="P19" s="2" t="s">
         <v>927</v>
@@ -15350,12 +15717,12 @@
         <v>929</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="20" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>976</v>
@@ -15370,10 +15737,10 @@
         <v>941</v>
       </c>
       <c r="F20" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>1133</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>1134</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>926</v>
@@ -15382,7 +15749,7 @@
         <v>98</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>929</v>
@@ -15397,7 +15764,7 @@
         <v>10</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>927</v>
@@ -15406,12 +15773,12 @@
         <v>929</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="21" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>979</v>
@@ -15426,10 +15793,10 @@
         <v>980</v>
       </c>
       <c r="F21" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>1133</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>1134</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>926</v>
@@ -15438,7 +15805,7 @@
         <v>98</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>927</v>
@@ -15453,7 +15820,7 @@
         <v>10</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>927</v>
@@ -15462,12 +15829,12 @@
         <v>929</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="22" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>983</v>
@@ -15482,10 +15849,10 @@
         <v>984</v>
       </c>
       <c r="F22" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>1133</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>1134</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>926</v>
@@ -15494,7 +15861,7 @@
         <v>98</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>929</v>
@@ -15509,7 +15876,7 @@
         <v>10</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>927</v>
@@ -15518,7 +15885,7 @@
         <v>929</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
   </sheetData>
@@ -15669,7 +16036,7 @@
     </row>
     <row r="2" spans="1:15" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>992</v>
@@ -15703,16 +16070,16 @@
       </c>
       <c r="L2" s="2"/>
       <c r="M2" s="2" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>998</v>
@@ -15739,23 +16106,25 @@
         <v>1003</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K3" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="K3" s="7">
+        <v>46324</v>
+      </c>
       <c r="L3" s="2"/>
       <c r="M3" s="2" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>1004</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>1158</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>1005</v>
@@ -15782,18 +16151,20 @@
         <v>1010</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K4" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="K4" s="7">
+        <v>46324</v>
+      </c>
       <c r="L4" s="2"/>
       <c r="M4" s="2" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>1004</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>1158</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="90" customHeight="1" x14ac:dyDescent="0.25">
@@ -16057,7 +16428,7 @@
     </row>
     <row r="12" spans="1:15" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>1052</v>
@@ -16084,22 +16455,24 @@
         <v>1057</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K12" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="K12" s="7">
+        <v>46324</v>
+      </c>
       <c r="L12" s="2"/>
       <c r="M12" s="2" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2" t="s">
-        <v>1058</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>52</v>
@@ -16108,19 +16481,19 @@
         <v>98</v>
       </c>
       <c r="E13" s="2" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>1060</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="G13" s="2" t="s">
         <v>1061</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="H13" s="2" t="s">
         <v>1062</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="I13" s="2" t="s">
         <v>1063</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>1064</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>6</v>
@@ -16130,7 +16503,7 @@
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
       <c r="O13" s="2" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
     </row>
   </sheetData>
@@ -16241,31 +16614,31 @@
         <v>84</v>
       </c>
       <c r="F1" s="6" t="s">
+        <v>1065</v>
+      </c>
+      <c r="G1" s="6" t="s">
         <v>1066</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="6" t="s">
         <v>1067</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="I1" s="6" t="s">
         <v>1068</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="J1" s="6" t="s">
         <v>1069</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="6" t="s">
         <v>1070</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>1071</v>
       </c>
       <c r="L1" s="6" t="s">
         <v>91</v>
       </c>
       <c r="M1" s="6" t="s">
+        <v>1071</v>
+      </c>
+      <c r="N1" s="6" t="s">
         <v>1072</v>
-      </c>
-      <c r="N1" s="6" t="s">
-        <v>1073</v>
       </c>
       <c r="O1" s="6" t="s">
         <v>47</v>
@@ -16291,7 +16664,7 @@
         <v>821</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>43</v>
@@ -16316,7 +16689,7 @@
         <v>spec/meals/README.md#phase-0a-technical-evidence; web release validation: spec/meals/README.md#web-release-validation</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O2" s="2"/>
     </row>
@@ -16340,7 +16713,7 @@
         <v>826</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>43</v>
@@ -16365,7 +16738,7 @@
         <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O3" s="2"/>
     </row>
@@ -16389,7 +16762,7 @@
         <v>831</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>43</v>
@@ -16414,7 +16787,7 @@
         <v>P0B-DB-001; package 0d30359ab5cdd4aa3577c33823de1bbc80a3d4f2; spec/meals/Phase 0B Recipe Persistence Design.md section 28; meals-db-final-manifest.json SHA256 4cbbc3eac24c13860d39ee3a0d8c6ae79c638cc5967d5274d1e7ea219091f8da; complete evidence in session b7458d86-6190-4718-8779-7c2b79a30630/files</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O4" s="2"/>
     </row>
@@ -16438,7 +16811,7 @@
         <v>835</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>43</v>
@@ -16463,7 +16836,7 @@
         <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O5" s="2"/>
     </row>
@@ -16487,7 +16860,7 @@
         <v>839</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>43</v>
@@ -16512,7 +16885,7 @@
         <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O6" s="2"/>
     </row>
@@ -16536,7 +16909,7 @@
         <v>844</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>43</v>
@@ -16561,7 +16934,7 @@
         <v>spec/meals/README.md#phase-0a-technical-evidence; web release validation: spec/meals/README.md#web-release-validation</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O7" s="2"/>
     </row>
@@ -16585,7 +16958,7 @@
         <v>848</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>43</v>
@@ -16610,7 +16983,7 @@
         <v>spec/meals/README.md#phase-0a-technical-evidence; web release validation: spec/meals/README.md#web-release-validation</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O8" s="2"/>
     </row>
@@ -16634,7 +17007,7 @@
         <v>852</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>43</v>
@@ -16659,7 +17032,7 @@
         <v>spec/meals/README.md#phase-0a-technical-evidence; web release validation: spec/meals/README.md#web-release-validation</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O9" s="2"/>
     </row>
@@ -16683,7 +17056,7 @@
         <v>856</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>43</v>
@@ -16708,7 +17081,7 @@
         <v>P0B-DB-001; package 0d30359ab5cdd4aa3577c33823de1bbc80a3d4f2; spec/meals/Phase 0B Recipe Persistence Design.md section 28; meals-db-final-manifest.json SHA256 4cbbc3eac24c13860d39ee3a0d8c6ae79c638cc5967d5274d1e7ea219091f8da; complete evidence in session b7458d86-6190-4718-8779-7c2b79a30630/files</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O10" s="2"/>
     </row>
@@ -16732,7 +17105,7 @@
         <v>933</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>44</v>
@@ -16754,13 +17127,13 @@
         <v>0</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O11" s="2"/>
     </row>
     <row r="12" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>54</v>
@@ -16775,13 +17148,13 @@
         <v>98</v>
       </c>
       <c r="F12" s="2" t="s">
+        <v>1077</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>1078</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="H12" s="2" t="s">
         <v>1079</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>1080</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
@@ -16789,7 +17162,7 @@
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="O12" s="2"/>
     </row>
@@ -16813,7 +17186,7 @@
         <v>860</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>43</v>
@@ -16838,7 +17211,7 @@
         <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O13" s="2"/>
     </row>
@@ -16862,7 +17235,7 @@
         <v>864</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>43</v>
@@ -16887,7 +17260,7 @@
         <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O14" s="2"/>
     </row>
@@ -16911,7 +17284,7 @@
         <v>868</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>43</v>
@@ -16936,7 +17309,7 @@
         <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O15" s="2"/>
     </row>
@@ -16960,7 +17333,7 @@
         <v>938</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>44</v>
@@ -16983,7 +17356,7 @@
 P0B-DB-001; package 0d30359ab5cdd4aa3577c33823de1bbc80a3d4f2; spec/meals/Phase 0B Recipe Persistence Design.md section 28; meals-db-final-manifest.json SHA256 4cbbc3eac24c13860d39ee3a0d8c6ae79c638cc5967d5274d1e7ea219091f8da; complete evidence in session b7458d86-6190-4718-8779-7c2b79a30630/files</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O16" s="2"/>
     </row>
@@ -17007,7 +17380,7 @@
         <v>102</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>41</v>
@@ -17032,7 +17405,7 @@
         <v>spec/meals/README.md#phase-0a-technical-evidence; P0-UAT-001: designated owner reported live Life Manager UAT PASS on 2026-10-28; release 8298e2e0797ddff7d2d53cc058fa41fb407ac0ab; recorded by Copilot from owner report, not automated authenticated verification</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O17" s="2"/>
     </row>
@@ -17056,7 +17429,7 @@
         <v>106</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>41</v>
@@ -17081,7 +17454,7 @@
         <v>spec/meals/README.md#phase-0a-technical-evidence; P0-UAT-001: designated owner reported live Life Manager UAT PASS on 2026-10-28; release 8298e2e0797ddff7d2d53cc058fa41fb407ac0ab; recorded by Copilot from owner report, not automated authenticated verification</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O18" s="2"/>
     </row>
@@ -17105,7 +17478,7 @@
         <v>111</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>41</v>
@@ -17130,7 +17503,7 @@
         <v>spec/meals/README.md#phase-0a-technical-evidence; P0-UAT-001: designated owner reported live Life Manager UAT PASS on 2026-10-28; release 8298e2e0797ddff7d2d53cc058fa41fb407ac0ab; recorded by Copilot from owner report, not automated authenticated verification</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O19" s="2"/>
     </row>
@@ -17154,7 +17527,7 @@
         <v>115</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>41</v>
@@ -17179,7 +17552,7 @@
         <v>spec/meals/README.md#phase-0a-technical-evidence; P0-UAT-001: designated owner reported live Life Manager UAT PASS on 2026-10-28; release 8298e2e0797ddff7d2d53cc058fa41fb407ac0ab; recorded by Copilot from owner report, not automated authenticated verification</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O20" s="2"/>
     </row>
@@ -17203,7 +17576,7 @@
         <v>119</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>41</v>
@@ -17213,11 +17586,11 @@
       </c>
       <c r="J21" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I21,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K21" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I21,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L21" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I21,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -17225,10 +17598,10 @@
       </c>
       <c r="M21" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I21,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O21" s="2"/>
     </row>
@@ -17252,7 +17625,7 @@
         <v>123</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>41</v>
@@ -17262,11 +17635,11 @@
       </c>
       <c r="J22" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I22,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K22" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I22,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L22" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I22,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -17274,10 +17647,10 @@
       </c>
       <c r="M22" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I22,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O22" s="2"/>
     </row>
@@ -17301,7 +17674,7 @@
         <v>127</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>41</v>
@@ -17326,13 +17699,13 @@
         <v>0</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O23" s="2"/>
     </row>
     <row r="24" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>56</v>
@@ -17347,13 +17720,13 @@
         <v>98</v>
       </c>
       <c r="F24" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>1084</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="H24" s="2" t="s">
         <v>1085</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>1086</v>
       </c>
       <c r="I24" s="2"/>
       <c r="J24" s="2" t="s">
@@ -17387,7 +17760,7 @@
         <v>131</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>41</v>
@@ -17412,7 +17785,7 @@
         <v>spec/meals/README.md#phase-0a-technical-evidence; P0-UAT-001: designated owner reported live Life Manager UAT PASS on 2026-10-28; release 8298e2e0797ddff7d2d53cc058fa41fb407ac0ab; recorded by Copilot from owner report, not automated authenticated verification</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O25" s="2"/>
     </row>
@@ -17436,7 +17809,7 @@
         <v>139</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>41</v>
@@ -17446,11 +17819,11 @@
       </c>
       <c r="J26" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I26,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K26" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I26,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L26" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I26,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -17458,10 +17831,10 @@
       </c>
       <c r="M26" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I26,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O26" s="2"/>
     </row>
@@ -17485,7 +17858,7 @@
         <v>146</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>41</v>
@@ -17495,11 +17868,11 @@
       </c>
       <c r="J27" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I27,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K27" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I27,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L27" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I27,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -17507,10 +17880,10 @@
       </c>
       <c r="M27" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I27,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md; P1-UAT-002; owner-reported live-web UAT; 2026-10-29; see Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O27" s="2"/>
     </row>
@@ -17534,7 +17907,7 @@
         <v>150</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>41</v>
@@ -17544,11 +17917,11 @@
       </c>
       <c r="J28" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I28,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K28" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I28,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L28" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I28,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -17556,10 +17929,10 @@
       </c>
       <c r="M28" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I28,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md; P1-UAT-002; owner-reported live-web UAT; 2026-10-29; see Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O28" s="2"/>
     </row>
@@ -17583,7 +17956,7 @@
         <v>154</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>41</v>
@@ -17593,11 +17966,11 @@
       </c>
       <c r="J29" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I29,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K29" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I29,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L29" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I29,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -17605,10 +17978,10 @@
       </c>
       <c r="M29" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I29,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O29" s="2"/>
     </row>
@@ -17632,7 +18005,7 @@
         <v>159</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>41</v>
@@ -17642,11 +18015,11 @@
       </c>
       <c r="J30" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I30,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K30" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I30,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L30" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I30,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -17654,10 +18027,10 @@
       </c>
       <c r="M30" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I30,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O30" s="2"/>
     </row>
@@ -17681,7 +18054,7 @@
         <v>164</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>41</v>
@@ -17691,11 +18064,11 @@
       </c>
       <c r="J31" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I31,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K31" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I31,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L31" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I31,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -17703,10 +18076,10 @@
       </c>
       <c r="M31" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I31,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O31" s="2"/>
     </row>
@@ -17730,7 +18103,7 @@
         <v>168</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>41</v>
@@ -17740,11 +18113,11 @@
       </c>
       <c r="J32" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I32,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K32" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I32,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L32" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I32,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -17752,10 +18125,10 @@
       </c>
       <c r="M32" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I32,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O32" s="2"/>
     </row>
@@ -17779,7 +18152,7 @@
         <v>172</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>41</v>
@@ -17789,11 +18162,11 @@
       </c>
       <c r="J33" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I33,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K33" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I33,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L33" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I33,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -17801,10 +18174,10 @@
       </c>
       <c r="M33" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I33,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O33" s="2"/>
     </row>
@@ -17828,7 +18201,7 @@
         <v>176</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>41</v>
@@ -17838,11 +18211,11 @@
       </c>
       <c r="J34" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I34,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K34" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I34,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L34" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I34,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -17850,10 +18223,10 @@
       </c>
       <c r="M34" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I34,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O34" s="2"/>
     </row>
@@ -17877,7 +18250,7 @@
         <v>180</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>41</v>
@@ -17887,11 +18260,11 @@
       </c>
       <c r="J35" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I35,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K35" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I35,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L35" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I35,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -17899,10 +18272,10 @@
       </c>
       <c r="M35" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I35,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-002; owner-reported live-web UAT; 2026-10-29; see Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O35" s="2"/>
     </row>
@@ -17926,7 +18299,7 @@
         <v>184</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>41</v>
@@ -17936,11 +18309,11 @@
       </c>
       <c r="J36" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I36,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K36" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I36,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L36" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I36,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -17948,10 +18321,10 @@
       </c>
       <c r="M36" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I36,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O36" s="2"/>
     </row>
@@ -17975,7 +18348,7 @@
         <v>189</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>41</v>
@@ -17985,11 +18358,11 @@
       </c>
       <c r="J37" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I37,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K37" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I37,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L37" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I37,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -17997,10 +18370,10 @@
       </c>
       <c r="M37" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I37,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-002; owner-reported live-web UAT; 2026-10-29; see Phase 1 Owner UAT Findings and Requirements Change Requests.md; P1-UAT-003; owner-reported live-web UAT; 2026-10-29; see Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O37" s="2"/>
     </row>
@@ -18024,7 +18397,7 @@
         <v>194</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>41</v>
@@ -18034,11 +18407,11 @@
       </c>
       <c r="J38" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I38,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K38" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I38,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L38" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I38,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -18046,10 +18419,10 @@
       </c>
       <c r="M38" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I38,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md; P1-UAT-002; owner-reported live-web UAT; 2026-10-29; see Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O38" s="2"/>
     </row>
@@ -18073,7 +18446,7 @@
         <v>198</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>41</v>
@@ -18083,11 +18456,11 @@
       </c>
       <c r="J39" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I39,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K39" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I39,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L39" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I39,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -18095,10 +18468,10 @@
       </c>
       <c r="M39" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I39,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md; P1-UAT-002; owner-reported live-web UAT; 2026-10-29; see Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O39" s="2"/>
     </row>
@@ -18122,7 +18495,7 @@
         <v>202</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>41</v>
@@ -18132,11 +18505,11 @@
       </c>
       <c r="J40" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I40,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K40" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I40,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L40" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I40,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -18144,10 +18517,10 @@
       </c>
       <c r="M40" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I40,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md; P1-UAT-002; owner-reported live-web UAT; 2026-10-29; see Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O40" s="2"/>
     </row>
@@ -18171,7 +18544,7 @@
         <v>206</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>41</v>
@@ -18196,7 +18569,7 @@
         <v>0</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O41" s="2"/>
     </row>
@@ -18220,7 +18593,7 @@
         <v>210</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>41</v>
@@ -18245,7 +18618,7 @@
         <v>0</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O42" s="2"/>
     </row>
@@ -18269,7 +18642,7 @@
         <v>214</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>41</v>
@@ -18294,7 +18667,7 @@
         <v>0</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O43" s="2"/>
     </row>
@@ -18318,7 +18691,7 @@
         <v>218</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>41</v>
@@ -18328,11 +18701,11 @@
       </c>
       <c r="J44" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I44,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K44" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I44,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L44" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I44,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -18340,10 +18713,10 @@
       </c>
       <c r="M44" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I44,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O44" s="2"/>
     </row>
@@ -18367,7 +18740,7 @@
         <v>222</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>41</v>
@@ -18377,11 +18750,11 @@
       </c>
       <c r="J45" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I45,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K45" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I45,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L45" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I45,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -18389,10 +18762,10 @@
       </c>
       <c r="M45" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I45,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O45" s="2"/>
     </row>
@@ -18416,7 +18789,7 @@
         <v>227</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>41</v>
@@ -18426,11 +18799,11 @@
       </c>
       <c r="J46" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I46,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K46" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I46,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L46" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I46,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -18438,10 +18811,10 @@
       </c>
       <c r="M46" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I46,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O46" s="2"/>
     </row>
@@ -18465,7 +18838,7 @@
         <v>231</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>41</v>
@@ -18475,11 +18848,11 @@
       </c>
       <c r="J47" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I47,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K47" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I47,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L47" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I47,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -18487,10 +18860,10 @@
       </c>
       <c r="M47" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I47,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md; P1-UAT-002; owner-reported live-web UAT; 2026-10-29; see Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O47" s="2"/>
     </row>
@@ -18514,7 +18887,7 @@
         <v>236</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>41</v>
@@ -18524,11 +18897,11 @@
       </c>
       <c r="J48" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I48,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K48" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I48,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L48" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I48,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -18536,10 +18909,10 @@
       </c>
       <c r="M48" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I48,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md; P1-UAT-002; owner-reported live-web UAT; 2026-10-29; see Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O48" s="2"/>
     </row>
@@ -18563,7 +18936,7 @@
         <v>240</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>41</v>
@@ -18573,11 +18946,11 @@
       </c>
       <c r="J49" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I49,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K49" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I49,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L49" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I49,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -18585,10 +18958,10 @@
       </c>
       <c r="M49" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I49,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-002; owner-reported live-web UAT; 2026-10-29; see Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O49" s="2"/>
     </row>
@@ -18612,7 +18985,7 @@
         <v>244</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>41</v>
@@ -18637,7 +19010,7 @@
         <v>0</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O50" s="2"/>
     </row>
@@ -18661,7 +19034,7 @@
         <v>249</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>41</v>
@@ -18671,11 +19044,11 @@
       </c>
       <c r="J51" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I51,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K51" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I51,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L51" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I51,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -18683,10 +19056,10 @@
       </c>
       <c r="M51" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I51,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-003; owner-reported live-web UAT; 2026-10-29; see Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O51" s="2"/>
     </row>
@@ -18710,7 +19083,7 @@
         <v>254</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>41</v>
@@ -18720,11 +19093,11 @@
       </c>
       <c r="J52" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I52,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K52" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I52,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L52" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I52,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -18732,10 +19105,10 @@
       </c>
       <c r="M52" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I52,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md; P1-UAT-002; owner-reported live-web UAT; 2026-10-29; see Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O52" s="2"/>
     </row>
@@ -18759,7 +19132,7 @@
         <v>258</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>41</v>
@@ -18769,11 +19142,11 @@
       </c>
       <c r="J53" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I53,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K53" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I53,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L53" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I53,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -18781,10 +19154,10 @@
       </c>
       <c r="M53" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I53,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O53" s="2"/>
     </row>
@@ -18808,7 +19181,7 @@
         <v>262</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>41</v>
@@ -18818,11 +19191,11 @@
       </c>
       <c r="J54" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I54,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K54" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I54,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L54" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I54,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -18830,10 +19203,10 @@
       </c>
       <c r="M54" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I54,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O54" s="2"/>
     </row>
@@ -18857,7 +19230,7 @@
         <v>266</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>41</v>
@@ -18882,7 +19255,7 @@
         <v>0</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O55" s="2"/>
     </row>
@@ -18906,7 +19279,7 @@
         <v>270</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>41</v>
@@ -18931,7 +19304,7 @@
         <v>0</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O56" s="2"/>
     </row>
@@ -18955,7 +19328,7 @@
         <v>274</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>41</v>
@@ -18965,11 +19338,11 @@
       </c>
       <c r="J57" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I57,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K57" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I57,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L57" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I57,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -18977,10 +19350,10 @@
       </c>
       <c r="M57" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I57,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O57" s="2"/>
     </row>
@@ -19004,7 +19377,7 @@
         <v>278</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>41</v>
@@ -19014,11 +19387,11 @@
       </c>
       <c r="J58" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I58,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K58" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I58,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L58" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I58,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -19026,10 +19399,10 @@
       </c>
       <c r="M58" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I58,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O58" s="2"/>
     </row>
@@ -19053,7 +19426,7 @@
         <v>282</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>41</v>
@@ -19063,11 +19436,11 @@
       </c>
       <c r="J59" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I59,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K59" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I59,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L59" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I59,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -19075,10 +19448,10 @@
       </c>
       <c r="M59" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I59,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md; P1-UAT-002; owner-reported live-web UAT; 2026-10-29; see Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O59" s="2"/>
     </row>
@@ -19102,7 +19475,7 @@
         <v>286</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>41</v>
@@ -19112,11 +19485,11 @@
       </c>
       <c r="J60" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I60,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Deferred</v>
       </c>
       <c r="K60" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I60,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L60" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I60,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -19124,10 +19497,10 @@
       </c>
       <c r="M60" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I60,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-003; owner-reported live-web UAT; 2026-10-29; see Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O60" s="2"/>
     </row>
@@ -19151,7 +19524,7 @@
         <v>290</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>41</v>
@@ -19176,7 +19549,7 @@
         <v>0</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O61" s="2"/>
     </row>
@@ -19200,7 +19573,7 @@
         <v>294</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>41</v>
@@ -19225,7 +19598,7 @@
         <v>0</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O62" s="2"/>
     </row>
@@ -19249,7 +19622,7 @@
         <v>299</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>41</v>
@@ -19259,11 +19632,11 @@
       </c>
       <c r="J63" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I63,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K63" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I63,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L63" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I63,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -19271,10 +19644,10 @@
       </c>
       <c r="M63" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I63,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O63" s="2"/>
     </row>
@@ -19298,7 +19671,7 @@
         <v>304</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>41</v>
@@ -19308,11 +19681,11 @@
       </c>
       <c r="J64" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I64,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K64" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I64,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L64" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I64,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -19320,10 +19693,10 @@
       </c>
       <c r="M64" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I64,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O64" s="2"/>
     </row>
@@ -19347,7 +19720,7 @@
         <v>308</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>41</v>
@@ -19357,11 +19730,11 @@
       </c>
       <c r="J65" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I65,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K65" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I65,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L65" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I65,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -19369,10 +19742,10 @@
       </c>
       <c r="M65" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I65,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O65" s="2"/>
     </row>
@@ -19396,7 +19769,7 @@
         <v>312</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>41</v>
@@ -19406,11 +19779,11 @@
       </c>
       <c r="J66" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I66,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K66" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I66,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L66" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I66,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -19418,10 +19791,10 @@
       </c>
       <c r="M66" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I66,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O66" s="2"/>
     </row>
@@ -19445,7 +19818,7 @@
         <v>316</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>41</v>
@@ -19455,11 +19828,11 @@
       </c>
       <c r="J67" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I67,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K67" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I67,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L67" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I67,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -19467,10 +19840,10 @@
       </c>
       <c r="M67" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I67,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O67" s="2"/>
     </row>
@@ -19494,7 +19867,7 @@
         <v>320</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>41</v>
@@ -19504,11 +19877,11 @@
       </c>
       <c r="J68" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I68,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K68" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I68,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L68" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I68,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -19516,10 +19889,10 @@
       </c>
       <c r="M68" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I68,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O68" s="2"/>
     </row>
@@ -19543,7 +19916,7 @@
         <v>324</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>41</v>
@@ -19553,11 +19926,11 @@
       </c>
       <c r="J69" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I69,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K69" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I69,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L69" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I69,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -19565,10 +19938,10 @@
       </c>
       <c r="M69" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I69,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md; P1-UAT-002; owner-reported live-web UAT; 2026-10-29; see Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O69" s="2"/>
     </row>
@@ -19592,7 +19965,7 @@
         <v>328</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>41</v>
@@ -19602,11 +19975,11 @@
       </c>
       <c r="J70" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I70,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K70" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I70,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L70" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I70,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -19614,10 +19987,10 @@
       </c>
       <c r="M70" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I70,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O70" s="2"/>
     </row>
@@ -19641,7 +20014,7 @@
         <v>332</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>41</v>
@@ -19651,11 +20024,11 @@
       </c>
       <c r="J71" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I71,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K71" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I71,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L71" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I71,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -19663,10 +20036,10 @@
       </c>
       <c r="M71" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I71,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md; P1-UAT-002; owner-reported live-web UAT; 2026-10-29; see Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O71" s="2"/>
     </row>
@@ -19690,7 +20063,7 @@
         <v>336</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>41</v>
@@ -19700,11 +20073,11 @@
       </c>
       <c r="J72" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I72,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K72" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I72,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L72" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I72,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -19712,10 +20085,10 @@
       </c>
       <c r="M72" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I72,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O72" s="2"/>
     </row>
@@ -19739,7 +20112,7 @@
         <v>340</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>41</v>
@@ -19749,11 +20122,11 @@
       </c>
       <c r="J73" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I73,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K73" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I73,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L73" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I73,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -19761,10 +20134,10 @@
       </c>
       <c r="M73" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I73,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O73" s="2"/>
     </row>
@@ -19788,7 +20161,7 @@
         <v>344</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>41</v>
@@ -19798,11 +20171,11 @@
       </c>
       <c r="J74" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I74,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K74" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I74,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L74" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I74,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -19810,10 +20183,10 @@
       </c>
       <c r="M74" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I74,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O74" s="2"/>
     </row>
@@ -19837,7 +20210,7 @@
         <v>349</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>41</v>
@@ -19847,11 +20220,11 @@
       </c>
       <c r="J75" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I75,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Deferred</v>
       </c>
       <c r="K75" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I75,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L75" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I75,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -19859,10 +20232,10 @@
       </c>
       <c r="M75" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I75,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported partial Phase 1 verification; Shopping not tested; P1-UAT-002; owner-reported live-web UAT; 2026-10-29; see Phase 1 Owner UAT Findings and Requirements Change Requests.md; P1-UAT-003; owner-reported live-web UAT; 2026-10-29; see Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O75" s="2"/>
     </row>
@@ -19886,7 +20259,7 @@
         <v>353</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>41</v>
@@ -19896,11 +20269,11 @@
       </c>
       <c r="J76" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I76,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K76" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I76,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L76" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I76,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -19908,10 +20281,10 @@
       </c>
       <c r="M76" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I76,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O76" s="2"/>
     </row>
@@ -19935,7 +20308,7 @@
         <v>357</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>41</v>
@@ -19945,11 +20318,11 @@
       </c>
       <c r="J77" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I77,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K77" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I77,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L77" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I77,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -19957,10 +20330,10 @@
       </c>
       <c r="M77" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I77,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-002; owner-reported live-web UAT; 2026-10-29; see Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O77" s="2"/>
     </row>
@@ -19984,7 +20357,7 @@
         <v>361</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>41</v>
@@ -19994,11 +20367,11 @@
       </c>
       <c r="J78" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I78,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K78" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I78,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L78" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I78,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -20006,10 +20379,10 @@
       </c>
       <c r="M78" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I78,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O78" s="2"/>
     </row>
@@ -20033,7 +20406,7 @@
         <v>365</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>41</v>
@@ -20043,11 +20416,11 @@
       </c>
       <c r="J79" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I79,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K79" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I79,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L79" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I79,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -20055,10 +20428,10 @@
       </c>
       <c r="M79" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I79,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-002; owner-reported live-web UAT; 2026-10-29; see Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O79" s="2"/>
     </row>
@@ -20082,7 +20455,7 @@
         <v>370</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>41</v>
@@ -20092,11 +20465,11 @@
       </c>
       <c r="J80" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I80,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K80" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I80,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L80" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I80,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -20104,10 +20477,10 @@
       </c>
       <c r="M80" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I80,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O80" s="2"/>
     </row>
@@ -20131,7 +20504,7 @@
         <v>375</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>41</v>
@@ -20141,11 +20514,11 @@
       </c>
       <c r="J81" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I81,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K81" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I81,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L81" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I81,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -20153,10 +20526,10 @@
       </c>
       <c r="M81" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I81,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-002; owner-reported live-web UAT; 2026-10-29; see Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O81" s="2"/>
     </row>
@@ -20180,7 +20553,7 @@
         <v>379</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>41</v>
@@ -20190,11 +20563,11 @@
       </c>
       <c r="J82" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I82,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K82" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I82,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L82" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I82,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -20202,10 +20575,10 @@
       </c>
       <c r="M82" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I82,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-002; owner-reported live-web UAT; 2026-10-29; see Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O82" s="2"/>
     </row>
@@ -20229,7 +20602,7 @@
         <v>384</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>41</v>
@@ -20239,11 +20612,11 @@
       </c>
       <c r="J83" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I83,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K83" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I83,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L83" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I83,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -20251,10 +20624,10 @@
       </c>
       <c r="M83" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I83,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; Executed: node --test tests/meals-recipe-interaction.test.cjs tests/meals-recipe-service.test.cjs tests/meals-recipe-persistence.test.cjs (19 passed, 0 failed; 2026-10-29)</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O83" s="2"/>
     </row>
@@ -20278,7 +20651,7 @@
         <v>389</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>41</v>
@@ -20288,11 +20661,11 @@
       </c>
       <c r="J84" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I84,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K84" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I84,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L84" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I84,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -20300,10 +20673,10 @@
       </c>
       <c r="M84" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I84,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O84" s="2"/>
     </row>
@@ -20327,7 +20700,7 @@
         <v>393</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>41</v>
@@ -20337,11 +20710,11 @@
       </c>
       <c r="J85" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I85,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K85" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I85,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L85" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I85,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -20349,10 +20722,10 @@
       </c>
       <c r="M85" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I85,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N85" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O85" s="2"/>
     </row>
@@ -20376,7 +20749,7 @@
         <v>397</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>41</v>
@@ -20386,11 +20759,11 @@
       </c>
       <c r="J86" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I86,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K86" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I86,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L86" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I86,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -20398,10 +20771,10 @@
       </c>
       <c r="M86" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I86,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N86" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O86" s="2"/>
     </row>
@@ -20425,7 +20798,7 @@
         <v>402</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>41</v>
@@ -20450,7 +20823,7 @@
         <v>0</v>
       </c>
       <c r="N87" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O87" s="2"/>
     </row>
@@ -20474,7 +20847,7 @@
         <v>406</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>41</v>
@@ -20499,7 +20872,7 @@
         <v>0</v>
       </c>
       <c r="N88" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O88" s="2"/>
     </row>
@@ -20523,7 +20896,7 @@
         <v>410</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>41</v>
@@ -20548,7 +20921,7 @@
         <v>0</v>
       </c>
       <c r="N89" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O89" s="2"/>
     </row>
@@ -20572,7 +20945,7 @@
         <v>414</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>41</v>
@@ -20597,7 +20970,7 @@
         <v>0</v>
       </c>
       <c r="N90" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O90" s="2"/>
     </row>
@@ -20621,7 +20994,7 @@
         <v>418</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>41</v>
@@ -20646,7 +21019,7 @@
         <v>0</v>
       </c>
       <c r="N91" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O91" s="2"/>
     </row>
@@ -20670,7 +21043,7 @@
         <v>423</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>41</v>
@@ -20695,7 +21068,7 @@
         <v>0</v>
       </c>
       <c r="N92" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O92" s="2"/>
     </row>
@@ -20719,7 +21092,7 @@
         <v>427</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>41</v>
@@ -20744,7 +21117,7 @@
         <v>0</v>
       </c>
       <c r="N93" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O93" s="2"/>
     </row>
@@ -20768,7 +21141,7 @@
         <v>431</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>41</v>
@@ -20793,7 +21166,7 @@
         <v>0</v>
       </c>
       <c r="N94" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O94" s="2"/>
     </row>
@@ -20817,7 +21190,7 @@
         <v>435</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>41</v>
@@ -20842,7 +21215,7 @@
         <v>0</v>
       </c>
       <c r="N95" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O95" s="2"/>
     </row>
@@ -20866,7 +21239,7 @@
         <v>439</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>41</v>
@@ -20891,7 +21264,7 @@
         <v>0</v>
       </c>
       <c r="N96" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O96" s="2"/>
     </row>
@@ -20915,7 +21288,7 @@
         <v>443</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>41</v>
@@ -20940,7 +21313,7 @@
         <v>0</v>
       </c>
       <c r="N97" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O97" s="2"/>
     </row>
@@ -20964,7 +21337,7 @@
         <v>447</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>41</v>
@@ -20989,7 +21362,7 @@
         <v>0</v>
       </c>
       <c r="N98" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O98" s="2"/>
     </row>
@@ -21013,7 +21386,7 @@
         <v>452</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>41</v>
@@ -21038,7 +21411,7 @@
         <v>0</v>
       </c>
       <c r="N99" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O99" s="2"/>
     </row>
@@ -21062,7 +21435,7 @@
         <v>456</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>41</v>
@@ -21087,7 +21460,7 @@
         <v>0</v>
       </c>
       <c r="N100" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O100" s="2"/>
     </row>
@@ -21111,7 +21484,7 @@
         <v>460</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>41</v>
@@ -21136,7 +21509,7 @@
         <v>0</v>
       </c>
       <c r="N101" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O101" s="2"/>
     </row>
@@ -21160,7 +21533,7 @@
         <v>464</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>41</v>
@@ -21185,7 +21558,7 @@
         <v>0</v>
       </c>
       <c r="N102" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O102" s="2"/>
     </row>
@@ -21209,7 +21582,7 @@
         <v>470</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>41</v>
@@ -21234,7 +21607,7 @@
         <v>0</v>
       </c>
       <c r="N103" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O103" s="2"/>
     </row>
@@ -21258,7 +21631,7 @@
         <v>474</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>41</v>
@@ -21283,7 +21656,7 @@
         <v>0</v>
       </c>
       <c r="N104" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O104" s="2"/>
     </row>
@@ -21307,7 +21680,7 @@
         <v>478</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>41</v>
@@ -21332,7 +21705,7 @@
         <v>0</v>
       </c>
       <c r="N105" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O105" s="2"/>
     </row>
@@ -21356,7 +21729,7 @@
         <v>482</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>41</v>
@@ -21381,7 +21754,7 @@
         <v>0</v>
       </c>
       <c r="N106" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O106" s="2"/>
     </row>
@@ -21405,7 +21778,7 @@
         <v>486</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>41</v>
@@ -21430,7 +21803,7 @@
         <v>0</v>
       </c>
       <c r="N107" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O107" s="2"/>
     </row>
@@ -21454,7 +21827,7 @@
         <v>490</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>41</v>
@@ -21479,7 +21852,7 @@
         <v>0</v>
       </c>
       <c r="N108" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O108" s="2"/>
     </row>
@@ -21503,7 +21876,7 @@
         <v>494</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>41</v>
@@ -21528,7 +21901,7 @@
         <v>0</v>
       </c>
       <c r="N109" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O109" s="2"/>
     </row>
@@ -21552,7 +21925,7 @@
         <v>498</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>41</v>
@@ -21577,7 +21950,7 @@
         <v>0</v>
       </c>
       <c r="N110" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O110" s="2"/>
     </row>
@@ -21601,7 +21974,7 @@
         <v>502</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>41</v>
@@ -21626,7 +21999,7 @@
         <v>0</v>
       </c>
       <c r="N111" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O111" s="2"/>
     </row>
@@ -21650,7 +22023,7 @@
         <v>506</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>41</v>
@@ -21675,7 +22048,7 @@
         <v>0</v>
       </c>
       <c r="N112" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O112" s="2"/>
     </row>
@@ -21699,7 +22072,7 @@
         <v>511</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>41</v>
@@ -21724,7 +22097,7 @@
         <v>0</v>
       </c>
       <c r="N113" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O113" s="2"/>
     </row>
@@ -21748,7 +22121,7 @@
         <v>515</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>41</v>
@@ -21773,7 +22146,7 @@
         <v>0</v>
       </c>
       <c r="N114" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O114" s="2"/>
     </row>
@@ -21797,7 +22170,7 @@
         <v>520</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>41</v>
@@ -21822,7 +22195,7 @@
         <v>0</v>
       </c>
       <c r="N115" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O115" s="2"/>
     </row>
@@ -21846,7 +22219,7 @@
         <v>525</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>41</v>
@@ -21871,7 +22244,7 @@
         <v>0</v>
       </c>
       <c r="N116" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O116" s="2"/>
     </row>
@@ -21895,7 +22268,7 @@
         <v>529</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>41</v>
@@ -21920,7 +22293,7 @@
         <v>0</v>
       </c>
       <c r="N117" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O117" s="2"/>
     </row>
@@ -21944,7 +22317,7 @@
         <v>533</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>41</v>
@@ -21969,7 +22342,7 @@
         <v>0</v>
       </c>
       <c r="N118" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O118" s="2"/>
     </row>
@@ -21993,7 +22366,7 @@
         <v>537</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>41</v>
@@ -22018,7 +22391,7 @@
         <v>0</v>
       </c>
       <c r="N119" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O119" s="2"/>
     </row>
@@ -22042,7 +22415,7 @@
         <v>541</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>41</v>
@@ -22067,7 +22440,7 @@
         <v>0</v>
       </c>
       <c r="N120" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O120" s="2"/>
     </row>
@@ -22091,7 +22464,7 @@
         <v>545</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>41</v>
@@ -22116,7 +22489,7 @@
         <v>0</v>
       </c>
       <c r="N121" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O121" s="2"/>
     </row>
@@ -22140,7 +22513,7 @@
         <v>549</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>41</v>
@@ -22165,7 +22538,7 @@
         <v>0</v>
       </c>
       <c r="N122" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O122" s="2"/>
     </row>
@@ -22189,7 +22562,7 @@
         <v>553</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>41</v>
@@ -22214,7 +22587,7 @@
         <v>0</v>
       </c>
       <c r="N123" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O123" s="2"/>
     </row>
@@ -22238,7 +22611,7 @@
         <v>557</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>41</v>
@@ -22263,7 +22636,7 @@
         <v>0</v>
       </c>
       <c r="N124" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O124" s="2"/>
     </row>
@@ -22287,7 +22660,7 @@
         <v>561</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>41</v>
@@ -22312,7 +22685,7 @@
         <v>0</v>
       </c>
       <c r="N125" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O125" s="2"/>
     </row>
@@ -22336,7 +22709,7 @@
         <v>565</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>41</v>
@@ -22361,7 +22734,7 @@
         <v>0</v>
       </c>
       <c r="N126" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O126" s="2"/>
     </row>
@@ -22385,7 +22758,7 @@
         <v>569</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>41</v>
@@ -22410,7 +22783,7 @@
         <v>0</v>
       </c>
       <c r="N127" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O127" s="2"/>
     </row>
@@ -22434,7 +22807,7 @@
         <v>573</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>41</v>
@@ -22459,7 +22832,7 @@
         <v>0</v>
       </c>
       <c r="N128" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O128" s="2"/>
     </row>
@@ -22483,7 +22856,7 @@
         <v>577</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>41</v>
@@ -22508,7 +22881,7 @@
         <v>0</v>
       </c>
       <c r="N129" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O129" s="2"/>
     </row>
@@ -22532,7 +22905,7 @@
         <v>581</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>41</v>
@@ -22557,7 +22930,7 @@
         <v>0</v>
       </c>
       <c r="N130" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O130" s="2"/>
     </row>
@@ -22581,7 +22954,7 @@
         <v>585</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>41</v>
@@ -22606,7 +22979,7 @@
         <v>0</v>
       </c>
       <c r="N131" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O131" s="2"/>
     </row>
@@ -22630,7 +23003,7 @@
         <v>590</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>41</v>
@@ -22655,7 +23028,7 @@
         <v>0</v>
       </c>
       <c r="N132" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O132" s="2"/>
     </row>
@@ -22679,7 +23052,7 @@
         <v>594</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>41</v>
@@ -22704,7 +23077,7 @@
         <v>0</v>
       </c>
       <c r="N133" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O133" s="2"/>
     </row>
@@ -22728,7 +23101,7 @@
         <v>598</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>41</v>
@@ -22753,7 +23126,7 @@
         <v>0</v>
       </c>
       <c r="N134" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O134" s="2"/>
     </row>
@@ -22777,7 +23150,7 @@
         <v>602</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>41</v>
@@ -22802,7 +23175,7 @@
         <v>0</v>
       </c>
       <c r="N135" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O135" s="2"/>
     </row>
@@ -22826,7 +23199,7 @@
         <v>606</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>41</v>
@@ -22851,7 +23224,7 @@
         <v>0</v>
       </c>
       <c r="N136" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O136" s="2"/>
     </row>
@@ -22875,7 +23248,7 @@
         <v>610</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>41</v>
@@ -22900,7 +23273,7 @@
         <v>0</v>
       </c>
       <c r="N137" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O137" s="2"/>
     </row>
@@ -22924,7 +23297,7 @@
         <v>614</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>41</v>
@@ -22949,7 +23322,7 @@
         <v>0</v>
       </c>
       <c r="N138" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O138" s="2"/>
     </row>
@@ -22973,7 +23346,7 @@
         <v>618</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>41</v>
@@ -22998,7 +23371,7 @@
         <v>0</v>
       </c>
       <c r="N139" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O139" s="2"/>
     </row>
@@ -23022,7 +23395,7 @@
         <v>622</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>41</v>
@@ -23047,7 +23420,7 @@
         <v>0</v>
       </c>
       <c r="N140" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O140" s="2"/>
     </row>
@@ -23071,7 +23444,7 @@
         <v>626</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>41</v>
@@ -23096,7 +23469,7 @@
         <v>0</v>
       </c>
       <c r="N141" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O141" s="2"/>
     </row>
@@ -23120,7 +23493,7 @@
         <v>630</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>41</v>
@@ -23145,7 +23518,7 @@
         <v>0</v>
       </c>
       <c r="N142" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O142" s="2"/>
     </row>
@@ -23169,7 +23542,7 @@
         <v>634</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>41</v>
@@ -23194,7 +23567,7 @@
         <v>0</v>
       </c>
       <c r="N143" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O143" s="2"/>
     </row>
@@ -23218,7 +23591,7 @@
         <v>639</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>41</v>
@@ -23243,7 +23616,7 @@
         <v>0</v>
       </c>
       <c r="N144" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O144" s="2"/>
     </row>
@@ -23267,7 +23640,7 @@
         <v>644</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>41</v>
@@ -23292,7 +23665,7 @@
         <v>0</v>
       </c>
       <c r="N145" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O145" s="2"/>
     </row>
@@ -23316,7 +23689,7 @@
         <v>648</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>41</v>
@@ -23341,7 +23714,7 @@
         <v>0</v>
       </c>
       <c r="N146" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O146" s="2"/>
     </row>
@@ -23365,7 +23738,7 @@
         <v>652</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H147" s="2" t="s">
         <v>41</v>
@@ -23390,7 +23763,7 @@
         <v>0</v>
       </c>
       <c r="N147" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O147" s="2"/>
     </row>
@@ -23414,7 +23787,7 @@
         <v>656</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>41</v>
@@ -23439,7 +23812,7 @@
         <v>0</v>
       </c>
       <c r="N148" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O148" s="2"/>
     </row>
@@ -23463,7 +23836,7 @@
         <v>660</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H149" s="2" t="s">
         <v>41</v>
@@ -23488,7 +23861,7 @@
         <v>0</v>
       </c>
       <c r="N149" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O149" s="2"/>
     </row>
@@ -23512,7 +23885,7 @@
         <v>664</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H150" s="2" t="s">
         <v>41</v>
@@ -23537,7 +23910,7 @@
         <v>0</v>
       </c>
       <c r="N150" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O150" s="2"/>
     </row>
@@ -23561,7 +23934,7 @@
         <v>668</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>41</v>
@@ -23586,7 +23959,7 @@
         <v>0</v>
       </c>
       <c r="N151" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O151" s="2"/>
     </row>
@@ -23610,7 +23983,7 @@
         <v>672</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>41</v>
@@ -23635,7 +24008,7 @@
         <v>0</v>
       </c>
       <c r="N152" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O152" s="2"/>
     </row>
@@ -23659,7 +24032,7 @@
         <v>676</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H153" s="2" t="s">
         <v>41</v>
@@ -23684,7 +24057,7 @@
         <v>0</v>
       </c>
       <c r="N153" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O153" s="2"/>
     </row>
@@ -23708,7 +24081,7 @@
         <v>680</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>41</v>
@@ -23733,7 +24106,7 @@
         <v>0</v>
       </c>
       <c r="N154" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O154" s="2"/>
     </row>
@@ -23757,7 +24130,7 @@
         <v>684</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>41</v>
@@ -23782,7 +24155,7 @@
         <v>0</v>
       </c>
       <c r="N155" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O155" s="2"/>
     </row>
@@ -23806,7 +24179,7 @@
         <v>688</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>41</v>
@@ -23831,7 +24204,7 @@
         <v>0</v>
       </c>
       <c r="N156" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O156" s="2"/>
     </row>
@@ -23855,7 +24228,7 @@
         <v>692</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H157" s="2" t="s">
         <v>41</v>
@@ -23880,7 +24253,7 @@
         <v>0</v>
       </c>
       <c r="N157" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O157" s="2"/>
     </row>
@@ -23904,7 +24277,7 @@
         <v>696</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>41</v>
@@ -23929,7 +24302,7 @@
         <v>0</v>
       </c>
       <c r="N158" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O158" s="2"/>
     </row>
@@ -23953,7 +24326,7 @@
         <v>700</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>41</v>
@@ -23978,7 +24351,7 @@
         <v>0</v>
       </c>
       <c r="N159" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O159" s="2"/>
     </row>
@@ -24002,7 +24375,7 @@
         <v>705</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>41</v>
@@ -24027,7 +24400,7 @@
         <v>0</v>
       </c>
       <c r="N160" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O160" s="2"/>
     </row>
@@ -24051,7 +24424,7 @@
         <v>709</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H161" s="2" t="s">
         <v>41</v>
@@ -24076,7 +24449,7 @@
         <v>0</v>
       </c>
       <c r="N161" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O161" s="2"/>
     </row>
@@ -24100,7 +24473,7 @@
         <v>713</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>41</v>
@@ -24125,7 +24498,7 @@
         <v>0</v>
       </c>
       <c r="N162" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O162" s="2"/>
     </row>
@@ -24149,7 +24522,7 @@
         <v>718</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H163" s="2" t="s">
         <v>41</v>
@@ -24174,7 +24547,7 @@
         <v>0</v>
       </c>
       <c r="N163" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O163" s="2"/>
     </row>
@@ -24198,7 +24571,7 @@
         <v>722</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H164" s="2" t="s">
         <v>41</v>
@@ -24223,7 +24596,7 @@
         <v>0</v>
       </c>
       <c r="N164" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O164" s="2"/>
     </row>
@@ -24247,7 +24620,7 @@
         <v>726</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H165" s="2" t="s">
         <v>41</v>
@@ -24272,7 +24645,7 @@
         <v>0</v>
       </c>
       <c r="N165" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O165" s="2"/>
     </row>
@@ -24296,7 +24669,7 @@
         <v>730</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H166" s="2" t="s">
         <v>41</v>
@@ -24321,7 +24694,7 @@
         <v>0</v>
       </c>
       <c r="N166" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O166" s="2"/>
     </row>
@@ -24345,7 +24718,7 @@
         <v>734</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H167" s="2" t="s">
         <v>41</v>
@@ -24370,7 +24743,7 @@
         <v>0</v>
       </c>
       <c r="N167" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O167" s="2"/>
     </row>
@@ -24394,7 +24767,7 @@
         <v>739</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H168" s="2" t="s">
         <v>41</v>
@@ -24419,7 +24792,7 @@
         <v>0</v>
       </c>
       <c r="N168" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O168" s="2"/>
     </row>
@@ -24443,7 +24816,7 @@
         <v>743</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H169" s="2" t="s">
         <v>41</v>
@@ -24468,7 +24841,7 @@
         <v>0</v>
       </c>
       <c r="N169" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O169" s="2"/>
     </row>
@@ -24492,7 +24865,7 @@
         <v>748</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H170" s="2" t="s">
         <v>41</v>
@@ -24517,7 +24890,7 @@
         <v>0</v>
       </c>
       <c r="N170" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O170" s="2"/>
     </row>
@@ -24541,7 +24914,7 @@
         <v>752</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H171" s="2" t="s">
         <v>41</v>
@@ -24566,7 +24939,7 @@
         <v>0</v>
       </c>
       <c r="N171" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O171" s="2"/>
     </row>
@@ -24590,7 +24963,7 @@
         <v>756</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H172" s="2" t="s">
         <v>41</v>
@@ -24615,7 +24988,7 @@
         <v>0</v>
       </c>
       <c r="N172" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O172" s="2"/>
     </row>
@@ -24639,7 +25012,7 @@
         <v>760</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H173" s="2" t="s">
         <v>41</v>
@@ -24664,7 +25037,7 @@
         <v>0</v>
       </c>
       <c r="N173" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O173" s="2"/>
     </row>
@@ -24688,7 +25061,7 @@
         <v>764</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H174" s="2" t="s">
         <v>41</v>
@@ -24713,7 +25086,7 @@
         <v>0</v>
       </c>
       <c r="N174" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O174" s="2"/>
     </row>
@@ -24737,7 +25110,7 @@
         <v>770</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H175" s="2" t="s">
         <v>41</v>
@@ -24762,7 +25135,7 @@
         <v>spec/meals/README.md#phase-0a-technical-evidence; P0-UAT-001: designated owner reported live Life Manager UAT PASS on 2026-10-28; release 8298e2e0797ddff7d2d53cc058fa41fb407ac0ab; recorded by Copilot from owner report, not automated authenticated verification</v>
       </c>
       <c r="N175" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O175" s="2"/>
     </row>
@@ -24786,7 +25159,7 @@
         <v>775</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H176" s="2" t="s">
         <v>41</v>
@@ -24796,11 +25169,11 @@
       </c>
       <c r="J176" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I176,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K176" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I176,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L176" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I176,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -24808,10 +25181,10 @@
       </c>
       <c r="M176" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I176,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md; P1-UAT-002; owner-reported live-web UAT; 2026-10-29; see Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N176" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O176" s="2"/>
     </row>
@@ -24835,7 +25208,7 @@
         <v>779</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H177" s="2" t="s">
         <v>41</v>
@@ -24845,11 +25218,11 @@
       </c>
       <c r="J177" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I177,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K177" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I177,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L177" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I177,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -24857,10 +25230,10 @@
       </c>
       <c r="M177" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I177,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md; P1-UAT-002; owner-reported live-web UAT; 2026-10-29; see Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N177" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O177" s="2"/>
     </row>
@@ -24884,7 +25257,7 @@
         <v>784</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H178" s="2" t="s">
         <v>41</v>
@@ -24894,11 +25267,11 @@
       </c>
       <c r="J178" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I178,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K178" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I178,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L178" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I178,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -24906,10 +25279,10 @@
       </c>
       <c r="M178" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I178,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-002; owner-reported live-web UAT; 2026-10-29; see Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N178" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O178" s="2"/>
     </row>
@@ -24933,7 +25306,7 @@
         <v>788</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H179" s="2" t="s">
         <v>41</v>
@@ -24943,11 +25316,11 @@
       </c>
       <c r="J179" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I179,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K179" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I179,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L179" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I179,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -24955,10 +25328,10 @@
       </c>
       <c r="M179" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I179,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; Executed: node --test tests/meals-recipe-interaction.test.cjs tests/meals-recipe-service.test.cjs tests/meals-recipe-persistence.test.cjs (19 passed, 0 failed; 2026-10-29); P1-TECH-002; node --test tests/meals-recipe-interaction.test.cjs tests/meals-recipe-service.test.cjs tests/meals-recipe-persistence.test.cjs (21 passed, 0 failed); tests/meals-recipe-interaction.test.cjs: rendered STATE-002 error/Retry/recovery across Library, Detail, Editor; persisted Favorite failure/state-preservation/retry; empty/no-match recovery assertions; Local/Test deterministic mocks; 2026-10-29</v>
       </c>
       <c r="N179" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O179" s="2"/>
     </row>
@@ -24982,7 +25355,7 @@
         <v>792</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H180" s="2" t="s">
         <v>41</v>
@@ -24992,11 +25365,11 @@
       </c>
       <c r="J180" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I180,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K180" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I180,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L180" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I180,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -25004,10 +25377,10 @@
       </c>
       <c r="M180" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I180,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; Executed: node --test tests/meals-recipe-interaction.test.cjs tests/meals-recipe-service.test.cjs tests/meals-recipe-persistence.test.cjs (19 passed, 0 failed; 2026-10-29)</v>
       </c>
       <c r="N180" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O180" s="2"/>
     </row>
@@ -25031,7 +25404,7 @@
         <v>796</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H181" s="2" t="s">
         <v>41</v>
@@ -25041,11 +25414,11 @@
       </c>
       <c r="J181" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I181,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K181" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I181,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L181" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I181,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -25053,10 +25426,10 @@
       </c>
       <c r="M181" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I181,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-002; owner-reported live-web UAT; 2026-10-29; see Phase 1 Owner UAT Findings and Requirements Change Requests.md; P1-UAT-003; owner-reported live-web UAT; 2026-10-29; see Phase 1 Owner UAT Findings and Requirements Change Requests.md; P1-UAT-004; owner-reported true-empty Recipe Library PASS; 2026-10-29; Round 4 record in Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N181" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O181" s="2"/>
     </row>
@@ -25080,7 +25453,7 @@
         <v>801</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H182" s="2" t="s">
         <v>41</v>
@@ -25090,11 +25463,11 @@
       </c>
       <c r="J182" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I182,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K182" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I182,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L182" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I182,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -25102,10 +25475,10 @@
       </c>
       <c r="M182" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I182,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md; P1-UAT-002; owner-reported live-web UAT; 2026-10-29; see Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N182" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O182" s="2"/>
     </row>
@@ -25129,7 +25502,7 @@
         <v>805</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H183" s="2" t="s">
         <v>41</v>
@@ -25154,7 +25527,7 @@
         <v>0</v>
       </c>
       <c r="N183" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O183" s="2"/>
     </row>
@@ -25178,7 +25551,7 @@
         <v>809</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H184" s="2" t="s">
         <v>41</v>
@@ -25188,11 +25561,11 @@
       </c>
       <c r="J184" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I184,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K184" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I184,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L184" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I184,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -25200,10 +25573,10 @@
       </c>
       <c r="M184" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I184,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; Executed: node --test tests/meals-recipe-interaction.test.cjs tests/meals-recipe-service.test.cjs tests/meals-recipe-persistence.test.cjs (19 passed, 0 failed; 2026-10-29); P1-TECH-002; node --test tests/meals-recipe-interaction.test.cjs tests/meals-recipe-service.test.cjs tests/meals-recipe-persistence.test.cjs (21 passed, 0 failed); tests/meals-recipe-interaction.test.cjs: rendered STATE-002 error/Retry/recovery across Library, Detail, Editor; persisted Favorite failure/state-preservation/retry; empty/no-match recovery assertions; Local/Test deterministic mocks; 2026-10-29</v>
       </c>
       <c r="N184" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O184" s="2"/>
     </row>
@@ -25218,7 +25591,7 @@
         <v>941</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E185" s="2" t="s">
         <v>98</v>
@@ -25227,7 +25600,7 @@
         <v>942</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="H185" s="2" t="s">
         <v>44</v>
@@ -25249,7 +25622,7 @@
         <v>P0B-DB-001; package 0d30359ab5cdd4aa3577c33823de1bbc80a3d4f2; spec/meals/Phase 0B Recipe Persistence Design.md section 28; meals-db-final-manifest.json SHA256 4cbbc3eac24c13860d39ee3a0d8c6ae79c638cc5967d5274d1e7ea219091f8da; complete evidence in session b7458d86-6190-4718-8779-7c2b79a30630/files</v>
       </c>
       <c r="N185" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O185" s="2"/>
     </row>
@@ -25264,7 +25637,7 @@
         <v>941</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E186" s="2" t="s">
         <v>98</v>
@@ -25273,7 +25646,7 @@
         <v>945</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="H186" s="2" t="s">
         <v>44</v>
@@ -25295,7 +25668,7 @@
         <v>P0B-DB-001; package 0d30359ab5cdd4aa3577c33823de1bbc80a3d4f2; spec/meals/Phase 0B Recipe Persistence Design.md section 28; meals-db-final-manifest.json SHA256 4cbbc3eac24c13860d39ee3a0d8c6ae79c638cc5967d5274d1e7ea219091f8da; complete evidence in session b7458d86-6190-4718-8779-7c2b79a30630/files</v>
       </c>
       <c r="N186" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O186" s="2"/>
     </row>
@@ -25310,7 +25683,7 @@
         <v>941</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E187" s="2" t="s">
         <v>98</v>
@@ -25319,7 +25692,7 @@
         <v>948</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="H187" s="2" t="s">
         <v>44</v>
@@ -25341,7 +25714,7 @@
         <v>P0B-DB-001; package 0d30359ab5cdd4aa3577c33823de1bbc80a3d4f2; spec/meals/Phase 0B Recipe Persistence Design.md section 28; meals-db-final-manifest.json SHA256 4cbbc3eac24c13860d39ee3a0d8c6ae79c638cc5967d5274d1e7ea219091f8da; complete evidence in session b7458d86-6190-4718-8779-7c2b79a30630/files</v>
       </c>
       <c r="N187" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O187" s="2"/>
     </row>
@@ -25356,7 +25729,7 @@
         <v>941</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E188" s="2" t="s">
         <v>98</v>
@@ -25365,7 +25738,7 @@
         <v>951</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="H188" s="2" t="s">
         <v>44</v>
@@ -25387,7 +25760,7 @@
         <v>P0B-DB-001; package 0d30359ab5cdd4aa3577c33823de1bbc80a3d4f2; spec/meals/Phase 0B Recipe Persistence Design.md section 28; meals-db-final-manifest.json SHA256 4cbbc3eac24c13860d39ee3a0d8c6ae79c638cc5967d5274d1e7ea219091f8da; complete evidence in session b7458d86-6190-4718-8779-7c2b79a30630/files</v>
       </c>
       <c r="N188" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O188" s="2"/>
     </row>
@@ -25402,7 +25775,7 @@
         <v>941</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>98</v>
@@ -25411,7 +25784,7 @@
         <v>954</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="H189" s="2" t="s">
         <v>44</v>
@@ -25433,7 +25806,7 @@
         <v>0</v>
       </c>
       <c r="N189" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O189" s="2"/>
     </row>
@@ -25448,7 +25821,7 @@
         <v>941</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E190" s="2" t="s">
         <v>98</v>
@@ -25457,7 +25830,7 @@
         <v>957</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="H190" s="2" t="s">
         <v>44</v>
@@ -25479,7 +25852,7 @@
         <v>P0B-DB-001; package 0d30359ab5cdd4aa3577c33823de1bbc80a3d4f2; spec/meals/Phase 0B Recipe Persistence Design.md section 28; meals-db-final-manifest.json SHA256 4cbbc3eac24c13860d39ee3a0d8c6ae79c638cc5967d5274d1e7ea219091f8da; complete evidence in session b7458d86-6190-4718-8779-7c2b79a30630/files</v>
       </c>
       <c r="N190" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O190" s="2"/>
     </row>
@@ -25494,7 +25867,7 @@
         <v>941</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E191" s="2" t="s">
         <v>98</v>
@@ -25503,7 +25876,7 @@
         <v>960</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="H191" s="2" t="s">
         <v>44</v>
@@ -25525,7 +25898,7 @@
         <v>P0B-DB-001; package 0d30359ab5cdd4aa3577c33823de1bbc80a3d4f2; spec/meals/Phase 0B Recipe Persistence Design.md section 28; meals-db-final-manifest.json SHA256 4cbbc3eac24c13860d39ee3a0d8c6ae79c638cc5967d5274d1e7ea219091f8da; complete evidence in session b7458d86-6190-4718-8779-7c2b79a30630/files</v>
       </c>
       <c r="N191" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O191" s="2"/>
     </row>
@@ -25540,7 +25913,7 @@
         <v>941</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E192" s="2" t="s">
         <v>98</v>
@@ -25549,7 +25922,7 @@
         <v>963</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="H192" s="2" t="s">
         <v>44</v>
@@ -25571,7 +25944,7 @@
         <v>0</v>
       </c>
       <c r="N192" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O192" s="2"/>
     </row>
@@ -25586,7 +25959,7 @@
         <v>941</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E193" s="2" t="s">
         <v>98</v>
@@ -25595,7 +25968,7 @@
         <v>966</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="H193" s="2" t="s">
         <v>44</v>
@@ -25617,7 +25990,7 @@
         <v>0</v>
       </c>
       <c r="N193" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O193" s="2"/>
     </row>
@@ -25632,7 +26005,7 @@
         <v>941</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E194" s="2" t="s">
         <v>98</v>
@@ -25641,7 +26014,7 @@
         <v>969</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="H194" s="2" t="s">
         <v>44</v>
@@ -25663,7 +26036,7 @@
         <v>0</v>
       </c>
       <c r="N194" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O194" s="2"/>
     </row>
@@ -25678,7 +26051,7 @@
         <v>941</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E195" s="2" t="s">
         <v>98</v>
@@ -25687,7 +26060,7 @@
         <v>972</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="H195" s="2" t="s">
         <v>44</v>
@@ -25709,7 +26082,7 @@
         <v>P0B-DB-001; package 0d30359ab5cdd4aa3577c33823de1bbc80a3d4f2; spec/meals/Phase 0B Recipe Persistence Design.md section 28; meals-db-final-manifest.json SHA256 4cbbc3eac24c13860d39ee3a0d8c6ae79c638cc5967d5274d1e7ea219091f8da; complete evidence in session b7458d86-6190-4718-8779-7c2b79a30630/files</v>
       </c>
       <c r="N195" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O195" s="2"/>
     </row>
@@ -25724,7 +26097,7 @@
         <v>941</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E196" s="2" t="s">
         <v>98</v>
@@ -25733,7 +26106,7 @@
         <v>975</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="H196" s="2" t="s">
         <v>44</v>
@@ -25755,7 +26128,7 @@
         <v>P0B-DB-001; package 0d30359ab5cdd4aa3577c33823de1bbc80a3d4f2; spec/meals/Phase 0B Recipe Persistence Design.md section 28; meals-db-final-manifest.json SHA256 4cbbc3eac24c13860d39ee3a0d8c6ae79c638cc5967d5274d1e7ea219091f8da; complete evidence in session b7458d86-6190-4718-8779-7c2b79a30630/files</v>
       </c>
       <c r="N196" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O196" s="2"/>
     </row>
@@ -25779,7 +26152,7 @@
         <v>978</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="H197" s="2" t="s">
         <v>44</v>
@@ -25801,7 +26174,7 @@
         <v>P0B-DB-001; package 0d30359ab5cdd4aa3577c33823de1bbc80a3d4f2; spec/meals/Phase 0B Recipe Persistence Design.md section 28; meals-db-final-manifest.json SHA256 4cbbc3eac24c13860d39ee3a0d8c6ae79c638cc5967d5274d1e7ea219091f8da; complete evidence in session b7458d86-6190-4718-8779-7c2b79a30630/files</v>
       </c>
       <c r="N197" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O197" s="2"/>
     </row>
@@ -25825,7 +26198,7 @@
         <v>875</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="H198" s="2" t="s">
         <v>43</v>
@@ -25850,7 +26223,7 @@
         <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N198" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O198" s="2"/>
     </row>
@@ -25874,7 +26247,7 @@
         <v>879</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="H199" s="2" t="s">
         <v>43</v>
@@ -25899,7 +26272,7 @@
         <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N199" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O199" s="2"/>
     </row>
@@ -25923,7 +26296,7 @@
         <v>883</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="H200" s="2" t="s">
         <v>43</v>
@@ -25948,7 +26321,7 @@
         <v>0</v>
       </c>
       <c r="N200" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O200" s="2"/>
     </row>
@@ -25972,7 +26345,7 @@
         <v>887</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="H201" s="2" t="s">
         <v>43</v>
@@ -25997,7 +26370,7 @@
         <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N201" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O201" s="2"/>
     </row>
@@ -26021,7 +26394,7 @@
         <v>891</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="H202" s="2" t="s">
         <v>43</v>
@@ -26046,7 +26419,7 @@
         <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
       </c>
       <c r="N202" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O202" s="2"/>
     </row>
@@ -26070,7 +26443,7 @@
         <v>895</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="H203" s="2" t="s">
         <v>43</v>
@@ -26095,7 +26468,7 @@
         <v>spec/meals/README.md#phase-0a-technical-evidence; web release validation: spec/meals/README.md#web-release-validation</v>
       </c>
       <c r="N203" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O203" s="2"/>
     </row>
@@ -26119,7 +26492,7 @@
         <v>899</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="H204" s="2" t="s">
         <v>43</v>
@@ -26144,7 +26517,7 @@
         <v>0</v>
       </c>
       <c r="N204" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O204" s="2"/>
     </row>
@@ -26168,7 +26541,7 @@
         <v>903</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="H205" s="2" t="s">
         <v>43</v>
@@ -26193,7 +26566,7 @@
         <v>P0B-DB-001; package 0d30359ab5cdd4aa3577c33823de1bbc80a3d4f2; spec/meals/Phase 0B Recipe Persistence Design.md section 28; meals-db-final-manifest.json SHA256 4cbbc3eac24c13860d39ee3a0d8c6ae79c638cc5967d5274d1e7ea219091f8da; complete evidence in session b7458d86-6190-4718-8779-7c2b79a30630/files</v>
       </c>
       <c r="N205" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O205" s="2"/>
     </row>
@@ -26217,7 +26590,7 @@
         <v>907</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="H206" s="2" t="s">
         <v>43</v>
@@ -26242,7 +26615,7 @@
         <v>spec/meals/README.md#phase-0a-technical-evidence; web release validation: spec/meals/README.md#web-release-validation</v>
       </c>
       <c r="N206" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O206" s="2"/>
     </row>
@@ -26266,7 +26639,7 @@
         <v>911</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="H207" s="2" t="s">
         <v>43</v>
@@ -26291,13 +26664,13 @@
         <v>0</v>
       </c>
       <c r="N207" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O207" s="2"/>
     </row>
     <row r="208" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="B208" s="2" t="s">
         <v>56</v>
@@ -26306,19 +26679,19 @@
         <v>78</v>
       </c>
       <c r="D208" s="2" t="s">
+        <v>1088</v>
+      </c>
+      <c r="E208" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F208" s="2" t="s">
         <v>1089</v>
       </c>
-      <c r="E208" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="F208" s="2" t="s">
-        <v>1090</v>
-      </c>
       <c r="G208" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="H208" s="2" t="s">
         <v>1085</v>
-      </c>
-      <c r="H208" s="2" t="s">
-        <v>1086</v>
       </c>
       <c r="I208" s="2"/>
       <c r="J208" s="2" t="s">
@@ -26334,7 +26707,7 @@
     </row>
     <row r="209" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="B209" s="2" t="s">
         <v>56</v>
@@ -26343,19 +26716,19 @@
         <v>78</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="E209" s="2" t="s">
         <v>98</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="G209" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="H209" s="2" t="s">
         <v>1085</v>
-      </c>
-      <c r="H209" s="2" t="s">
-        <v>1086</v>
       </c>
       <c r="I209" s="2"/>
       <c r="J209" s="2" t="s">
@@ -26371,7 +26744,7 @@
     </row>
     <row r="210" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="B210" s="2" t="s">
         <v>56</v>
@@ -26380,19 +26753,19 @@
         <v>78</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="E210" s="2" t="s">
         <v>98</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="G210" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="H210" s="2" t="s">
         <v>1085</v>
-      </c>
-      <c r="H210" s="2" t="s">
-        <v>1086</v>
       </c>
       <c r="I210" s="2"/>
       <c r="J210" s="2" t="s">
@@ -26408,7 +26781,7 @@
     </row>
     <row r="211" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="B211" s="2" t="s">
         <v>56</v>
@@ -26417,19 +26790,19 @@
         <v>78</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="E211" s="2" t="s">
         <v>98</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="G211" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="H211" s="2" t="s">
         <v>1085</v>
-      </c>
-      <c r="H211" s="2" t="s">
-        <v>1086</v>
       </c>
       <c r="I211" s="2"/>
       <c r="J211" s="2" t="s">
@@ -26445,7 +26818,7 @@
     </row>
     <row r="212" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="B212" s="2" t="s">
         <v>56</v>
@@ -26454,19 +26827,19 @@
         <v>78</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="E212" s="2" t="s">
         <v>98</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="G212" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="H212" s="2" t="s">
         <v>1085</v>
-      </c>
-      <c r="H212" s="2" t="s">
-        <v>1086</v>
       </c>
       <c r="I212" s="2"/>
       <c r="J212" s="2" t="s">
@@ -26482,7 +26855,7 @@
     </row>
     <row r="213" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="B213" s="2" t="s">
         <v>56</v>
@@ -26491,19 +26864,19 @@
         <v>78</v>
       </c>
       <c r="D213" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="E213" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F213" s="2" t="s">
         <v>1100</v>
       </c>
-      <c r="E213" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="F213" s="2" t="s">
-        <v>1101</v>
-      </c>
       <c r="G213" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="H213" s="2" t="s">
         <v>1085</v>
-      </c>
-      <c r="H213" s="2" t="s">
-        <v>1086</v>
       </c>
       <c r="I213" s="2"/>
       <c r="J213" s="2" t="s">
@@ -26519,7 +26892,7 @@
     </row>
     <row r="214" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="B214" s="2" t="s">
         <v>56</v>
@@ -26528,19 +26901,19 @@
         <v>78</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="E214" s="2" t="s">
         <v>98</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="G214" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="H214" s="2" t="s">
         <v>1085</v>
-      </c>
-      <c r="H214" s="2" t="s">
-        <v>1086</v>
       </c>
       <c r="I214" s="2"/>
       <c r="J214" s="2" t="s">
@@ -26556,7 +26929,7 @@
     </row>
     <row r="215" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="B215" s="2" t="s">
         <v>56</v>
@@ -26565,19 +26938,19 @@
         <v>78</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="E215" s="2" t="s">
         <v>98</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="G215" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="H215" s="2" t="s">
         <v>1085</v>
-      </c>
-      <c r="H215" s="2" t="s">
-        <v>1086</v>
       </c>
       <c r="I215" s="2"/>
       <c r="J215" s="2" t="s">
@@ -26593,7 +26966,7 @@
     </row>
     <row r="216" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="B216" s="2" t="s">
         <v>56</v>
@@ -26602,19 +26975,19 @@
         <v>78</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="E216" s="2" t="s">
         <v>98</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="G216" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="H216" s="2" t="s">
         <v>1085</v>
-      </c>
-      <c r="H216" s="2" t="s">
-        <v>1086</v>
       </c>
       <c r="I216" s="2"/>
       <c r="J216" s="2" t="s">
@@ -26630,7 +27003,7 @@
     </row>
     <row r="217" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="B217" s="2" t="s">
         <v>56</v>
@@ -26639,19 +27012,19 @@
         <v>78</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="E217" s="2" t="s">
         <v>98</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="G217" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="H217" s="2" t="s">
         <v>1085</v>
-      </c>
-      <c r="H217" s="2" t="s">
-        <v>1086</v>
       </c>
       <c r="I217" s="2"/>
       <c r="J217" s="2" t="s">
@@ -26685,7 +27058,7 @@
         <v>139</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H218" s="2" t="s">
         <v>41</v>
@@ -26695,11 +27068,11 @@
       </c>
       <c r="J218" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I218,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K218" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I218,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L218" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I218,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -26707,10 +27080,10 @@
       </c>
       <c r="M218" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I218,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-001; owner-reported live-web UAT; 2026-10-29; see spec/meals/Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N218" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O218" s="2"/>
     </row>
@@ -26734,7 +27107,7 @@
         <v>189</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H219" s="2" t="s">
         <v>41</v>
@@ -26744,11 +27117,11 @@
       </c>
       <c r="J219" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I219,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K219" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I219,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L219" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I219,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -26756,10 +27129,10 @@
       </c>
       <c r="M219" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I219,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-002; owner-reported live-web UAT; 2026-10-29; see Phase 1 Owner UAT Findings and Requirements Change Requests.md; P1-UAT-003; owner-reported live-web UAT; 2026-10-29; see Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N219" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O219" s="2"/>
     </row>
@@ -26783,7 +27156,7 @@
         <v>249</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H220" s="2" t="s">
         <v>41</v>
@@ -26793,11 +27166,11 @@
       </c>
       <c r="J220" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I220,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K220" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I220,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L220" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I220,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -26805,10 +27178,10 @@
       </c>
       <c r="M220" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I220,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-002; owner-reported live-web UAT; 2026-10-29; see Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N220" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O220" s="2"/>
     </row>
@@ -26832,7 +27205,7 @@
         <v>365</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H221" s="2" t="s">
         <v>41</v>
@@ -26842,11 +27215,11 @@
       </c>
       <c r="J221" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I221,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K221" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I221,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L221" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I221,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -26854,10 +27227,10 @@
       </c>
       <c r="M221" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I221,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-002; owner-reported live-web UAT; 2026-10-29; see Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N221" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O221" s="2"/>
     </row>
@@ -26881,7 +27254,7 @@
         <v>770</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H222" s="2" t="s">
         <v>41</v>
@@ -26906,7 +27279,7 @@
         <v>spec/meals/README.md#phase-0a-technical-evidence; P0-UAT-001: designated owner reported live Life Manager UAT PASS on 2026-10-28; release 8298e2e0797ddff7d2d53cc058fa41fb407ac0ab; recorded by Copilot from owner report, not automated authenticated verification</v>
       </c>
       <c r="N222" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O222" s="2"/>
     </row>
@@ -26930,7 +27303,7 @@
         <v>796</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H223" s="2" t="s">
         <v>41</v>
@@ -26940,11 +27313,11 @@
       </c>
       <c r="J223" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$L:$L,MATCH($I223,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>Ready to Test</v>
+        <v>Pass</v>
       </c>
       <c r="K223" s="7">
         <f>IFERROR(INDEX('Functional Acceptance'!$M:$M,MATCH($I223,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>0</v>
+        <v>46324</v>
       </c>
       <c r="L223" s="2">
         <f>IFERROR(INDEX('Functional Acceptance'!$N:$N,MATCH($I223,'Functional Acceptance'!$B:$B,0)),"")</f>
@@ -26952,10 +27325,10 @@
       </c>
       <c r="M223" s="2" t="str">
         <f>IFERROR(INDEX('Functional Acceptance'!$O:$O,MATCH($I223,'Functional Acceptance'!$B:$B,0)),"")</f>
-        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json</v>
+        <v>P1-TECH-001; dev baseline 8645287; spec/meals/README.md#phase-1-technical-evidence-and-limitations; phase1-focused-tests.log; phase1-full-tests.log; phase1-build-inspection.json; P1-UAT-002; owner-reported live-web UAT; 2026-10-29; see Phase 1 Owner UAT Findings and Requirements Change Requests.md; P1-UAT-003; owner-reported live-web UAT; 2026-10-29; see Phase 1 Owner UAT Findings and Requirements Change Requests.md; P1-UAT-004; owner-reported true-empty Recipe Library PASS; 2026-10-29; Round 4 record in Phase 1 Owner UAT Findings and Requirements Change Requests.md</v>
       </c>
       <c r="N223" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O223" s="2"/>
     </row>
